--- a/public/moduli/FoglioPresenze_StudioBaiocco.xlsx
+++ b/public/moduli/FoglioPresenze_StudioBaiocco.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Desktop/sito_mamma/public/moduli/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C181E254-1B3D-C549-95E2-45955CDE2F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E7D7E3-E5FC-374C-B550-04FF756CA452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17760" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presenze" sheetId="1" r:id="rId1"/>
@@ -661,19 +661,79 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="justify"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="justify"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="justify"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -691,66 +751,6 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="justify"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="justify"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="justify"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
@@ -1879,12 +1879,12 @@
   <sheetData>
     <row r="1" spans="1:44" ht="35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14"/>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="23" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="24"/>
       <c r="D1" s="24"/>
-      <c r="E1" s="23"/>
+      <c r="E1" s="28"/>
       <c r="F1" s="24"/>
       <c r="G1" s="24"/>
       <c r="H1" s="24"/>
@@ -1930,7 +1930,7 @@
       <c r="B2" s="24"/>
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="55" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="24"/>
@@ -1939,13 +1939,13 @@
       <c r="I2" s="24"/>
       <c r="J2" s="24"/>
       <c r="K2" s="24"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="30">
+      <c r="L2" s="56"/>
+      <c r="M2" s="52">
         <v>3</v>
       </c>
-      <c r="N2" s="31"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="33" t="s">
+      <c r="N2" s="53"/>
+      <c r="O2" s="54"/>
+      <c r="P2" s="55" t="s">
         <v>2</v>
       </c>
       <c r="Q2" s="24"/>
@@ -1954,12 +1954,12 @@
       <c r="T2" s="24"/>
       <c r="U2" s="24"/>
       <c r="V2" s="24"/>
-      <c r="W2" s="34"/>
-      <c r="X2" s="35">
+      <c r="W2" s="56"/>
+      <c r="X2" s="57">
         <v>2026</v>
       </c>
-      <c r="Y2" s="31"/>
-      <c r="Z2" s="32"/>
+      <c r="Y2" s="53"/>
+      <c r="Z2" s="54"/>
       <c r="AA2" s="15"/>
       <c r="AB2" s="15"/>
       <c r="AC2" s="15"/>
@@ -1981,28 +1981,28 @@
     </row>
     <row r="3" spans="1:44" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14"/>
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="51" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="24"/>
       <c r="D3" s="24"/>
-      <c r="E3" s="23"/>
+      <c r="E3" s="28"/>
       <c r="F3" s="24"/>
       <c r="G3" s="24"/>
       <c r="H3" s="24"/>
-      <c r="I3" s="23"/>
+      <c r="I3" s="28"/>
       <c r="J3" s="24"/>
       <c r="K3" s="24"/>
       <c r="L3" s="24"/>
-      <c r="M3" s="23"/>
+      <c r="M3" s="28"/>
       <c r="N3" s="24"/>
       <c r="O3" s="24"/>
       <c r="P3" s="24"/>
-      <c r="Q3" s="23"/>
+      <c r="Q3" s="28"/>
       <c r="R3" s="24"/>
       <c r="S3" s="24"/>
       <c r="T3" s="24"/>
-      <c r="U3" s="23"/>
+      <c r="U3" s="28"/>
       <c r="V3" s="24"/>
       <c r="W3" s="15"/>
       <c r="X3" s="15"/>
@@ -2032,7 +2032,7 @@
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
       <c r="D4" s="24"/>
-      <c r="E4" s="36" t="s">
+      <c r="E4" s="58" t="s">
         <v>25</v>
       </c>
       <c r="F4" s="24"/>
@@ -2077,13 +2077,13 @@
     </row>
     <row r="5" spans="1:44" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14"/>
-      <c r="B5" s="47" t="s">
+      <c r="B5" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="55" t="s">
+      <c r="C5" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="49"/>
+      <c r="D5" s="50"/>
       <c r="E5" s="1">
         <v>1</v>
       </c>
@@ -2177,39 +2177,39 @@
       <c r="AI5" s="1">
         <v>31</v>
       </c>
-      <c r="AJ5" s="25" t="s">
+      <c r="AJ5" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="AK5" s="25" t="s">
+      <c r="AK5" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="AL5" s="25" t="s">
+      <c r="AL5" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="AM5" s="25" t="s">
+      <c r="AM5" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="AN5" s="25" t="s">
+      <c r="AN5" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="AO5" s="25" t="s">
+      <c r="AO5" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="AP5" s="25" t="s">
+      <c r="AP5" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="AQ5" s="25" t="s">
+      <c r="AQ5" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="AR5" s="25" t="s">
+      <c r="AR5" s="45" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="14"/>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
+      <c r="B6" s="37"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
       <c r="E6" s="2" t="str">
         <f>IFERROR(IF(1&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,1),2),"L","M","M","G","V","S","D")),"")</f>
         <v>D</v>
@@ -2334,22 +2334,22 @@
         <f>IFERROR(IF(31&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,31),2),"L","M","M","G","V","S","D")),"")</f>
         <v>M</v>
       </c>
-      <c r="AJ6" s="26"/>
-      <c r="AK6" s="26"/>
-      <c r="AL6" s="26"/>
-      <c r="AM6" s="26"/>
-      <c r="AN6" s="26"/>
-      <c r="AO6" s="26"/>
-      <c r="AP6" s="26"/>
-      <c r="AQ6" s="26"/>
-      <c r="AR6" s="26"/>
+      <c r="AJ6" s="46"/>
+      <c r="AK6" s="46"/>
+      <c r="AL6" s="46"/>
+      <c r="AM6" s="46"/>
+      <c r="AN6" s="46"/>
+      <c r="AO6" s="46"/>
+      <c r="AP6" s="46"/>
+      <c r="AQ6" s="46"/>
+      <c r="AR6" s="46"/>
     </row>
     <row r="7" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="39"/>
-      <c r="B7" s="45">
+      <c r="A7" s="42"/>
+      <c r="B7" s="47">
         <v>1</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="29" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -2396,16 +2396,16 @@
       <c r="AN7" s="5"/>
       <c r="AO7" s="5"/>
       <c r="AP7" s="5"/>
-      <c r="AQ7" s="46">
+      <c r="AQ7" s="48">
         <f>COUNTIF(E7:AI7,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR7" s="42"/>
+      <c r="AR7" s="25"/>
     </row>
     <row r="8" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="40"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
+      <c r="A8" s="43"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
       <c r="D8" s="6" t="s">
         <v>17</v>
       </c>
@@ -2450,13 +2450,13 @@
       <c r="AN8" s="5"/>
       <c r="AO8" s="5"/>
       <c r="AP8" s="5"/>
-      <c r="AQ8" s="28"/>
-      <c r="AR8" s="43"/>
+      <c r="AQ8" s="30"/>
+      <c r="AR8" s="26"/>
     </row>
     <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="40"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
+      <c r="A9" s="43"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
       <c r="D9" s="7" t="s">
         <v>18</v>
       </c>
@@ -2501,13 +2501,13 @@
       <c r="AN9" s="5"/>
       <c r="AO9" s="5"/>
       <c r="AP9" s="5"/>
-      <c r="AQ9" s="28"/>
-      <c r="AR9" s="43"/>
+      <c r="AQ9" s="30"/>
+      <c r="AR9" s="26"/>
     </row>
     <row r="10" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="40"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
+      <c r="A10" s="43"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
       <c r="D10" s="8" t="s">
         <v>19</v>
       </c>
@@ -2552,13 +2552,13 @@
       <c r="AN10" s="5"/>
       <c r="AO10" s="5"/>
       <c r="AP10" s="5"/>
-      <c r="AQ10" s="28"/>
-      <c r="AR10" s="43"/>
+      <c r="AQ10" s="30"/>
+      <c r="AR10" s="26"/>
     </row>
     <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="40"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
+      <c r="A11" s="43"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
       <c r="D11" s="9" t="s">
         <v>20</v>
       </c>
@@ -2603,13 +2603,13 @@
       </c>
       <c r="AO11" s="5"/>
       <c r="AP11" s="5"/>
-      <c r="AQ11" s="28"/>
-      <c r="AR11" s="43"/>
+      <c r="AQ11" s="30"/>
+      <c r="AR11" s="26"/>
     </row>
     <row r="12" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="40"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
+      <c r="A12" s="43"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
       <c r="D12" s="9" t="s">
         <v>21</v>
       </c>
@@ -2654,13 +2654,13 @@
         <v>0</v>
       </c>
       <c r="AP12" s="5"/>
-      <c r="AQ12" s="28"/>
-      <c r="AR12" s="43"/>
+      <c r="AQ12" s="30"/>
+      <c r="AR12" s="26"/>
     </row>
     <row r="13" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="40"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
+      <c r="A13" s="43"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
       <c r="D13" s="10" t="s">
         <v>22</v>
       </c>
@@ -2705,15 +2705,15 @@
         <f>SUM(E13:AI13)</f>
         <v>0</v>
       </c>
-      <c r="AQ13" s="29"/>
-      <c r="AR13" s="44"/>
+      <c r="AQ13" s="31"/>
+      <c r="AR13" s="27"/>
     </row>
     <row r="14" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="39"/>
+      <c r="A14" s="42"/>
       <c r="B14" s="38">
         <v>2</v>
       </c>
-      <c r="C14" s="37" t="s">
+      <c r="C14" s="29" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -2760,16 +2760,16 @@
       <c r="AN14" s="5"/>
       <c r="AO14" s="5"/>
       <c r="AP14" s="5"/>
-      <c r="AQ14" s="27">
+      <c r="AQ14" s="35">
         <f>COUNTIF(E14:AI14,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR14" s="42"/>
+      <c r="AR14" s="25"/>
     </row>
     <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="40"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
+      <c r="A15" s="43"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
       <c r="D15" s="6" t="s">
         <v>17</v>
       </c>
@@ -2814,13 +2814,13 @@
       <c r="AN15" s="5"/>
       <c r="AO15" s="5"/>
       <c r="AP15" s="5"/>
-      <c r="AQ15" s="28"/>
-      <c r="AR15" s="43"/>
+      <c r="AQ15" s="30"/>
+      <c r="AR15" s="26"/>
     </row>
     <row r="16" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="40"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
+      <c r="A16" s="43"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
       <c r="D16" s="7" t="s">
         <v>18</v>
       </c>
@@ -2865,13 +2865,13 @@
       <c r="AN16" s="5"/>
       <c r="AO16" s="5"/>
       <c r="AP16" s="5"/>
-      <c r="AQ16" s="28"/>
-      <c r="AR16" s="43"/>
+      <c r="AQ16" s="30"/>
+      <c r="AR16" s="26"/>
     </row>
     <row r="17" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="40"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
+      <c r="A17" s="43"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
       <c r="D17" s="8" t="s">
         <v>19</v>
       </c>
@@ -2916,13 +2916,13 @@
       <c r="AN17" s="5"/>
       <c r="AO17" s="5"/>
       <c r="AP17" s="5"/>
-      <c r="AQ17" s="28"/>
-      <c r="AR17" s="43"/>
+      <c r="AQ17" s="30"/>
+      <c r="AR17" s="26"/>
     </row>
     <row r="18" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="40"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
+      <c r="A18" s="43"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
       <c r="D18" s="9" t="s">
         <v>20</v>
       </c>
@@ -2967,13 +2967,13 @@
       </c>
       <c r="AO18" s="5"/>
       <c r="AP18" s="5"/>
-      <c r="AQ18" s="28"/>
-      <c r="AR18" s="43"/>
+      <c r="AQ18" s="30"/>
+      <c r="AR18" s="26"/>
     </row>
     <row r="19" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="40"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
+      <c r="A19" s="43"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
       <c r="D19" s="9" t="s">
         <v>21</v>
       </c>
@@ -3018,13 +3018,13 @@
         <v>0</v>
       </c>
       <c r="AP19" s="5"/>
-      <c r="AQ19" s="28"/>
-      <c r="AR19" s="43"/>
+      <c r="AQ19" s="30"/>
+      <c r="AR19" s="26"/>
     </row>
     <row r="20" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="40"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
+      <c r="A20" s="43"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
       <c r="D20" s="10" t="s">
         <v>22</v>
       </c>
@@ -3069,15 +3069,15 @@
         <f>SUM(E20:AI20)</f>
         <v>0</v>
       </c>
-      <c r="AQ20" s="29"/>
-      <c r="AR20" s="44"/>
+      <c r="AQ20" s="31"/>
+      <c r="AR20" s="27"/>
     </row>
     <row r="21" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="39"/>
+      <c r="A21" s="42"/>
       <c r="B21" s="38">
         <v>3</v>
       </c>
-      <c r="C21" s="37" t="s">
+      <c r="C21" s="29" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3" t="s">
@@ -3124,16 +3124,16 @@
       <c r="AN21" s="5"/>
       <c r="AO21" s="5"/>
       <c r="AP21" s="5"/>
-      <c r="AQ21" s="27">
+      <c r="AQ21" s="35">
         <f>COUNTIF(E21:AI21,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR21" s="42"/>
+      <c r="AR21" s="25"/>
     </row>
     <row r="22" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="40"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
+      <c r="A22" s="43"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="30"/>
       <c r="D22" s="6" t="s">
         <v>17</v>
       </c>
@@ -3178,13 +3178,13 @@
       <c r="AN22" s="5"/>
       <c r="AO22" s="5"/>
       <c r="AP22" s="5"/>
-      <c r="AQ22" s="28"/>
-      <c r="AR22" s="43"/>
+      <c r="AQ22" s="30"/>
+      <c r="AR22" s="26"/>
     </row>
     <row r="23" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="40"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
+      <c r="A23" s="43"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
       <c r="D23" s="7" t="s">
         <v>18</v>
       </c>
@@ -3229,13 +3229,13 @@
       <c r="AN23" s="5"/>
       <c r="AO23" s="5"/>
       <c r="AP23" s="5"/>
-      <c r="AQ23" s="28"/>
-      <c r="AR23" s="43"/>
+      <c r="AQ23" s="30"/>
+      <c r="AR23" s="26"/>
     </row>
     <row r="24" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="40"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
+      <c r="A24" s="43"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="30"/>
       <c r="D24" s="8" t="s">
         <v>19</v>
       </c>
@@ -3280,13 +3280,13 @@
       <c r="AN24" s="5"/>
       <c r="AO24" s="5"/>
       <c r="AP24" s="5"/>
-      <c r="AQ24" s="28"/>
-      <c r="AR24" s="43"/>
+      <c r="AQ24" s="30"/>
+      <c r="AR24" s="26"/>
     </row>
     <row r="25" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="40"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
+      <c r="A25" s="43"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
       <c r="D25" s="9" t="s">
         <v>20</v>
       </c>
@@ -3331,13 +3331,13 @@
       </c>
       <c r="AO25" s="5"/>
       <c r="AP25" s="5"/>
-      <c r="AQ25" s="28"/>
-      <c r="AR25" s="43"/>
+      <c r="AQ25" s="30"/>
+      <c r="AR25" s="26"/>
     </row>
     <row r="26" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="40"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
+      <c r="A26" s="43"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
       <c r="D26" s="9" t="s">
         <v>21</v>
       </c>
@@ -3382,13 +3382,13 @@
         <v>0</v>
       </c>
       <c r="AP26" s="5"/>
-      <c r="AQ26" s="28"/>
-      <c r="AR26" s="43"/>
+      <c r="AQ26" s="30"/>
+      <c r="AR26" s="26"/>
     </row>
     <row r="27" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="40"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
+      <c r="A27" s="43"/>
+      <c r="B27" s="31"/>
+      <c r="C27" s="31"/>
       <c r="D27" s="10" t="s">
         <v>22</v>
       </c>
@@ -3433,15 +3433,15 @@
         <f>SUM(E27:AI27)</f>
         <v>0</v>
       </c>
-      <c r="AQ27" s="29"/>
-      <c r="AR27" s="44"/>
+      <c r="AQ27" s="31"/>
+      <c r="AR27" s="27"/>
     </row>
     <row r="28" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="39"/>
+      <c r="A28" s="42"/>
       <c r="B28" s="38">
         <v>4</v>
       </c>
-      <c r="C28" s="37" t="s">
+      <c r="C28" s="29" t="s">
         <v>15</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -3488,16 +3488,16 @@
       <c r="AN28" s="5"/>
       <c r="AO28" s="5"/>
       <c r="AP28" s="5"/>
-      <c r="AQ28" s="27">
+      <c r="AQ28" s="35">
         <f>COUNTIF(E28:AI28,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR28" s="42"/>
+      <c r="AR28" s="25"/>
     </row>
     <row r="29" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="40"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
+      <c r="A29" s="43"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
       <c r="D29" s="6" t="s">
         <v>17</v>
       </c>
@@ -3542,13 +3542,13 @@
       <c r="AN29" s="5"/>
       <c r="AO29" s="5"/>
       <c r="AP29" s="5"/>
-      <c r="AQ29" s="28"/>
-      <c r="AR29" s="43"/>
+      <c r="AQ29" s="30"/>
+      <c r="AR29" s="26"/>
     </row>
     <row r="30" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="40"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
+      <c r="A30" s="43"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="30"/>
       <c r="D30" s="7" t="s">
         <v>18</v>
       </c>
@@ -3593,13 +3593,13 @@
       <c r="AN30" s="5"/>
       <c r="AO30" s="5"/>
       <c r="AP30" s="5"/>
-      <c r="AQ30" s="28"/>
-      <c r="AR30" s="43"/>
+      <c r="AQ30" s="30"/>
+      <c r="AR30" s="26"/>
     </row>
     <row r="31" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="40"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
+      <c r="A31" s="43"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
       <c r="D31" s="8" t="s">
         <v>19</v>
       </c>
@@ -3644,13 +3644,13 @@
       <c r="AN31" s="5"/>
       <c r="AO31" s="5"/>
       <c r="AP31" s="5"/>
-      <c r="AQ31" s="28"/>
-      <c r="AR31" s="43"/>
+      <c r="AQ31" s="30"/>
+      <c r="AR31" s="26"/>
     </row>
     <row r="32" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="40"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
+      <c r="A32" s="43"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
       <c r="D32" s="9" t="s">
         <v>20</v>
       </c>
@@ -3695,13 +3695,13 @@
       </c>
       <c r="AO32" s="5"/>
       <c r="AP32" s="5"/>
-      <c r="AQ32" s="28"/>
-      <c r="AR32" s="43"/>
+      <c r="AQ32" s="30"/>
+      <c r="AR32" s="26"/>
     </row>
     <row r="33" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="40"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
+      <c r="A33" s="43"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="30"/>
       <c r="D33" s="9" t="s">
         <v>21</v>
       </c>
@@ -3746,13 +3746,13 @@
         <v>0</v>
       </c>
       <c r="AP33" s="5"/>
-      <c r="AQ33" s="28"/>
-      <c r="AR33" s="43"/>
+      <c r="AQ33" s="30"/>
+      <c r="AR33" s="26"/>
     </row>
     <row r="34" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="40"/>
-      <c r="B34" s="29"/>
-      <c r="C34" s="29"/>
+      <c r="A34" s="43"/>
+      <c r="B34" s="31"/>
+      <c r="C34" s="31"/>
       <c r="D34" s="10" t="s">
         <v>22</v>
       </c>
@@ -3797,15 +3797,15 @@
         <f>SUM(E34:AI34)</f>
         <v>0</v>
       </c>
-      <c r="AQ34" s="29"/>
-      <c r="AR34" s="44"/>
+      <c r="AQ34" s="31"/>
+      <c r="AR34" s="27"/>
     </row>
     <row r="35" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="39"/>
+      <c r="A35" s="42"/>
       <c r="B35" s="38">
         <v>5</v>
       </c>
-      <c r="C35" s="37" t="s">
+      <c r="C35" s="29" t="s">
         <v>15</v>
       </c>
       <c r="D35" s="3" t="s">
@@ -3852,16 +3852,16 @@
       <c r="AN35" s="5"/>
       <c r="AO35" s="5"/>
       <c r="AP35" s="5"/>
-      <c r="AQ35" s="27">
+      <c r="AQ35" s="35">
         <f>COUNTIF(E35:AI35,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR35" s="42"/>
+      <c r="AR35" s="25"/>
     </row>
     <row r="36" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="40"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
+      <c r="A36" s="43"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
       <c r="D36" s="6" t="s">
         <v>17</v>
       </c>
@@ -3906,13 +3906,13 @@
       <c r="AN36" s="5"/>
       <c r="AO36" s="5"/>
       <c r="AP36" s="5"/>
-      <c r="AQ36" s="28"/>
-      <c r="AR36" s="43"/>
+      <c r="AQ36" s="30"/>
+      <c r="AR36" s="26"/>
     </row>
     <row r="37" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="40"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
+      <c r="A37" s="43"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
       <c r="D37" s="7" t="s">
         <v>18</v>
       </c>
@@ -3957,13 +3957,13 @@
       <c r="AN37" s="5"/>
       <c r="AO37" s="5"/>
       <c r="AP37" s="5"/>
-      <c r="AQ37" s="28"/>
-      <c r="AR37" s="43"/>
+      <c r="AQ37" s="30"/>
+      <c r="AR37" s="26"/>
     </row>
     <row r="38" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="40"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
+      <c r="A38" s="43"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
       <c r="D38" s="8" t="s">
         <v>19</v>
       </c>
@@ -4008,13 +4008,13 @@
       <c r="AN38" s="5"/>
       <c r="AO38" s="5"/>
       <c r="AP38" s="5"/>
-      <c r="AQ38" s="28"/>
-      <c r="AR38" s="43"/>
+      <c r="AQ38" s="30"/>
+      <c r="AR38" s="26"/>
     </row>
     <row r="39" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="40"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="28"/>
+      <c r="A39" s="43"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
       <c r="D39" s="9" t="s">
         <v>20</v>
       </c>
@@ -4059,13 +4059,13 @@
       </c>
       <c r="AO39" s="5"/>
       <c r="AP39" s="5"/>
-      <c r="AQ39" s="28"/>
-      <c r="AR39" s="43"/>
+      <c r="AQ39" s="30"/>
+      <c r="AR39" s="26"/>
     </row>
     <row r="40" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="40"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
+      <c r="A40" s="43"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
       <c r="D40" s="9" t="s">
         <v>21</v>
       </c>
@@ -4110,13 +4110,13 @@
         <v>0</v>
       </c>
       <c r="AP40" s="5"/>
-      <c r="AQ40" s="28"/>
-      <c r="AR40" s="43"/>
+      <c r="AQ40" s="30"/>
+      <c r="AR40" s="26"/>
     </row>
     <row r="41" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="40"/>
-      <c r="B41" s="29"/>
-      <c r="C41" s="29"/>
+      <c r="A41" s="43"/>
+      <c r="B41" s="31"/>
+      <c r="C41" s="31"/>
       <c r="D41" s="10" t="s">
         <v>22</v>
       </c>
@@ -4161,15 +4161,15 @@
         <f>SUM(E41:AI41)</f>
         <v>0</v>
       </c>
-      <c r="AQ41" s="29"/>
-      <c r="AR41" s="44"/>
+      <c r="AQ41" s="31"/>
+      <c r="AR41" s="27"/>
     </row>
     <row r="42" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="39"/>
+      <c r="A42" s="42"/>
       <c r="B42" s="38">
         <v>6</v>
       </c>
-      <c r="C42" s="37" t="s">
+      <c r="C42" s="29" t="s">
         <v>15</v>
       </c>
       <c r="D42" s="3" t="s">
@@ -4216,16 +4216,16 @@
       <c r="AN42" s="5"/>
       <c r="AO42" s="5"/>
       <c r="AP42" s="5"/>
-      <c r="AQ42" s="27">
+      <c r="AQ42" s="35">
         <f>COUNTIF(E42:AI42,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR42" s="42"/>
+      <c r="AR42" s="25"/>
     </row>
     <row r="43" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="40"/>
-      <c r="B43" s="28"/>
-      <c r="C43" s="28"/>
+      <c r="A43" s="43"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
       <c r="D43" s="6" t="s">
         <v>17</v>
       </c>
@@ -4270,13 +4270,13 @@
       <c r="AN43" s="5"/>
       <c r="AO43" s="5"/>
       <c r="AP43" s="5"/>
-      <c r="AQ43" s="28"/>
-      <c r="AR43" s="43"/>
+      <c r="AQ43" s="30"/>
+      <c r="AR43" s="26"/>
     </row>
     <row r="44" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="40"/>
-      <c r="B44" s="28"/>
-      <c r="C44" s="28"/>
+      <c r="A44" s="43"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
       <c r="D44" s="7" t="s">
         <v>18</v>
       </c>
@@ -4321,13 +4321,13 @@
       <c r="AN44" s="5"/>
       <c r="AO44" s="5"/>
       <c r="AP44" s="5"/>
-      <c r="AQ44" s="28"/>
-      <c r="AR44" s="43"/>
+      <c r="AQ44" s="30"/>
+      <c r="AR44" s="26"/>
     </row>
     <row r="45" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="40"/>
-      <c r="B45" s="28"/>
-      <c r="C45" s="28"/>
+      <c r="A45" s="43"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="30"/>
       <c r="D45" s="8" t="s">
         <v>19</v>
       </c>
@@ -4372,13 +4372,13 @@
       <c r="AN45" s="5"/>
       <c r="AO45" s="5"/>
       <c r="AP45" s="5"/>
-      <c r="AQ45" s="28"/>
-      <c r="AR45" s="43"/>
+      <c r="AQ45" s="30"/>
+      <c r="AR45" s="26"/>
     </row>
     <row r="46" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="40"/>
-      <c r="B46" s="28"/>
-      <c r="C46" s="28"/>
+      <c r="A46" s="43"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
       <c r="D46" s="9" t="s">
         <v>20</v>
       </c>
@@ -4423,13 +4423,13 @@
       </c>
       <c r="AO46" s="5"/>
       <c r="AP46" s="5"/>
-      <c r="AQ46" s="28"/>
-      <c r="AR46" s="43"/>
+      <c r="AQ46" s="30"/>
+      <c r="AR46" s="26"/>
     </row>
     <row r="47" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="40"/>
-      <c r="B47" s="28"/>
-      <c r="C47" s="28"/>
+      <c r="A47" s="43"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
       <c r="D47" s="9" t="s">
         <v>21</v>
       </c>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="AP47" s="5"/>
-      <c r="AQ47" s="28"/>
-      <c r="AR47" s="43"/>
+      <c r="AQ47" s="30"/>
+      <c r="AR47" s="26"/>
     </row>
     <row r="48" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="40"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
+      <c r="A48" s="43"/>
+      <c r="B48" s="31"/>
+      <c r="C48" s="31"/>
       <c r="D48" s="10" t="s">
         <v>22</v>
       </c>
@@ -4525,15 +4525,15 @@
         <f>SUM(E48:AI48)</f>
         <v>0</v>
       </c>
-      <c r="AQ48" s="29"/>
-      <c r="AR48" s="44"/>
+      <c r="AQ48" s="31"/>
+      <c r="AR48" s="27"/>
     </row>
     <row r="49" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="39"/>
+      <c r="A49" s="42"/>
       <c r="B49" s="38">
         <v>7</v>
       </c>
-      <c r="C49" s="50" t="s">
+      <c r="C49" s="44" t="s">
         <v>15</v>
       </c>
       <c r="D49" s="3" t="s">
@@ -4580,16 +4580,16 @@
       <c r="AN49" s="5"/>
       <c r="AO49" s="5"/>
       <c r="AP49" s="5"/>
-      <c r="AQ49" s="27">
+      <c r="AQ49" s="35">
         <f>COUNTIF(E49:AI49,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR49" s="42"/>
+      <c r="AR49" s="25"/>
     </row>
     <row r="50" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="40"/>
-      <c r="B50" s="28"/>
-      <c r="C50" s="28"/>
+      <c r="A50" s="43"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="30"/>
       <c r="D50" s="6" t="s">
         <v>17</v>
       </c>
@@ -4634,13 +4634,13 @@
       <c r="AN50" s="5"/>
       <c r="AO50" s="5"/>
       <c r="AP50" s="5"/>
-      <c r="AQ50" s="28"/>
-      <c r="AR50" s="43"/>
+      <c r="AQ50" s="30"/>
+      <c r="AR50" s="26"/>
     </row>
     <row r="51" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="40"/>
-      <c r="B51" s="28"/>
-      <c r="C51" s="28"/>
+      <c r="A51" s="43"/>
+      <c r="B51" s="30"/>
+      <c r="C51" s="30"/>
       <c r="D51" s="7" t="s">
         <v>18</v>
       </c>
@@ -4685,13 +4685,13 @@
       <c r="AN51" s="5"/>
       <c r="AO51" s="5"/>
       <c r="AP51" s="5"/>
-      <c r="AQ51" s="28"/>
-      <c r="AR51" s="43"/>
+      <c r="AQ51" s="30"/>
+      <c r="AR51" s="26"/>
     </row>
     <row r="52" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="40"/>
-      <c r="B52" s="28"/>
-      <c r="C52" s="28"/>
+      <c r="A52" s="43"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
       <c r="D52" s="8" t="s">
         <v>19</v>
       </c>
@@ -4736,13 +4736,13 @@
       <c r="AN52" s="5"/>
       <c r="AO52" s="5"/>
       <c r="AP52" s="5"/>
-      <c r="AQ52" s="28"/>
-      <c r="AR52" s="43"/>
+      <c r="AQ52" s="30"/>
+      <c r="AR52" s="26"/>
     </row>
     <row r="53" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="40"/>
-      <c r="B53" s="28"/>
-      <c r="C53" s="28"/>
+      <c r="A53" s="43"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
       <c r="D53" s="9" t="s">
         <v>20</v>
       </c>
@@ -4787,13 +4787,13 @@
       </c>
       <c r="AO53" s="5"/>
       <c r="AP53" s="5"/>
-      <c r="AQ53" s="28"/>
-      <c r="AR53" s="43"/>
+      <c r="AQ53" s="30"/>
+      <c r="AR53" s="26"/>
     </row>
     <row r="54" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="40"/>
-      <c r="B54" s="28"/>
-      <c r="C54" s="28"/>
+      <c r="A54" s="43"/>
+      <c r="B54" s="30"/>
+      <c r="C54" s="30"/>
       <c r="D54" s="9" t="s">
         <v>21</v>
       </c>
@@ -4838,13 +4838,13 @@
         <v>0</v>
       </c>
       <c r="AP54" s="5"/>
-      <c r="AQ54" s="28"/>
-      <c r="AR54" s="43"/>
+      <c r="AQ54" s="30"/>
+      <c r="AR54" s="26"/>
     </row>
     <row r="55" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="40"/>
-      <c r="B55" s="29"/>
-      <c r="C55" s="29"/>
+      <c r="A55" s="43"/>
+      <c r="B55" s="31"/>
+      <c r="C55" s="31"/>
       <c r="D55" s="10" t="s">
         <v>22</v>
       </c>
@@ -4889,15 +4889,15 @@
         <f>SUM(E55:AI55)</f>
         <v>0</v>
       </c>
-      <c r="AQ55" s="29"/>
-      <c r="AR55" s="44"/>
+      <c r="AQ55" s="31"/>
+      <c r="AR55" s="27"/>
     </row>
     <row r="56" spans="1:44" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="39"/>
+      <c r="A56" s="42"/>
       <c r="B56" s="38">
         <v>8</v>
       </c>
-      <c r="C56" s="50" t="s">
+      <c r="C56" s="44" t="s">
         <v>15</v>
       </c>
       <c r="D56" s="3" t="s">
@@ -4944,16 +4944,16 @@
       <c r="AN56" s="5"/>
       <c r="AO56" s="5"/>
       <c r="AP56" s="5"/>
-      <c r="AQ56" s="27">
+      <c r="AQ56" s="35">
         <f>COUNTIF(E56:AI56,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR56" s="42"/>
+      <c r="AR56" s="25"/>
     </row>
     <row r="57" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="40"/>
-      <c r="B57" s="28"/>
-      <c r="C57" s="28"/>
+      <c r="A57" s="43"/>
+      <c r="B57" s="30"/>
+      <c r="C57" s="30"/>
       <c r="D57" s="6" t="s">
         <v>17</v>
       </c>
@@ -4998,13 +4998,13 @@
       <c r="AN57" s="5"/>
       <c r="AO57" s="5"/>
       <c r="AP57" s="5"/>
-      <c r="AQ57" s="28"/>
-      <c r="AR57" s="43"/>
+      <c r="AQ57" s="30"/>
+      <c r="AR57" s="26"/>
     </row>
     <row r="58" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="40"/>
-      <c r="B58" s="28"/>
-      <c r="C58" s="28"/>
+      <c r="A58" s="43"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
       <c r="D58" s="7" t="s">
         <v>18</v>
       </c>
@@ -5049,13 +5049,13 @@
       <c r="AN58" s="5"/>
       <c r="AO58" s="5"/>
       <c r="AP58" s="5"/>
-      <c r="AQ58" s="28"/>
-      <c r="AR58" s="43"/>
+      <c r="AQ58" s="30"/>
+      <c r="AR58" s="26"/>
     </row>
     <row r="59" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="40"/>
-      <c r="B59" s="28"/>
-      <c r="C59" s="28"/>
+      <c r="A59" s="43"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
       <c r="D59" s="8" t="s">
         <v>19</v>
       </c>
@@ -5100,13 +5100,13 @@
       <c r="AN59" s="5"/>
       <c r="AO59" s="5"/>
       <c r="AP59" s="5"/>
-      <c r="AQ59" s="28"/>
-      <c r="AR59" s="43"/>
+      <c r="AQ59" s="30"/>
+      <c r="AR59" s="26"/>
     </row>
     <row r="60" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="40"/>
-      <c r="B60" s="28"/>
-      <c r="C60" s="28"/>
+      <c r="A60" s="43"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="30"/>
       <c r="D60" s="9" t="s">
         <v>20</v>
       </c>
@@ -5151,13 +5151,13 @@
       </c>
       <c r="AO60" s="5"/>
       <c r="AP60" s="5"/>
-      <c r="AQ60" s="28"/>
-      <c r="AR60" s="43"/>
+      <c r="AQ60" s="30"/>
+      <c r="AR60" s="26"/>
     </row>
     <row r="61" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="40"/>
-      <c r="B61" s="28"/>
-      <c r="C61" s="28"/>
+      <c r="A61" s="43"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
       <c r="D61" s="9" t="s">
         <v>21</v>
       </c>
@@ -5202,13 +5202,13 @@
         <v>0</v>
       </c>
       <c r="AP61" s="5"/>
-      <c r="AQ61" s="28"/>
-      <c r="AR61" s="43"/>
+      <c r="AQ61" s="30"/>
+      <c r="AR61" s="26"/>
     </row>
     <row r="62" spans="1:44" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="40"/>
-      <c r="B62" s="29"/>
-      <c r="C62" s="29"/>
+      <c r="A62" s="43"/>
+      <c r="B62" s="31"/>
+      <c r="C62" s="31"/>
       <c r="D62" s="10" t="s">
         <v>22</v>
       </c>
@@ -5253,47 +5253,47 @@
         <f>SUM(E62:AI62)</f>
         <v>0</v>
       </c>
-      <c r="AQ62" s="29"/>
-      <c r="AR62" s="44"/>
+      <c r="AQ62" s="31"/>
+      <c r="AR62" s="27"/>
     </row>
     <row r="63" spans="1:44" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="14"/>
-      <c r="B63" s="56" t="s">
+      <c r="B63" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C63" s="53"/>
-      <c r="D63" s="54"/>
-      <c r="E63" s="52"/>
-      <c r="F63" s="53"/>
-      <c r="G63" s="53"/>
-      <c r="H63" s="53"/>
-      <c r="I63" s="53"/>
-      <c r="J63" s="53"/>
-      <c r="K63" s="53"/>
-      <c r="L63" s="53"/>
-      <c r="M63" s="53"/>
-      <c r="N63" s="53"/>
-      <c r="O63" s="53"/>
-      <c r="P63" s="53"/>
-      <c r="Q63" s="53"/>
-      <c r="R63" s="53"/>
-      <c r="S63" s="53"/>
-      <c r="T63" s="53"/>
-      <c r="U63" s="53"/>
-      <c r="V63" s="53"/>
-      <c r="W63" s="53"/>
-      <c r="X63" s="53"/>
-      <c r="Y63" s="53"/>
-      <c r="Z63" s="53"/>
-      <c r="AA63" s="53"/>
-      <c r="AB63" s="53"/>
-      <c r="AC63" s="53"/>
-      <c r="AD63" s="53"/>
-      <c r="AE63" s="53"/>
-      <c r="AF63" s="53"/>
-      <c r="AG63" s="53"/>
-      <c r="AH63" s="53"/>
-      <c r="AI63" s="54"/>
+      <c r="C63" s="33"/>
+      <c r="D63" s="34"/>
+      <c r="E63" s="32"/>
+      <c r="F63" s="33"/>
+      <c r="G63" s="33"/>
+      <c r="H63" s="33"/>
+      <c r="I63" s="33"/>
+      <c r="J63" s="33"/>
+      <c r="K63" s="33"/>
+      <c r="L63" s="33"/>
+      <c r="M63" s="33"/>
+      <c r="N63" s="33"/>
+      <c r="O63" s="33"/>
+      <c r="P63" s="33"/>
+      <c r="Q63" s="33"/>
+      <c r="R63" s="33"/>
+      <c r="S63" s="33"/>
+      <c r="T63" s="33"/>
+      <c r="U63" s="33"/>
+      <c r="V63" s="33"/>
+      <c r="W63" s="33"/>
+      <c r="X63" s="33"/>
+      <c r="Y63" s="33"/>
+      <c r="Z63" s="33"/>
+      <c r="AA63" s="33"/>
+      <c r="AB63" s="33"/>
+      <c r="AC63" s="33"/>
+      <c r="AD63" s="33"/>
+      <c r="AE63" s="33"/>
+      <c r="AF63" s="33"/>
+      <c r="AG63" s="33"/>
+      <c r="AH63" s="33"/>
+      <c r="AI63" s="34"/>
       <c r="AJ63" s="13">
         <f t="shared" ref="AJ63:AP63" si="0">SUM(AJ7:AJ55)</f>
         <v>0</v>
@@ -5322,13 +5322,66 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AQ63" s="57" t="s">
+      <c r="AQ63" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="AR63" s="58"/>
+      <c r="AR63" s="41"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="dtCmCygegEzU/8/F3QBsKPNjtVleaM7WtfwWcPHRyLFI/g9F9yeK9q8Y+arnGvRhl52+eGvwv8+6dNEpi+XXkw==" saltValue="7ViFD7S7TvPRkvNcrjPlFA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="68">
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="M3:P3"/>
+    <mergeCell ref="AP5:AP6"/>
+    <mergeCell ref="AQ21:AQ27"/>
+    <mergeCell ref="E1:V1"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="P2:W2"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="E2:L2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="E4:AQ4"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="A28:A34"/>
+    <mergeCell ref="A14:A20"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="AR42:AR48"/>
+    <mergeCell ref="AQ28:AQ34"/>
+    <mergeCell ref="A35:A41"/>
+    <mergeCell ref="AJ5:AJ6"/>
+    <mergeCell ref="B35:B41"/>
+    <mergeCell ref="AR28:AR34"/>
+    <mergeCell ref="B28:B34"/>
+    <mergeCell ref="A21:A27"/>
+    <mergeCell ref="AQ14:AQ20"/>
+    <mergeCell ref="AK5:AK6"/>
+    <mergeCell ref="AM5:AM6"/>
+    <mergeCell ref="AL5:AL6"/>
+    <mergeCell ref="AQ5:AQ6"/>
+    <mergeCell ref="AR21:AR27"/>
+    <mergeCell ref="AQ35:AQ41"/>
+    <mergeCell ref="C7:C13"/>
+    <mergeCell ref="B7:B13"/>
+    <mergeCell ref="AR7:AR13"/>
+    <mergeCell ref="B21:B27"/>
+    <mergeCell ref="AQ7:AQ13"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="AR5:AR6"/>
+    <mergeCell ref="AO5:AO6"/>
+    <mergeCell ref="C21:C27"/>
+    <mergeCell ref="AN5:AN6"/>
+    <mergeCell ref="B56:B62"/>
+    <mergeCell ref="AR56:AR62"/>
+    <mergeCell ref="A49:A55"/>
+    <mergeCell ref="C42:C48"/>
+    <mergeCell ref="C49:C55"/>
+    <mergeCell ref="AR49:AR55"/>
+    <mergeCell ref="C56:C62"/>
+    <mergeCell ref="A56:A62"/>
+    <mergeCell ref="A42:A48"/>
+    <mergeCell ref="AQ42:AQ48"/>
+    <mergeCell ref="B49:B55"/>
     <mergeCell ref="B1:D2"/>
     <mergeCell ref="AR14:AR20"/>
     <mergeCell ref="I3:L3"/>
@@ -5345,58 +5398,6 @@
     <mergeCell ref="C28:C34"/>
     <mergeCell ref="AQ63:AR63"/>
     <mergeCell ref="E3:H3"/>
-    <mergeCell ref="B56:B62"/>
-    <mergeCell ref="AR56:AR62"/>
-    <mergeCell ref="A49:A55"/>
-    <mergeCell ref="C42:C48"/>
-    <mergeCell ref="C49:C55"/>
-    <mergeCell ref="AR49:AR55"/>
-    <mergeCell ref="C56:C62"/>
-    <mergeCell ref="A56:A62"/>
-    <mergeCell ref="A42:A48"/>
-    <mergeCell ref="AQ5:AQ6"/>
-    <mergeCell ref="AR21:AR27"/>
-    <mergeCell ref="AQ35:AQ41"/>
-    <mergeCell ref="C7:C13"/>
-    <mergeCell ref="B7:B13"/>
-    <mergeCell ref="AR7:AR13"/>
-    <mergeCell ref="B21:B27"/>
-    <mergeCell ref="AQ7:AQ13"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="A28:A34"/>
-    <mergeCell ref="A14:A20"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="AR42:AR48"/>
-    <mergeCell ref="AQ28:AQ34"/>
-    <mergeCell ref="A35:A41"/>
-    <mergeCell ref="AJ5:AJ6"/>
-    <mergeCell ref="B35:B41"/>
-    <mergeCell ref="AR28:AR34"/>
-    <mergeCell ref="B28:B34"/>
-    <mergeCell ref="A21:A27"/>
-    <mergeCell ref="AQ14:AQ20"/>
-    <mergeCell ref="AK5:AK6"/>
-    <mergeCell ref="AM5:AM6"/>
-    <mergeCell ref="AL5:AL6"/>
-    <mergeCell ref="AR5:AR6"/>
-    <mergeCell ref="AO5:AO6"/>
-    <mergeCell ref="C21:C27"/>
-    <mergeCell ref="AQ42:AQ48"/>
-    <mergeCell ref="B49:B55"/>
-    <mergeCell ref="AN5:AN6"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="M3:P3"/>
-    <mergeCell ref="AP5:AP6"/>
-    <mergeCell ref="AQ21:AQ27"/>
-    <mergeCell ref="E1:V1"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="P2:W2"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="E2:L2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="E4:AQ4"/>
   </mergeCells>
   <conditionalFormatting sqref="E6">
     <cfRule type="expression" dxfId="61" priority="188">
@@ -5717,7 +5718,16 @@
       <formula1>2000</formula1>
       <formula2>2100</formula2>
     </dataValidation>
-    <dataValidation type="list" sqref="E7:AI12 E14:AI19 E21:AI26 E28:AI33 E35:AI40 E42:AI47 E49:AI54 E56:AI61" xr:uid="{00000000-0002-0000-0000-000002000000}"/>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E7:AI62" xr:uid="{C469599C-8936-2B4F-A74F-4313CA841FB1}">
+      <mc:AlternateContent xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+        <mc:Choice Requires="x12ac">
+          <x12ac:list>8,"7,5",7,"6,5",6,"5,5",5,"4,5",4,"3,5",3,"2,5",2,"1,5",1,"0,5"</x12ac:list>
+        </mc:Choice>
+        <mc:Fallback>
+          <formula1>"8,7,5,7,6,5,6,5,5,5,4,5,4,3,5,3,2,5,2,1,5,1,0,5"</formula1>
+        </mc:Fallback>
+      </mc:AlternateContent>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="49" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>

--- a/public/moduli/FoglioPresenze_StudioBaiocco.xlsx
+++ b/public/moduli/FoglioPresenze_StudioBaiocco.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Desktop/sito_mamma/public/moduli/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E7D7E3-E5FC-374C-B550-04FF756CA452}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C531FF-E77C-854F-9AA5-94166617CA2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="27">
   <si>
     <t>FOGLIO PRESENZE</t>
   </si>
@@ -138,12 +138,15 @@
       <t xml:space="preserve"> Prima di cambiare mese → stampa/salva il foglio in PDF → poi cambia mese e cancella manualmente le ore inserite.</t>
     </r>
   </si>
+  <si>
+    <t>www.studioromanabaiocco.it</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,6 +249,31 @@
       <b/>
       <sz val="18"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <u/>
+      <sz val="16"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="16"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -588,10 +616,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -686,11 +715,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -704,6 +737,8 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -716,6 +751,10 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -726,10 +765,6 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -752,7 +787,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="62">
@@ -1930,7 +1966,7 @@
       <c r="B2" s="24"/>
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
-      <c r="E2" s="55" t="s">
+      <c r="E2" s="57" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="24"/>
@@ -1939,13 +1975,13 @@
       <c r="I2" s="24"/>
       <c r="J2" s="24"/>
       <c r="K2" s="24"/>
-      <c r="L2" s="56"/>
-      <c r="M2" s="52">
+      <c r="L2" s="58"/>
+      <c r="M2" s="54">
         <v>3</v>
       </c>
-      <c r="N2" s="53"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="55" t="s">
+      <c r="N2" s="55"/>
+      <c r="O2" s="56"/>
+      <c r="P2" s="57" t="s">
         <v>2</v>
       </c>
       <c r="Q2" s="24"/>
@@ -1954,12 +1990,12 @@
       <c r="T2" s="24"/>
       <c r="U2" s="24"/>
       <c r="V2" s="24"/>
-      <c r="W2" s="56"/>
-      <c r="X2" s="57">
+      <c r="W2" s="58"/>
+      <c r="X2" s="59">
         <v>2026</v>
       </c>
-      <c r="Y2" s="53"/>
-      <c r="Z2" s="54"/>
+      <c r="Y2" s="55"/>
+      <c r="Z2" s="56"/>
       <c r="AA2" s="15"/>
       <c r="AB2" s="15"/>
       <c r="AC2" s="15"/>
@@ -1981,7 +2017,7 @@
     </row>
     <row r="3" spans="1:44" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14"/>
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="53" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="24"/>
@@ -2032,7 +2068,7 @@
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
       <c r="D4" s="24"/>
-      <c r="E4" s="58" t="s">
+      <c r="E4" s="60" t="s">
         <v>25</v>
       </c>
       <c r="F4" s="24"/>
@@ -2077,13 +2113,13 @@
     </row>
     <row r="5" spans="1:44" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14"/>
-      <c r="B5" s="49" t="s">
+      <c r="B5" s="47" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="50"/>
+      <c r="D5" s="48"/>
       <c r="E5" s="1">
         <v>1</v>
       </c>
@@ -2177,31 +2213,31 @@
       <c r="AI5" s="1">
         <v>31</v>
       </c>
-      <c r="AJ5" s="45" t="s">
+      <c r="AJ5" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="AK5" s="45" t="s">
+      <c r="AK5" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="AL5" s="45" t="s">
+      <c r="AL5" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="AM5" s="45" t="s">
+      <c r="AM5" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="AN5" s="45" t="s">
+      <c r="AN5" s="49" t="s">
         <v>10</v>
       </c>
-      <c r="AO5" s="45" t="s">
+      <c r="AO5" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="AP5" s="45" t="s">
+      <c r="AP5" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="AQ5" s="45" t="s">
+      <c r="AQ5" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="AR5" s="45" t="s">
+      <c r="AR5" s="49" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2334,19 +2370,19 @@
         <f>IFERROR(IF(31&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,31),2),"L","M","M","G","V","S","D")),"")</f>
         <v>M</v>
       </c>
-      <c r="AJ6" s="46"/>
-      <c r="AK6" s="46"/>
-      <c r="AL6" s="46"/>
-      <c r="AM6" s="46"/>
-      <c r="AN6" s="46"/>
-      <c r="AO6" s="46"/>
-      <c r="AP6" s="46"/>
-      <c r="AQ6" s="46"/>
-      <c r="AR6" s="46"/>
+      <c r="AJ6" s="50"/>
+      <c r="AK6" s="50"/>
+      <c r="AL6" s="50"/>
+      <c r="AM6" s="50"/>
+      <c r="AN6" s="50"/>
+      <c r="AO6" s="50"/>
+      <c r="AP6" s="50"/>
+      <c r="AQ6" s="50"/>
+      <c r="AR6" s="50"/>
     </row>
     <row r="7" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="42"/>
-      <c r="B7" s="47">
+      <c r="A7" s="44"/>
+      <c r="B7" s="51">
         <v>1</v>
       </c>
       <c r="C7" s="29" t="s">
@@ -2396,14 +2432,14 @@
       <c r="AN7" s="5"/>
       <c r="AO7" s="5"/>
       <c r="AP7" s="5"/>
-      <c r="AQ7" s="48">
+      <c r="AQ7" s="52">
         <f>COUNTIF(E7:AI7,"&gt;0")</f>
         <v>0</v>
       </c>
       <c r="AR7" s="25"/>
     </row>
     <row r="8" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="43"/>
+      <c r="A8" s="45"/>
       <c r="B8" s="30"/>
       <c r="C8" s="30"/>
       <c r="D8" s="6" t="s">
@@ -2454,7 +2490,7 @@
       <c r="AR8" s="26"/>
     </row>
     <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="43"/>
+      <c r="A9" s="45"/>
       <c r="B9" s="30"/>
       <c r="C9" s="30"/>
       <c r="D9" s="7" t="s">
@@ -2505,7 +2541,7 @@
       <c r="AR9" s="26"/>
     </row>
     <row r="10" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="43"/>
+      <c r="A10" s="45"/>
       <c r="B10" s="30"/>
       <c r="C10" s="30"/>
       <c r="D10" s="8" t="s">
@@ -2556,7 +2592,7 @@
       <c r="AR10" s="26"/>
     </row>
     <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="43"/>
+      <c r="A11" s="45"/>
       <c r="B11" s="30"/>
       <c r="C11" s="30"/>
       <c r="D11" s="9" t="s">
@@ -2607,7 +2643,7 @@
       <c r="AR11" s="26"/>
     </row>
     <row r="12" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="43"/>
+      <c r="A12" s="45"/>
       <c r="B12" s="30"/>
       <c r="C12" s="30"/>
       <c r="D12" s="9" t="s">
@@ -2658,7 +2694,7 @@
       <c r="AR12" s="26"/>
     </row>
     <row r="13" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="43"/>
+      <c r="A13" s="45"/>
       <c r="B13" s="31"/>
       <c r="C13" s="31"/>
       <c r="D13" s="10" t="s">
@@ -2709,7 +2745,7 @@
       <c r="AR13" s="27"/>
     </row>
     <row r="14" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="42"/>
+      <c r="A14" s="44"/>
       <c r="B14" s="38">
         <v>2</v>
       </c>
@@ -2767,7 +2803,7 @@
       <c r="AR14" s="25"/>
     </row>
     <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="43"/>
+      <c r="A15" s="45"/>
       <c r="B15" s="30"/>
       <c r="C15" s="30"/>
       <c r="D15" s="6" t="s">
@@ -2818,7 +2854,7 @@
       <c r="AR15" s="26"/>
     </row>
     <row r="16" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="43"/>
+      <c r="A16" s="45"/>
       <c r="B16" s="30"/>
       <c r="C16" s="30"/>
       <c r="D16" s="7" t="s">
@@ -2869,7 +2905,7 @@
       <c r="AR16" s="26"/>
     </row>
     <row r="17" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="43"/>
+      <c r="A17" s="45"/>
       <c r="B17" s="30"/>
       <c r="C17" s="30"/>
       <c r="D17" s="8" t="s">
@@ -2920,7 +2956,7 @@
       <c r="AR17" s="26"/>
     </row>
     <row r="18" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="43"/>
+      <c r="A18" s="45"/>
       <c r="B18" s="30"/>
       <c r="C18" s="30"/>
       <c r="D18" s="9" t="s">
@@ -2971,7 +3007,7 @@
       <c r="AR18" s="26"/>
     </row>
     <row r="19" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="43"/>
+      <c r="A19" s="45"/>
       <c r="B19" s="30"/>
       <c r="C19" s="30"/>
       <c r="D19" s="9" t="s">
@@ -3022,7 +3058,7 @@
       <c r="AR19" s="26"/>
     </row>
     <row r="20" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="43"/>
+      <c r="A20" s="45"/>
       <c r="B20" s="31"/>
       <c r="C20" s="31"/>
       <c r="D20" s="10" t="s">
@@ -3073,7 +3109,7 @@
       <c r="AR20" s="27"/>
     </row>
     <row r="21" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="42"/>
+      <c r="A21" s="44"/>
       <c r="B21" s="38">
         <v>3</v>
       </c>
@@ -3131,7 +3167,7 @@
       <c r="AR21" s="25"/>
     </row>
     <row r="22" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="43"/>
+      <c r="A22" s="45"/>
       <c r="B22" s="30"/>
       <c r="C22" s="30"/>
       <c r="D22" s="6" t="s">
@@ -3182,7 +3218,7 @@
       <c r="AR22" s="26"/>
     </row>
     <row r="23" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="43"/>
+      <c r="A23" s="45"/>
       <c r="B23" s="30"/>
       <c r="C23" s="30"/>
       <c r="D23" s="7" t="s">
@@ -3233,7 +3269,7 @@
       <c r="AR23" s="26"/>
     </row>
     <row r="24" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="43"/>
+      <c r="A24" s="45"/>
       <c r="B24" s="30"/>
       <c r="C24" s="30"/>
       <c r="D24" s="8" t="s">
@@ -3284,7 +3320,7 @@
       <c r="AR24" s="26"/>
     </row>
     <row r="25" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="43"/>
+      <c r="A25" s="45"/>
       <c r="B25" s="30"/>
       <c r="C25" s="30"/>
       <c r="D25" s="9" t="s">
@@ -3335,7 +3371,7 @@
       <c r="AR25" s="26"/>
     </row>
     <row r="26" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="43"/>
+      <c r="A26" s="45"/>
       <c r="B26" s="30"/>
       <c r="C26" s="30"/>
       <c r="D26" s="9" t="s">
@@ -3386,7 +3422,7 @@
       <c r="AR26" s="26"/>
     </row>
     <row r="27" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="43"/>
+      <c r="A27" s="45"/>
       <c r="B27" s="31"/>
       <c r="C27" s="31"/>
       <c r="D27" s="10" t="s">
@@ -3437,7 +3473,7 @@
       <c r="AR27" s="27"/>
     </row>
     <row r="28" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="42"/>
+      <c r="A28" s="44"/>
       <c r="B28" s="38">
         <v>4</v>
       </c>
@@ -3495,7 +3531,7 @@
       <c r="AR28" s="25"/>
     </row>
     <row r="29" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="43"/>
+      <c r="A29" s="45"/>
       <c r="B29" s="30"/>
       <c r="C29" s="30"/>
       <c r="D29" s="6" t="s">
@@ -3546,7 +3582,7 @@
       <c r="AR29" s="26"/>
     </row>
     <row r="30" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="43"/>
+      <c r="A30" s="45"/>
       <c r="B30" s="30"/>
       <c r="C30" s="30"/>
       <c r="D30" s="7" t="s">
@@ -3597,7 +3633,7 @@
       <c r="AR30" s="26"/>
     </row>
     <row r="31" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="43"/>
+      <c r="A31" s="45"/>
       <c r="B31" s="30"/>
       <c r="C31" s="30"/>
       <c r="D31" s="8" t="s">
@@ -3648,7 +3684,7 @@
       <c r="AR31" s="26"/>
     </row>
     <row r="32" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="43"/>
+      <c r="A32" s="45"/>
       <c r="B32" s="30"/>
       <c r="C32" s="30"/>
       <c r="D32" s="9" t="s">
@@ -3699,7 +3735,7 @@
       <c r="AR32" s="26"/>
     </row>
     <row r="33" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="43"/>
+      <c r="A33" s="45"/>
       <c r="B33" s="30"/>
       <c r="C33" s="30"/>
       <c r="D33" s="9" t="s">
@@ -3750,7 +3786,7 @@
       <c r="AR33" s="26"/>
     </row>
     <row r="34" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="43"/>
+      <c r="A34" s="45"/>
       <c r="B34" s="31"/>
       <c r="C34" s="31"/>
       <c r="D34" s="10" t="s">
@@ -3801,7 +3837,7 @@
       <c r="AR34" s="27"/>
     </row>
     <row r="35" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="42"/>
+      <c r="A35" s="44"/>
       <c r="B35" s="38">
         <v>5</v>
       </c>
@@ -3859,7 +3895,7 @@
       <c r="AR35" s="25"/>
     </row>
     <row r="36" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="43"/>
+      <c r="A36" s="45"/>
       <c r="B36" s="30"/>
       <c r="C36" s="30"/>
       <c r="D36" s="6" t="s">
@@ -3910,7 +3946,7 @@
       <c r="AR36" s="26"/>
     </row>
     <row r="37" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="43"/>
+      <c r="A37" s="45"/>
       <c r="B37" s="30"/>
       <c r="C37" s="30"/>
       <c r="D37" s="7" t="s">
@@ -3961,7 +3997,7 @@
       <c r="AR37" s="26"/>
     </row>
     <row r="38" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="43"/>
+      <c r="A38" s="45"/>
       <c r="B38" s="30"/>
       <c r="C38" s="30"/>
       <c r="D38" s="8" t="s">
@@ -4012,7 +4048,7 @@
       <c r="AR38" s="26"/>
     </row>
     <row r="39" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="43"/>
+      <c r="A39" s="45"/>
       <c r="B39" s="30"/>
       <c r="C39" s="30"/>
       <c r="D39" s="9" t="s">
@@ -4063,7 +4099,7 @@
       <c r="AR39" s="26"/>
     </row>
     <row r="40" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="43"/>
+      <c r="A40" s="45"/>
       <c r="B40" s="30"/>
       <c r="C40" s="30"/>
       <c r="D40" s="9" t="s">
@@ -4114,7 +4150,7 @@
       <c r="AR40" s="26"/>
     </row>
     <row r="41" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="43"/>
+      <c r="A41" s="45"/>
       <c r="B41" s="31"/>
       <c r="C41" s="31"/>
       <c r="D41" s="10" t="s">
@@ -4165,7 +4201,7 @@
       <c r="AR41" s="27"/>
     </row>
     <row r="42" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="42"/>
+      <c r="A42" s="44"/>
       <c r="B42" s="38">
         <v>6</v>
       </c>
@@ -4223,7 +4259,7 @@
       <c r="AR42" s="25"/>
     </row>
     <row r="43" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="43"/>
+      <c r="A43" s="45"/>
       <c r="B43" s="30"/>
       <c r="C43" s="30"/>
       <c r="D43" s="6" t="s">
@@ -4274,7 +4310,7 @@
       <c r="AR43" s="26"/>
     </row>
     <row r="44" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="43"/>
+      <c r="A44" s="45"/>
       <c r="B44" s="30"/>
       <c r="C44" s="30"/>
       <c r="D44" s="7" t="s">
@@ -4325,7 +4361,7 @@
       <c r="AR44" s="26"/>
     </row>
     <row r="45" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="43"/>
+      <c r="A45" s="45"/>
       <c r="B45" s="30"/>
       <c r="C45" s="30"/>
       <c r="D45" s="8" t="s">
@@ -4376,7 +4412,7 @@
       <c r="AR45" s="26"/>
     </row>
     <row r="46" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="43"/>
+      <c r="A46" s="45"/>
       <c r="B46" s="30"/>
       <c r="C46" s="30"/>
       <c r="D46" s="9" t="s">
@@ -4427,7 +4463,7 @@
       <c r="AR46" s="26"/>
     </row>
     <row r="47" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="43"/>
+      <c r="A47" s="45"/>
       <c r="B47" s="30"/>
       <c r="C47" s="30"/>
       <c r="D47" s="9" t="s">
@@ -4478,7 +4514,7 @@
       <c r="AR47" s="26"/>
     </row>
     <row r="48" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="43"/>
+      <c r="A48" s="45"/>
       <c r="B48" s="31"/>
       <c r="C48" s="31"/>
       <c r="D48" s="10" t="s">
@@ -4529,11 +4565,11 @@
       <c r="AR48" s="27"/>
     </row>
     <row r="49" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="42"/>
+      <c r="A49" s="44"/>
       <c r="B49" s="38">
         <v>7</v>
       </c>
-      <c r="C49" s="44" t="s">
+      <c r="C49" s="46" t="s">
         <v>15</v>
       </c>
       <c r="D49" s="3" t="s">
@@ -4587,7 +4623,7 @@
       <c r="AR49" s="25"/>
     </row>
     <row r="50" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="43"/>
+      <c r="A50" s="45"/>
       <c r="B50" s="30"/>
       <c r="C50" s="30"/>
       <c r="D50" s="6" t="s">
@@ -4638,7 +4674,7 @@
       <c r="AR50" s="26"/>
     </row>
     <row r="51" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="43"/>
+      <c r="A51" s="45"/>
       <c r="B51" s="30"/>
       <c r="C51" s="30"/>
       <c r="D51" s="7" t="s">
@@ -4689,7 +4725,7 @@
       <c r="AR51" s="26"/>
     </row>
     <row r="52" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="43"/>
+      <c r="A52" s="45"/>
       <c r="B52" s="30"/>
       <c r="C52" s="30"/>
       <c r="D52" s="8" t="s">
@@ -4740,7 +4776,7 @@
       <c r="AR52" s="26"/>
     </row>
     <row r="53" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="43"/>
+      <c r="A53" s="45"/>
       <c r="B53" s="30"/>
       <c r="C53" s="30"/>
       <c r="D53" s="9" t="s">
@@ -4791,7 +4827,7 @@
       <c r="AR53" s="26"/>
     </row>
     <row r="54" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="43"/>
+      <c r="A54" s="45"/>
       <c r="B54" s="30"/>
       <c r="C54" s="30"/>
       <c r="D54" s="9" t="s">
@@ -4842,7 +4878,7 @@
       <c r="AR54" s="26"/>
     </row>
     <row r="55" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="43"/>
+      <c r="A55" s="45"/>
       <c r="B55" s="31"/>
       <c r="C55" s="31"/>
       <c r="D55" s="10" t="s">
@@ -4893,11 +4929,11 @@
       <c r="AR55" s="27"/>
     </row>
     <row r="56" spans="1:44" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="42"/>
+      <c r="A56" s="44"/>
       <c r="B56" s="38">
         <v>8</v>
       </c>
-      <c r="C56" s="44" t="s">
+      <c r="C56" s="46" t="s">
         <v>15</v>
       </c>
       <c r="D56" s="3" t="s">
@@ -4951,7 +4987,7 @@
       <c r="AR56" s="25"/>
     </row>
     <row r="57" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="43"/>
+      <c r="A57" s="45"/>
       <c r="B57" s="30"/>
       <c r="C57" s="30"/>
       <c r="D57" s="6" t="s">
@@ -5002,7 +5038,7 @@
       <c r="AR57" s="26"/>
     </row>
     <row r="58" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="43"/>
+      <c r="A58" s="45"/>
       <c r="B58" s="30"/>
       <c r="C58" s="30"/>
       <c r="D58" s="7" t="s">
@@ -5053,7 +5089,7 @@
       <c r="AR58" s="26"/>
     </row>
     <row r="59" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="43"/>
+      <c r="A59" s="45"/>
       <c r="B59" s="30"/>
       <c r="C59" s="30"/>
       <c r="D59" s="8" t="s">
@@ -5104,7 +5140,7 @@
       <c r="AR59" s="26"/>
     </row>
     <row r="60" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="43"/>
+      <c r="A60" s="45"/>
       <c r="B60" s="30"/>
       <c r="C60" s="30"/>
       <c r="D60" s="9" t="s">
@@ -5155,7 +5191,7 @@
       <c r="AR60" s="26"/>
     </row>
     <row r="61" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="43"/>
+      <c r="A61" s="45"/>
       <c r="B61" s="30"/>
       <c r="C61" s="30"/>
       <c r="D61" s="9" t="s">
@@ -5206,7 +5242,7 @@
       <c r="AR61" s="26"/>
     </row>
     <row r="62" spans="1:44" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="43"/>
+      <c r="A62" s="45"/>
       <c r="B62" s="31"/>
       <c r="C62" s="31"/>
       <c r="D62" s="10" t="s">
@@ -5261,9 +5297,11 @@
       <c r="B63" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="C63" s="33"/>
-      <c r="D63" s="34"/>
-      <c r="E63" s="32"/>
+      <c r="C63" s="40"/>
+      <c r="D63" s="41"/>
+      <c r="E63" s="32" t="s">
+        <v>26</v>
+      </c>
       <c r="F63" s="33"/>
       <c r="G63" s="33"/>
       <c r="H63" s="33"/>
@@ -5322,13 +5360,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AQ63" s="40" t="s">
+      <c r="AQ63" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="AR63" s="41"/>
+      <c r="AR63" s="43"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="dtCmCygegEzU/8/F3QBsKPNjtVleaM7WtfwWcPHRyLFI/g9F9yeK9q8Y+arnGvRhl52+eGvwv8+6dNEpi+XXkw==" saltValue="7ViFD7S7TvPRkvNcrjPlFA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="uXz7IkwNnKjilI/Hz/CZ0V74Yl6g0tz3rpClsJ+nYXWRF4U6PfxzxVf7aO2sKzmAqwtgPwrNgoZGnO30/Yf18g==" saltValue="PkgGAmfnKf0KnwCCqwTXlw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="68">
     <mergeCell ref="Q3:T3"/>
     <mergeCell ref="M3:P3"/>
@@ -5341,6 +5379,7 @@
     <mergeCell ref="E2:L2"/>
     <mergeCell ref="X2:Z2"/>
     <mergeCell ref="E4:AQ4"/>
+    <mergeCell ref="AQ5:AQ6"/>
     <mergeCell ref="A7:A13"/>
     <mergeCell ref="A28:A34"/>
     <mergeCell ref="A14:A20"/>
@@ -5357,8 +5396,6 @@
     <mergeCell ref="AK5:AK6"/>
     <mergeCell ref="AM5:AM6"/>
     <mergeCell ref="AL5:AL6"/>
-    <mergeCell ref="AQ5:AQ6"/>
-    <mergeCell ref="AR21:AR27"/>
     <mergeCell ref="AQ35:AQ41"/>
     <mergeCell ref="C7:C13"/>
     <mergeCell ref="B7:B13"/>
@@ -5371,6 +5408,7 @@
     <mergeCell ref="AO5:AO6"/>
     <mergeCell ref="C21:C27"/>
     <mergeCell ref="AN5:AN6"/>
+    <mergeCell ref="AR21:AR27"/>
     <mergeCell ref="B56:B62"/>
     <mergeCell ref="AR56:AR62"/>
     <mergeCell ref="A49:A55"/>
@@ -5729,8 +5767,11 @@
       </mc:AlternateContent>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="E63" r:id="rId1" xr:uid="{4343CFC4-42A5-F64B-80BF-488245BAFF7A}"/>
+  </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="49" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/public/moduli/FoglioPresenze_StudioBaiocco.xlsx
+++ b/public/moduli/FoglioPresenze_StudioBaiocco.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Desktop/sito_mamma/public/moduli/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5C531FF-E77C-854F-9AA5-94166617CA2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{615AE5AF-E6F9-244E-9428-4DED83935449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -146,7 +146,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -233,13 +233,6 @@
     </font>
     <font>
       <b/>
-      <sz val="26"/>
-      <color rgb="FF1A2B4A"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -276,6 +269,27 @@
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF1A2B4A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="16">
@@ -618,9 +632,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -690,10 +704,38 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="justify"/>
       <protection locked="0"/>
@@ -706,32 +748,41 @@
       <alignment horizontal="left" vertical="justify"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -743,49 +794,14 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -1906,7 +1922,11 @@
     <col min="2" max="2" width="4" customWidth="1"/>
     <col min="3" max="3" width="18.6640625" customWidth="1"/>
     <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="35" width="3.83203125" customWidth="1"/>
+    <col min="5" max="14" width="3.83203125" customWidth="1"/>
+    <col min="15" max="15" width="7.5" customWidth="1"/>
+    <col min="16" max="25" width="3.83203125" customWidth="1"/>
+    <col min="26" max="26" width="10" customWidth="1"/>
+    <col min="27" max="35" width="3.83203125" customWidth="1"/>
     <col min="36" max="40" width="7" customWidth="1"/>
     <col min="42" max="42" width="8.33203125" customWidth="1"/>
     <col min="43" max="43" width="6" customWidth="1"/>
@@ -1915,12 +1935,12 @@
   <sheetData>
     <row r="1" spans="1:44" ht="35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14"/>
-      <c r="B1" s="23" t="s">
+      <c r="B1" s="48" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="24"/>
       <c r="D1" s="24"/>
-      <c r="E1" s="28"/>
+      <c r="E1" s="23"/>
       <c r="F1" s="24"/>
       <c r="G1" s="24"/>
       <c r="H1" s="24"/>
@@ -1961,12 +1981,12 @@
       <c r="AQ1" s="15"/>
       <c r="AR1" s="15"/>
     </row>
-    <row r="2" spans="1:44" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:44" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="14"/>
       <c r="B2" s="24"/>
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
-      <c r="E2" s="57" t="s">
+      <c r="E2" s="30" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="24"/>
@@ -1975,13 +1995,13 @@
       <c r="I2" s="24"/>
       <c r="J2" s="24"/>
       <c r="K2" s="24"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="54">
+      <c r="L2" s="31"/>
+      <c r="M2" s="32">
         <v>3</v>
       </c>
-      <c r="N2" s="55"/>
-      <c r="O2" s="56"/>
-      <c r="P2" s="57" t="s">
+      <c r="N2" s="61"/>
+      <c r="O2" s="62"/>
+      <c r="P2" s="30" t="s">
         <v>2</v>
       </c>
       <c r="Q2" s="24"/>
@@ -1990,12 +2010,12 @@
       <c r="T2" s="24"/>
       <c r="U2" s="24"/>
       <c r="V2" s="24"/>
-      <c r="W2" s="58"/>
-      <c r="X2" s="59">
+      <c r="W2" s="31"/>
+      <c r="X2" s="58">
         <v>2026</v>
       </c>
-      <c r="Y2" s="55"/>
-      <c r="Z2" s="56"/>
+      <c r="Y2" s="59"/>
+      <c r="Z2" s="60"/>
       <c r="AA2" s="15"/>
       <c r="AB2" s="15"/>
       <c r="AC2" s="15"/>
@@ -2017,28 +2037,28 @@
     </row>
     <row r="3" spans="1:44" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14"/>
-      <c r="B3" s="53" t="s">
+      <c r="B3" s="36" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="24"/>
       <c r="D3" s="24"/>
-      <c r="E3" s="28"/>
+      <c r="E3" s="23"/>
       <c r="F3" s="24"/>
       <c r="G3" s="24"/>
       <c r="H3" s="24"/>
-      <c r="I3" s="28"/>
+      <c r="I3" s="23"/>
       <c r="J3" s="24"/>
       <c r="K3" s="24"/>
       <c r="L3" s="24"/>
-      <c r="M3" s="28"/>
+      <c r="M3" s="23"/>
       <c r="N3" s="24"/>
       <c r="O3" s="24"/>
       <c r="P3" s="24"/>
-      <c r="Q3" s="28"/>
+      <c r="Q3" s="23"/>
       <c r="R3" s="24"/>
       <c r="S3" s="24"/>
       <c r="T3" s="24"/>
-      <c r="U3" s="28"/>
+      <c r="U3" s="23"/>
       <c r="V3" s="24"/>
       <c r="W3" s="15"/>
       <c r="X3" s="15"/>
@@ -2068,7 +2088,7 @@
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
       <c r="D4" s="24"/>
-      <c r="E4" s="60" t="s">
+      <c r="E4" s="33" t="s">
         <v>25</v>
       </c>
       <c r="F4" s="24"/>
@@ -2113,13 +2133,13 @@
     </row>
     <row r="5" spans="1:44" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14"/>
-      <c r="B5" s="47" t="s">
+      <c r="B5" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C5" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="48"/>
+      <c r="D5" s="46"/>
       <c r="E5" s="1">
         <v>1</v>
       </c>
@@ -2213,39 +2233,39 @@
       <c r="AI5" s="1">
         <v>31</v>
       </c>
-      <c r="AJ5" s="49" t="s">
+      <c r="AJ5" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="AK5" s="49" t="s">
+      <c r="AK5" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="AL5" s="49" t="s">
+      <c r="AL5" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="AM5" s="49" t="s">
+      <c r="AM5" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="AN5" s="49" t="s">
+      <c r="AN5" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="AO5" s="49" t="s">
+      <c r="AO5" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="AP5" s="49" t="s">
+      <c r="AP5" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="AQ5" s="49" t="s">
+      <c r="AQ5" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="AR5" s="49" t="s">
+      <c r="AR5" s="25" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="14"/>
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
       <c r="E6" s="2" t="str">
         <f>IFERROR(IF(1&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,1),2),"L","M","M","G","V","S","D")),"")</f>
         <v>D</v>
@@ -2370,22 +2390,22 @@
         <f>IFERROR(IF(31&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,31),2),"L","M","M","G","V","S","D")),"")</f>
         <v>M</v>
       </c>
-      <c r="AJ6" s="50"/>
-      <c r="AK6" s="50"/>
-      <c r="AL6" s="50"/>
-      <c r="AM6" s="50"/>
-      <c r="AN6" s="50"/>
-      <c r="AO6" s="50"/>
-      <c r="AP6" s="50"/>
-      <c r="AQ6" s="50"/>
-      <c r="AR6" s="50"/>
+      <c r="AJ6" s="26"/>
+      <c r="AK6" s="26"/>
+      <c r="AL6" s="26"/>
+      <c r="AM6" s="26"/>
+      <c r="AN6" s="26"/>
+      <c r="AO6" s="26"/>
+      <c r="AP6" s="26"/>
+      <c r="AQ6" s="26"/>
+      <c r="AR6" s="26"/>
     </row>
     <row r="7" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="44"/>
-      <c r="B7" s="51">
+      <c r="A7" s="34"/>
+      <c r="B7" s="42">
         <v>1</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="41" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -2432,16 +2452,16 @@
       <c r="AN7" s="5"/>
       <c r="AO7" s="5"/>
       <c r="AP7" s="5"/>
-      <c r="AQ7" s="52">
+      <c r="AQ7" s="43">
         <f>COUNTIF(E7:AI7,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR7" s="25"/>
+      <c r="AR7" s="37"/>
     </row>
     <row r="8" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="45"/>
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
+      <c r="A8" s="35"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
       <c r="D8" s="6" t="s">
         <v>17</v>
       </c>
@@ -2486,13 +2506,13 @@
       <c r="AN8" s="5"/>
       <c r="AO8" s="5"/>
       <c r="AP8" s="5"/>
-      <c r="AQ8" s="30"/>
-      <c r="AR8" s="26"/>
+      <c r="AQ8" s="28"/>
+      <c r="AR8" s="38"/>
     </row>
     <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="45"/>
-      <c r="B9" s="30"/>
-      <c r="C9" s="30"/>
+      <c r="A9" s="35"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
       <c r="D9" s="7" t="s">
         <v>18</v>
       </c>
@@ -2537,13 +2557,13 @@
       <c r="AN9" s="5"/>
       <c r="AO9" s="5"/>
       <c r="AP9" s="5"/>
-      <c r="AQ9" s="30"/>
-      <c r="AR9" s="26"/>
+      <c r="AQ9" s="28"/>
+      <c r="AR9" s="38"/>
     </row>
     <row r="10" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="45"/>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
+      <c r="A10" s="35"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
       <c r="D10" s="8" t="s">
         <v>19</v>
       </c>
@@ -2588,13 +2608,13 @@
       <c r="AN10" s="5"/>
       <c r="AO10" s="5"/>
       <c r="AP10" s="5"/>
-      <c r="AQ10" s="30"/>
-      <c r="AR10" s="26"/>
+      <c r="AQ10" s="28"/>
+      <c r="AR10" s="38"/>
     </row>
     <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="45"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
+      <c r="A11" s="35"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
       <c r="D11" s="9" t="s">
         <v>20</v>
       </c>
@@ -2639,13 +2659,13 @@
       </c>
       <c r="AO11" s="5"/>
       <c r="AP11" s="5"/>
-      <c r="AQ11" s="30"/>
-      <c r="AR11" s="26"/>
+      <c r="AQ11" s="28"/>
+      <c r="AR11" s="38"/>
     </row>
     <row r="12" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="45"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="30"/>
+      <c r="A12" s="35"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
       <c r="D12" s="9" t="s">
         <v>21</v>
       </c>
@@ -2690,13 +2710,13 @@
         <v>0</v>
       </c>
       <c r="AP12" s="5"/>
-      <c r="AQ12" s="30"/>
-      <c r="AR12" s="26"/>
+      <c r="AQ12" s="28"/>
+      <c r="AR12" s="38"/>
     </row>
     <row r="13" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="45"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="31"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="29"/>
       <c r="D13" s="10" t="s">
         <v>22</v>
       </c>
@@ -2741,15 +2761,15 @@
         <f>SUM(E13:AI13)</f>
         <v>0</v>
       </c>
-      <c r="AQ13" s="31"/>
-      <c r="AR13" s="27"/>
+      <c r="AQ13" s="29"/>
+      <c r="AR13" s="39"/>
     </row>
     <row r="14" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="44"/>
-      <c r="B14" s="38">
+      <c r="A14" s="34"/>
+      <c r="B14" s="40">
         <v>2</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" s="41" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -2796,16 +2816,16 @@
       <c r="AN14" s="5"/>
       <c r="AO14" s="5"/>
       <c r="AP14" s="5"/>
-      <c r="AQ14" s="35">
+      <c r="AQ14" s="27">
         <f>COUNTIF(E14:AI14,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR14" s="25"/>
+      <c r="AR14" s="37"/>
     </row>
     <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="45"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
+      <c r="A15" s="35"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
       <c r="D15" s="6" t="s">
         <v>17</v>
       </c>
@@ -2850,13 +2870,13 @@
       <c r="AN15" s="5"/>
       <c r="AO15" s="5"/>
       <c r="AP15" s="5"/>
-      <c r="AQ15" s="30"/>
-      <c r="AR15" s="26"/>
+      <c r="AQ15" s="28"/>
+      <c r="AR15" s="38"/>
     </row>
     <row r="16" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="45"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
+      <c r="A16" s="35"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
       <c r="D16" s="7" t="s">
         <v>18</v>
       </c>
@@ -2901,13 +2921,13 @@
       <c r="AN16" s="5"/>
       <c r="AO16" s="5"/>
       <c r="AP16" s="5"/>
-      <c r="AQ16" s="30"/>
-      <c r="AR16" s="26"/>
+      <c r="AQ16" s="28"/>
+      <c r="AR16" s="38"/>
     </row>
     <row r="17" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="45"/>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
+      <c r="A17" s="35"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
       <c r="D17" s="8" t="s">
         <v>19</v>
       </c>
@@ -2952,13 +2972,13 @@
       <c r="AN17" s="5"/>
       <c r="AO17" s="5"/>
       <c r="AP17" s="5"/>
-      <c r="AQ17" s="30"/>
-      <c r="AR17" s="26"/>
+      <c r="AQ17" s="28"/>
+      <c r="AR17" s="38"/>
     </row>
     <row r="18" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="45"/>
-      <c r="B18" s="30"/>
-      <c r="C18" s="30"/>
+      <c r="A18" s="35"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
       <c r="D18" s="9" t="s">
         <v>20</v>
       </c>
@@ -3003,13 +3023,13 @@
       </c>
       <c r="AO18" s="5"/>
       <c r="AP18" s="5"/>
-      <c r="AQ18" s="30"/>
-      <c r="AR18" s="26"/>
+      <c r="AQ18" s="28"/>
+      <c r="AR18" s="38"/>
     </row>
     <row r="19" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="45"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
+      <c r="A19" s="35"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
       <c r="D19" s="9" t="s">
         <v>21</v>
       </c>
@@ -3054,13 +3074,13 @@
         <v>0</v>
       </c>
       <c r="AP19" s="5"/>
-      <c r="AQ19" s="30"/>
-      <c r="AR19" s="26"/>
+      <c r="AQ19" s="28"/>
+      <c r="AR19" s="38"/>
     </row>
     <row r="20" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="45"/>
-      <c r="B20" s="31"/>
-      <c r="C20" s="31"/>
+      <c r="A20" s="35"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
       <c r="D20" s="10" t="s">
         <v>22</v>
       </c>
@@ -3105,15 +3125,15 @@
         <f>SUM(E20:AI20)</f>
         <v>0</v>
       </c>
-      <c r="AQ20" s="31"/>
-      <c r="AR20" s="27"/>
+      <c r="AQ20" s="29"/>
+      <c r="AR20" s="39"/>
     </row>
     <row r="21" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="44"/>
-      <c r="B21" s="38">
+      <c r="A21" s="34"/>
+      <c r="B21" s="40">
         <v>3</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="41" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3" t="s">
@@ -3160,16 +3180,16 @@
       <c r="AN21" s="5"/>
       <c r="AO21" s="5"/>
       <c r="AP21" s="5"/>
-      <c r="AQ21" s="35">
+      <c r="AQ21" s="27">
         <f>COUNTIF(E21:AI21,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR21" s="25"/>
+      <c r="AR21" s="37"/>
     </row>
     <row r="22" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="45"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="30"/>
+      <c r="A22" s="35"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="28"/>
       <c r="D22" s="6" t="s">
         <v>17</v>
       </c>
@@ -3214,13 +3234,13 @@
       <c r="AN22" s="5"/>
       <c r="AO22" s="5"/>
       <c r="AP22" s="5"/>
-      <c r="AQ22" s="30"/>
-      <c r="AR22" s="26"/>
+      <c r="AQ22" s="28"/>
+      <c r="AR22" s="38"/>
     </row>
     <row r="23" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="45"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
+      <c r="A23" s="35"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
       <c r="D23" s="7" t="s">
         <v>18</v>
       </c>
@@ -3265,13 +3285,13 @@
       <c r="AN23" s="5"/>
       <c r="AO23" s="5"/>
       <c r="AP23" s="5"/>
-      <c r="AQ23" s="30"/>
-      <c r="AR23" s="26"/>
+      <c r="AQ23" s="28"/>
+      <c r="AR23" s="38"/>
     </row>
     <row r="24" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="45"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
+      <c r="A24" s="35"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="28"/>
       <c r="D24" s="8" t="s">
         <v>19</v>
       </c>
@@ -3316,13 +3336,13 @@
       <c r="AN24" s="5"/>
       <c r="AO24" s="5"/>
       <c r="AP24" s="5"/>
-      <c r="AQ24" s="30"/>
-      <c r="AR24" s="26"/>
+      <c r="AQ24" s="28"/>
+      <c r="AR24" s="38"/>
     </row>
     <row r="25" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="45"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
+      <c r="A25" s="35"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
       <c r="D25" s="9" t="s">
         <v>20</v>
       </c>
@@ -3367,13 +3387,13 @@
       </c>
       <c r="AO25" s="5"/>
       <c r="AP25" s="5"/>
-      <c r="AQ25" s="30"/>
-      <c r="AR25" s="26"/>
+      <c r="AQ25" s="28"/>
+      <c r="AR25" s="38"/>
     </row>
     <row r="26" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="45"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
+      <c r="A26" s="35"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
       <c r="D26" s="9" t="s">
         <v>21</v>
       </c>
@@ -3418,13 +3438,13 @@
         <v>0</v>
       </c>
       <c r="AP26" s="5"/>
-      <c r="AQ26" s="30"/>
-      <c r="AR26" s="26"/>
+      <c r="AQ26" s="28"/>
+      <c r="AR26" s="38"/>
     </row>
     <row r="27" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="45"/>
-      <c r="B27" s="31"/>
-      <c r="C27" s="31"/>
+      <c r="A27" s="35"/>
+      <c r="B27" s="29"/>
+      <c r="C27" s="29"/>
       <c r="D27" s="10" t="s">
         <v>22</v>
       </c>
@@ -3469,15 +3489,15 @@
         <f>SUM(E27:AI27)</f>
         <v>0</v>
       </c>
-      <c r="AQ27" s="31"/>
-      <c r="AR27" s="27"/>
+      <c r="AQ27" s="29"/>
+      <c r="AR27" s="39"/>
     </row>
     <row r="28" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="44"/>
-      <c r="B28" s="38">
+      <c r="A28" s="34"/>
+      <c r="B28" s="40">
         <v>4</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="41" t="s">
         <v>15</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -3524,16 +3544,16 @@
       <c r="AN28" s="5"/>
       <c r="AO28" s="5"/>
       <c r="AP28" s="5"/>
-      <c r="AQ28" s="35">
+      <c r="AQ28" s="27">
         <f>COUNTIF(E28:AI28,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR28" s="25"/>
+      <c r="AR28" s="37"/>
     </row>
     <row r="29" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="45"/>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
+      <c r="A29" s="35"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
       <c r="D29" s="6" t="s">
         <v>17</v>
       </c>
@@ -3578,13 +3598,13 @@
       <c r="AN29" s="5"/>
       <c r="AO29" s="5"/>
       <c r="AP29" s="5"/>
-      <c r="AQ29" s="30"/>
-      <c r="AR29" s="26"/>
+      <c r="AQ29" s="28"/>
+      <c r="AR29" s="38"/>
     </row>
     <row r="30" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="45"/>
-      <c r="B30" s="30"/>
-      <c r="C30" s="30"/>
+      <c r="A30" s="35"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
       <c r="D30" s="7" t="s">
         <v>18</v>
       </c>
@@ -3629,13 +3649,13 @@
       <c r="AN30" s="5"/>
       <c r="AO30" s="5"/>
       <c r="AP30" s="5"/>
-      <c r="AQ30" s="30"/>
-      <c r="AR30" s="26"/>
+      <c r="AQ30" s="28"/>
+      <c r="AR30" s="38"/>
     </row>
     <row r="31" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="45"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="30"/>
+      <c r="A31" s="35"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
       <c r="D31" s="8" t="s">
         <v>19</v>
       </c>
@@ -3680,13 +3700,13 @@
       <c r="AN31" s="5"/>
       <c r="AO31" s="5"/>
       <c r="AP31" s="5"/>
-      <c r="AQ31" s="30"/>
-      <c r="AR31" s="26"/>
+      <c r="AQ31" s="28"/>
+      <c r="AR31" s="38"/>
     </row>
     <row r="32" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="45"/>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
+      <c r="A32" s="35"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
       <c r="D32" s="9" t="s">
         <v>20</v>
       </c>
@@ -3731,13 +3751,13 @@
       </c>
       <c r="AO32" s="5"/>
       <c r="AP32" s="5"/>
-      <c r="AQ32" s="30"/>
-      <c r="AR32" s="26"/>
+      <c r="AQ32" s="28"/>
+      <c r="AR32" s="38"/>
     </row>
     <row r="33" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="45"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="30"/>
+      <c r="A33" s="35"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
       <c r="D33" s="9" t="s">
         <v>21</v>
       </c>
@@ -3782,13 +3802,13 @@
         <v>0</v>
       </c>
       <c r="AP33" s="5"/>
-      <c r="AQ33" s="30"/>
-      <c r="AR33" s="26"/>
+      <c r="AQ33" s="28"/>
+      <c r="AR33" s="38"/>
     </row>
     <row r="34" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="45"/>
-      <c r="B34" s="31"/>
-      <c r="C34" s="31"/>
+      <c r="A34" s="35"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
       <c r="D34" s="10" t="s">
         <v>22</v>
       </c>
@@ -3833,15 +3853,15 @@
         <f>SUM(E34:AI34)</f>
         <v>0</v>
       </c>
-      <c r="AQ34" s="31"/>
-      <c r="AR34" s="27"/>
+      <c r="AQ34" s="29"/>
+      <c r="AR34" s="39"/>
     </row>
     <row r="35" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="44"/>
-      <c r="B35" s="38">
+      <c r="A35" s="34"/>
+      <c r="B35" s="40">
         <v>5</v>
       </c>
-      <c r="C35" s="29" t="s">
+      <c r="C35" s="41" t="s">
         <v>15</v>
       </c>
       <c r="D35" s="3" t="s">
@@ -3888,16 +3908,16 @@
       <c r="AN35" s="5"/>
       <c r="AO35" s="5"/>
       <c r="AP35" s="5"/>
-      <c r="AQ35" s="35">
+      <c r="AQ35" s="27">
         <f>COUNTIF(E35:AI35,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR35" s="25"/>
+      <c r="AR35" s="37"/>
     </row>
     <row r="36" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="45"/>
-      <c r="B36" s="30"/>
-      <c r="C36" s="30"/>
+      <c r="A36" s="35"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
       <c r="D36" s="6" t="s">
         <v>17</v>
       </c>
@@ -3942,13 +3962,13 @@
       <c r="AN36" s="5"/>
       <c r="AO36" s="5"/>
       <c r="AP36" s="5"/>
-      <c r="AQ36" s="30"/>
-      <c r="AR36" s="26"/>
+      <c r="AQ36" s="28"/>
+      <c r="AR36" s="38"/>
     </row>
     <row r="37" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="45"/>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
+      <c r="A37" s="35"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
       <c r="D37" s="7" t="s">
         <v>18</v>
       </c>
@@ -3993,13 +4013,13 @@
       <c r="AN37" s="5"/>
       <c r="AO37" s="5"/>
       <c r="AP37" s="5"/>
-      <c r="AQ37" s="30"/>
-      <c r="AR37" s="26"/>
+      <c r="AQ37" s="28"/>
+      <c r="AR37" s="38"/>
     </row>
     <row r="38" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="45"/>
-      <c r="B38" s="30"/>
-      <c r="C38" s="30"/>
+      <c r="A38" s="35"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="28"/>
       <c r="D38" s="8" t="s">
         <v>19</v>
       </c>
@@ -4044,13 +4064,13 @@
       <c r="AN38" s="5"/>
       <c r="AO38" s="5"/>
       <c r="AP38" s="5"/>
-      <c r="AQ38" s="30"/>
-      <c r="AR38" s="26"/>
+      <c r="AQ38" s="28"/>
+      <c r="AR38" s="38"/>
     </row>
     <row r="39" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="45"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="30"/>
+      <c r="A39" s="35"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="28"/>
       <c r="D39" s="9" t="s">
         <v>20</v>
       </c>
@@ -4095,13 +4115,13 @@
       </c>
       <c r="AO39" s="5"/>
       <c r="AP39" s="5"/>
-      <c r="AQ39" s="30"/>
-      <c r="AR39" s="26"/>
+      <c r="AQ39" s="28"/>
+      <c r="AR39" s="38"/>
     </row>
     <row r="40" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="45"/>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
+      <c r="A40" s="35"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="28"/>
       <c r="D40" s="9" t="s">
         <v>21</v>
       </c>
@@ -4146,13 +4166,13 @@
         <v>0</v>
       </c>
       <c r="AP40" s="5"/>
-      <c r="AQ40" s="30"/>
-      <c r="AR40" s="26"/>
+      <c r="AQ40" s="28"/>
+      <c r="AR40" s="38"/>
     </row>
     <row r="41" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="45"/>
-      <c r="B41" s="31"/>
-      <c r="C41" s="31"/>
+      <c r="A41" s="35"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
       <c r="D41" s="10" t="s">
         <v>22</v>
       </c>
@@ -4197,15 +4217,15 @@
         <f>SUM(E41:AI41)</f>
         <v>0</v>
       </c>
-      <c r="AQ41" s="31"/>
-      <c r="AR41" s="27"/>
+      <c r="AQ41" s="29"/>
+      <c r="AR41" s="39"/>
     </row>
     <row r="42" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="44"/>
-      <c r="B42" s="38">
+      <c r="A42" s="34"/>
+      <c r="B42" s="40">
         <v>6</v>
       </c>
-      <c r="C42" s="29" t="s">
+      <c r="C42" s="41" t="s">
         <v>15</v>
       </c>
       <c r="D42" s="3" t="s">
@@ -4252,16 +4272,16 @@
       <c r="AN42" s="5"/>
       <c r="AO42" s="5"/>
       <c r="AP42" s="5"/>
-      <c r="AQ42" s="35">
+      <c r="AQ42" s="27">
         <f>COUNTIF(E42:AI42,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR42" s="25"/>
+      <c r="AR42" s="37"/>
     </row>
     <row r="43" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="45"/>
-      <c r="B43" s="30"/>
-      <c r="C43" s="30"/>
+      <c r="A43" s="35"/>
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
       <c r="D43" s="6" t="s">
         <v>17</v>
       </c>
@@ -4306,13 +4326,13 @@
       <c r="AN43" s="5"/>
       <c r="AO43" s="5"/>
       <c r="AP43" s="5"/>
-      <c r="AQ43" s="30"/>
-      <c r="AR43" s="26"/>
+      <c r="AQ43" s="28"/>
+      <c r="AR43" s="38"/>
     </row>
     <row r="44" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="45"/>
-      <c r="B44" s="30"/>
-      <c r="C44" s="30"/>
+      <c r="A44" s="35"/>
+      <c r="B44" s="28"/>
+      <c r="C44" s="28"/>
       <c r="D44" s="7" t="s">
         <v>18</v>
       </c>
@@ -4357,13 +4377,13 @@
       <c r="AN44" s="5"/>
       <c r="AO44" s="5"/>
       <c r="AP44" s="5"/>
-      <c r="AQ44" s="30"/>
-      <c r="AR44" s="26"/>
+      <c r="AQ44" s="28"/>
+      <c r="AR44" s="38"/>
     </row>
     <row r="45" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="45"/>
-      <c r="B45" s="30"/>
-      <c r="C45" s="30"/>
+      <c r="A45" s="35"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="28"/>
       <c r="D45" s="8" t="s">
         <v>19</v>
       </c>
@@ -4408,13 +4428,13 @@
       <c r="AN45" s="5"/>
       <c r="AO45" s="5"/>
       <c r="AP45" s="5"/>
-      <c r="AQ45" s="30"/>
-      <c r="AR45" s="26"/>
+      <c r="AQ45" s="28"/>
+      <c r="AR45" s="38"/>
     </row>
     <row r="46" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="45"/>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
+      <c r="A46" s="35"/>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
       <c r="D46" s="9" t="s">
         <v>20</v>
       </c>
@@ -4459,13 +4479,13 @@
       </c>
       <c r="AO46" s="5"/>
       <c r="AP46" s="5"/>
-      <c r="AQ46" s="30"/>
-      <c r="AR46" s="26"/>
+      <c r="AQ46" s="28"/>
+      <c r="AR46" s="38"/>
     </row>
     <row r="47" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="45"/>
-      <c r="B47" s="30"/>
-      <c r="C47" s="30"/>
+      <c r="A47" s="35"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
       <c r="D47" s="9" t="s">
         <v>21</v>
       </c>
@@ -4510,13 +4530,13 @@
         <v>0</v>
       </c>
       <c r="AP47" s="5"/>
-      <c r="AQ47" s="30"/>
-      <c r="AR47" s="26"/>
+      <c r="AQ47" s="28"/>
+      <c r="AR47" s="38"/>
     </row>
     <row r="48" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="45"/>
-      <c r="B48" s="31"/>
-      <c r="C48" s="31"/>
+      <c r="A48" s="35"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
       <c r="D48" s="10" t="s">
         <v>22</v>
       </c>
@@ -4561,15 +4581,15 @@
         <f>SUM(E48:AI48)</f>
         <v>0</v>
       </c>
-      <c r="AQ48" s="31"/>
-      <c r="AR48" s="27"/>
+      <c r="AQ48" s="29"/>
+      <c r="AR48" s="39"/>
     </row>
     <row r="49" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="44"/>
-      <c r="B49" s="38">
+      <c r="A49" s="34"/>
+      <c r="B49" s="40">
         <v>7</v>
       </c>
-      <c r="C49" s="46" t="s">
+      <c r="C49" s="47" t="s">
         <v>15</v>
       </c>
       <c r="D49" s="3" t="s">
@@ -4616,16 +4636,16 @@
       <c r="AN49" s="5"/>
       <c r="AO49" s="5"/>
       <c r="AP49" s="5"/>
-      <c r="AQ49" s="35">
+      <c r="AQ49" s="27">
         <f>COUNTIF(E49:AI49,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR49" s="25"/>
+      <c r="AR49" s="37"/>
     </row>
     <row r="50" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="45"/>
-      <c r="B50" s="30"/>
-      <c r="C50" s="30"/>
+      <c r="A50" s="35"/>
+      <c r="B50" s="28"/>
+      <c r="C50" s="28"/>
       <c r="D50" s="6" t="s">
         <v>17</v>
       </c>
@@ -4670,13 +4690,13 @@
       <c r="AN50" s="5"/>
       <c r="AO50" s="5"/>
       <c r="AP50" s="5"/>
-      <c r="AQ50" s="30"/>
-      <c r="AR50" s="26"/>
+      <c r="AQ50" s="28"/>
+      <c r="AR50" s="38"/>
     </row>
     <row r="51" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="45"/>
-      <c r="B51" s="30"/>
-      <c r="C51" s="30"/>
+      <c r="A51" s="35"/>
+      <c r="B51" s="28"/>
+      <c r="C51" s="28"/>
       <c r="D51" s="7" t="s">
         <v>18</v>
       </c>
@@ -4721,13 +4741,13 @@
       <c r="AN51" s="5"/>
       <c r="AO51" s="5"/>
       <c r="AP51" s="5"/>
-      <c r="AQ51" s="30"/>
-      <c r="AR51" s="26"/>
+      <c r="AQ51" s="28"/>
+      <c r="AR51" s="38"/>
     </row>
     <row r="52" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="45"/>
-      <c r="B52" s="30"/>
-      <c r="C52" s="30"/>
+      <c r="A52" s="35"/>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
       <c r="D52" s="8" t="s">
         <v>19</v>
       </c>
@@ -4772,13 +4792,13 @@
       <c r="AN52" s="5"/>
       <c r="AO52" s="5"/>
       <c r="AP52" s="5"/>
-      <c r="AQ52" s="30"/>
-      <c r="AR52" s="26"/>
+      <c r="AQ52" s="28"/>
+      <c r="AR52" s="38"/>
     </row>
     <row r="53" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="45"/>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30"/>
+      <c r="A53" s="35"/>
+      <c r="B53" s="28"/>
+      <c r="C53" s="28"/>
       <c r="D53" s="9" t="s">
         <v>20</v>
       </c>
@@ -4823,13 +4843,13 @@
       </c>
       <c r="AO53" s="5"/>
       <c r="AP53" s="5"/>
-      <c r="AQ53" s="30"/>
-      <c r="AR53" s="26"/>
+      <c r="AQ53" s="28"/>
+      <c r="AR53" s="38"/>
     </row>
     <row r="54" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="45"/>
-      <c r="B54" s="30"/>
-      <c r="C54" s="30"/>
+      <c r="A54" s="35"/>
+      <c r="B54" s="28"/>
+      <c r="C54" s="28"/>
       <c r="D54" s="9" t="s">
         <v>21</v>
       </c>
@@ -4874,13 +4894,13 @@
         <v>0</v>
       </c>
       <c r="AP54" s="5"/>
-      <c r="AQ54" s="30"/>
-      <c r="AR54" s="26"/>
+      <c r="AQ54" s="28"/>
+      <c r="AR54" s="38"/>
     </row>
     <row r="55" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="45"/>
-      <c r="B55" s="31"/>
-      <c r="C55" s="31"/>
+      <c r="A55" s="35"/>
+      <c r="B55" s="29"/>
+      <c r="C55" s="29"/>
       <c r="D55" s="10" t="s">
         <v>22</v>
       </c>
@@ -4925,15 +4945,15 @@
         <f>SUM(E55:AI55)</f>
         <v>0</v>
       </c>
-      <c r="AQ55" s="31"/>
-      <c r="AR55" s="27"/>
+      <c r="AQ55" s="29"/>
+      <c r="AR55" s="39"/>
     </row>
     <row r="56" spans="1:44" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="44"/>
-      <c r="B56" s="38">
+      <c r="A56" s="34"/>
+      <c r="B56" s="40">
         <v>8</v>
       </c>
-      <c r="C56" s="46" t="s">
+      <c r="C56" s="47" t="s">
         <v>15</v>
       </c>
       <c r="D56" s="3" t="s">
@@ -4980,16 +5000,16 @@
       <c r="AN56" s="5"/>
       <c r="AO56" s="5"/>
       <c r="AP56" s="5"/>
-      <c r="AQ56" s="35">
+      <c r="AQ56" s="27">
         <f>COUNTIF(E56:AI56,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR56" s="25"/>
+      <c r="AR56" s="37"/>
     </row>
     <row r="57" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="45"/>
-      <c r="B57" s="30"/>
-      <c r="C57" s="30"/>
+      <c r="A57" s="35"/>
+      <c r="B57" s="28"/>
+      <c r="C57" s="28"/>
       <c r="D57" s="6" t="s">
         <v>17</v>
       </c>
@@ -5034,13 +5054,13 @@
       <c r="AN57" s="5"/>
       <c r="AO57" s="5"/>
       <c r="AP57" s="5"/>
-      <c r="AQ57" s="30"/>
-      <c r="AR57" s="26"/>
+      <c r="AQ57" s="28"/>
+      <c r="AR57" s="38"/>
     </row>
     <row r="58" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="45"/>
-      <c r="B58" s="30"/>
-      <c r="C58" s="30"/>
+      <c r="A58" s="35"/>
+      <c r="B58" s="28"/>
+      <c r="C58" s="28"/>
       <c r="D58" s="7" t="s">
         <v>18</v>
       </c>
@@ -5085,13 +5105,13 @@
       <c r="AN58" s="5"/>
       <c r="AO58" s="5"/>
       <c r="AP58" s="5"/>
-      <c r="AQ58" s="30"/>
-      <c r="AR58" s="26"/>
+      <c r="AQ58" s="28"/>
+      <c r="AR58" s="38"/>
     </row>
     <row r="59" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="45"/>
-      <c r="B59" s="30"/>
-      <c r="C59" s="30"/>
+      <c r="A59" s="35"/>
+      <c r="B59" s="28"/>
+      <c r="C59" s="28"/>
       <c r="D59" s="8" t="s">
         <v>19</v>
       </c>
@@ -5136,13 +5156,13 @@
       <c r="AN59" s="5"/>
       <c r="AO59" s="5"/>
       <c r="AP59" s="5"/>
-      <c r="AQ59" s="30"/>
-      <c r="AR59" s="26"/>
+      <c r="AQ59" s="28"/>
+      <c r="AR59" s="38"/>
     </row>
     <row r="60" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="45"/>
-      <c r="B60" s="30"/>
-      <c r="C60" s="30"/>
+      <c r="A60" s="35"/>
+      <c r="B60" s="28"/>
+      <c r="C60" s="28"/>
       <c r="D60" s="9" t="s">
         <v>20</v>
       </c>
@@ -5187,13 +5207,13 @@
       </c>
       <c r="AO60" s="5"/>
       <c r="AP60" s="5"/>
-      <c r="AQ60" s="30"/>
-      <c r="AR60" s="26"/>
+      <c r="AQ60" s="28"/>
+      <c r="AR60" s="38"/>
     </row>
     <row r="61" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="45"/>
-      <c r="B61" s="30"/>
-      <c r="C61" s="30"/>
+      <c r="A61" s="35"/>
+      <c r="B61" s="28"/>
+      <c r="C61" s="28"/>
       <c r="D61" s="9" t="s">
         <v>21</v>
       </c>
@@ -5238,13 +5258,13 @@
         <v>0</v>
       </c>
       <c r="AP61" s="5"/>
-      <c r="AQ61" s="30"/>
-      <c r="AR61" s="26"/>
+      <c r="AQ61" s="28"/>
+      <c r="AR61" s="38"/>
     </row>
     <row r="62" spans="1:44" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="45"/>
-      <c r="B62" s="31"/>
-      <c r="C62" s="31"/>
+      <c r="A62" s="35"/>
+      <c r="B62" s="29"/>
+      <c r="C62" s="29"/>
       <c r="D62" s="10" t="s">
         <v>22</v>
       </c>
@@ -5289,49 +5309,49 @@
         <f>SUM(E62:AI62)</f>
         <v>0</v>
       </c>
-      <c r="AQ62" s="31"/>
-      <c r="AR62" s="27"/>
+      <c r="AQ62" s="29"/>
+      <c r="AR62" s="39"/>
     </row>
     <row r="63" spans="1:44" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="14"/>
-      <c r="B63" s="39" t="s">
+      <c r="B63" s="53" t="s">
         <v>23</v>
       </c>
-      <c r="C63" s="40"/>
-      <c r="D63" s="41"/>
-      <c r="E63" s="32" t="s">
+      <c r="C63" s="54"/>
+      <c r="D63" s="55"/>
+      <c r="E63" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="F63" s="33"/>
-      <c r="G63" s="33"/>
-      <c r="H63" s="33"/>
-      <c r="I63" s="33"/>
-      <c r="J63" s="33"/>
-      <c r="K63" s="33"/>
-      <c r="L63" s="33"/>
-      <c r="M63" s="33"/>
-      <c r="N63" s="33"/>
-      <c r="O63" s="33"/>
-      <c r="P63" s="33"/>
-      <c r="Q63" s="33"/>
-      <c r="R63" s="33"/>
-      <c r="S63" s="33"/>
-      <c r="T63" s="33"/>
-      <c r="U63" s="33"/>
-      <c r="V63" s="33"/>
-      <c r="W63" s="33"/>
-      <c r="X63" s="33"/>
-      <c r="Y63" s="33"/>
-      <c r="Z63" s="33"/>
-      <c r="AA63" s="33"/>
-      <c r="AB63" s="33"/>
-      <c r="AC63" s="33"/>
-      <c r="AD63" s="33"/>
-      <c r="AE63" s="33"/>
-      <c r="AF63" s="33"/>
-      <c r="AG63" s="33"/>
-      <c r="AH63" s="33"/>
-      <c r="AI63" s="34"/>
+      <c r="F63" s="50"/>
+      <c r="G63" s="50"/>
+      <c r="H63" s="50"/>
+      <c r="I63" s="50"/>
+      <c r="J63" s="50"/>
+      <c r="K63" s="50"/>
+      <c r="L63" s="50"/>
+      <c r="M63" s="50"/>
+      <c r="N63" s="50"/>
+      <c r="O63" s="50"/>
+      <c r="P63" s="50"/>
+      <c r="Q63" s="50"/>
+      <c r="R63" s="50"/>
+      <c r="S63" s="50"/>
+      <c r="T63" s="50"/>
+      <c r="U63" s="50"/>
+      <c r="V63" s="50"/>
+      <c r="W63" s="50"/>
+      <c r="X63" s="50"/>
+      <c r="Y63" s="50"/>
+      <c r="Z63" s="50"/>
+      <c r="AA63" s="50"/>
+      <c r="AB63" s="50"/>
+      <c r="AC63" s="50"/>
+      <c r="AD63" s="50"/>
+      <c r="AE63" s="50"/>
+      <c r="AF63" s="50"/>
+      <c r="AG63" s="50"/>
+      <c r="AH63" s="50"/>
+      <c r="AI63" s="51"/>
       <c r="AJ63" s="13">
         <f t="shared" ref="AJ63:AP63" si="0">SUM(AJ7:AJ55)</f>
         <v>0</v>
@@ -5360,26 +5380,54 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AQ63" s="42" t="s">
+      <c r="AQ63" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="AR63" s="43"/>
+      <c r="AR63" s="57"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="uXz7IkwNnKjilI/Hz/CZ0V74Yl6g0tz3rpClsJ+nYXWRF4U6PfxzxVf7aO2sKzmAqwtgPwrNgoZGnO30/Yf18g==" saltValue="PkgGAmfnKf0KnwCCqwTXlw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="7l2H75vtBAPXuNk3rjxQR/apet362+8gn6pMMFGEbdiJmbGMaSswqqK23Ij0Bor2UOmWYi2XHJRMjhEivPTH3A==" saltValue="tebfZusMGaVWgzqHUaB6Xg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="68">
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="M3:P3"/>
-    <mergeCell ref="AP5:AP6"/>
-    <mergeCell ref="AQ21:AQ27"/>
-    <mergeCell ref="E1:V1"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="P2:W2"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="E2:L2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="E4:AQ4"/>
-    <mergeCell ref="AQ5:AQ6"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="AR14:AR20"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="C14:C20"/>
+    <mergeCell ref="E63:AI63"/>
+    <mergeCell ref="AQ56:AQ62"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="B42:B48"/>
+    <mergeCell ref="B14:B20"/>
+    <mergeCell ref="C35:C41"/>
+    <mergeCell ref="AR35:AR41"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="AQ49:AQ55"/>
+    <mergeCell ref="C28:C34"/>
+    <mergeCell ref="AQ63:AR63"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="B56:B62"/>
+    <mergeCell ref="AR56:AR62"/>
+    <mergeCell ref="A49:A55"/>
+    <mergeCell ref="C42:C48"/>
+    <mergeCell ref="C49:C55"/>
+    <mergeCell ref="AR49:AR55"/>
+    <mergeCell ref="C56:C62"/>
+    <mergeCell ref="A56:A62"/>
+    <mergeCell ref="A42:A48"/>
+    <mergeCell ref="AQ42:AQ48"/>
+    <mergeCell ref="B49:B55"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="AR5:AR6"/>
+    <mergeCell ref="AO5:AO6"/>
+    <mergeCell ref="C21:C27"/>
+    <mergeCell ref="AN5:AN6"/>
+    <mergeCell ref="AR21:AR27"/>
+    <mergeCell ref="AQ35:AQ41"/>
+    <mergeCell ref="C7:C13"/>
+    <mergeCell ref="B7:B13"/>
+    <mergeCell ref="AR7:AR13"/>
+    <mergeCell ref="B21:B27"/>
+    <mergeCell ref="AQ7:AQ13"/>
     <mergeCell ref="A7:A13"/>
     <mergeCell ref="A28:A34"/>
     <mergeCell ref="A14:A20"/>
@@ -5396,46 +5444,18 @@
     <mergeCell ref="AK5:AK6"/>
     <mergeCell ref="AM5:AM6"/>
     <mergeCell ref="AL5:AL6"/>
-    <mergeCell ref="AQ35:AQ41"/>
-    <mergeCell ref="C7:C13"/>
-    <mergeCell ref="B7:B13"/>
-    <mergeCell ref="AR7:AR13"/>
-    <mergeCell ref="B21:B27"/>
-    <mergeCell ref="AQ7:AQ13"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="AR5:AR6"/>
-    <mergeCell ref="AO5:AO6"/>
-    <mergeCell ref="C21:C27"/>
-    <mergeCell ref="AN5:AN6"/>
-    <mergeCell ref="AR21:AR27"/>
-    <mergeCell ref="B56:B62"/>
-    <mergeCell ref="AR56:AR62"/>
-    <mergeCell ref="A49:A55"/>
-    <mergeCell ref="C42:C48"/>
-    <mergeCell ref="C49:C55"/>
-    <mergeCell ref="AR49:AR55"/>
-    <mergeCell ref="C56:C62"/>
-    <mergeCell ref="A56:A62"/>
-    <mergeCell ref="A42:A48"/>
-    <mergeCell ref="AQ42:AQ48"/>
-    <mergeCell ref="B49:B55"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="AR14:AR20"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="C14:C20"/>
-    <mergeCell ref="E63:AI63"/>
-    <mergeCell ref="AQ56:AQ62"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="B42:B48"/>
-    <mergeCell ref="B14:B20"/>
-    <mergeCell ref="C35:C41"/>
-    <mergeCell ref="AR35:AR41"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="AQ49:AQ55"/>
-    <mergeCell ref="C28:C34"/>
-    <mergeCell ref="AQ63:AR63"/>
-    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="M3:P3"/>
+    <mergeCell ref="AP5:AP6"/>
+    <mergeCell ref="AQ21:AQ27"/>
+    <mergeCell ref="E1:V1"/>
+    <mergeCell ref="M2:O2"/>
+    <mergeCell ref="P2:W2"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="E2:L2"/>
+    <mergeCell ref="X2:Z2"/>
+    <mergeCell ref="E4:AQ4"/>
+    <mergeCell ref="AQ5:AQ6"/>
   </mergeCells>
   <conditionalFormatting sqref="E6">
     <cfRule type="expression" dxfId="61" priority="188">

--- a/public/moduli/FoglioPresenze_StudioBaiocco.xlsx
+++ b/public/moduli/FoglioPresenze_StudioBaiocco.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Desktop/sito_mamma/public/moduli/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{615AE5AF-E6F9-244E-9428-4DED83935449}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E9D341-80FB-5F44-B068-12227D44736B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="660" windowWidth="30240" windowHeight="17680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presenze" sheetId="1" r:id="rId1"/>
@@ -146,7 +146,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -226,13 +226,6 @@
     </font>
     <font>
       <b/>
-      <sz val="24"/>
-      <color rgb="FF1A2B4A"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -264,32 +257,17 @@
     </font>
     <font>
       <b/>
-      <i/>
-      <sz val="16"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="20"/>
       <color rgb="FF1A2B4A"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <b/>
+      <sz val="22"/>
+      <color rgb="FF1A2B4A"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="24"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="16">
@@ -384,7 +362,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -572,21 +550,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="medium">
         <color indexed="64"/>
@@ -629,12 +592,73 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -704,88 +728,27 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="justify"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="justify"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="justify"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
@@ -793,15 +756,110 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="justify"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="justify"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="justify"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="justify"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -1544,16 +1602,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>139700</xdr:colOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>41</xdr:col>
-      <xdr:colOff>127000</xdr:colOff>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>20985</xdr:rowOff>
+      <xdr:rowOff>46385</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1576,7 +1634,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11150600" y="12700"/>
+          <a:off x="12153900" y="38100"/>
           <a:ext cx="5067300" cy="1240185"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1923,9 +1981,9 @@
     <col min="3" max="3" width="18.6640625" customWidth="1"/>
     <col min="4" max="4" width="20.6640625" customWidth="1"/>
     <col min="5" max="14" width="3.83203125" customWidth="1"/>
-    <col min="15" max="15" width="7.5" customWidth="1"/>
+    <col min="15" max="15" width="2.83203125" bestFit="1" customWidth="1"/>
     <col min="16" max="25" width="3.83203125" customWidth="1"/>
-    <col min="26" max="26" width="10" customWidth="1"/>
+    <col min="26" max="26" width="2.83203125" bestFit="1" customWidth="1"/>
     <col min="27" max="35" width="3.83203125" customWidth="1"/>
     <col min="36" max="40" width="7" customWidth="1"/>
     <col min="42" max="42" width="8.33203125" customWidth="1"/>
@@ -1935,29 +1993,29 @@
   <sheetData>
     <row r="1" spans="1:44" ht="35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14"/>
-      <c r="B1" s="48" t="s">
+      <c r="B1" s="23" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="24"/>
       <c r="D1" s="24"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
-      <c r="R1" s="24"/>
-      <c r="S1" s="24"/>
-      <c r="T1" s="24"/>
-      <c r="U1" s="24"/>
-      <c r="V1" s="24"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="25"/>
+      <c r="Q1" s="25"/>
+      <c r="R1" s="25"/>
+      <c r="S1" s="25"/>
+      <c r="T1" s="25"/>
+      <c r="U1" s="25"/>
+      <c r="V1" s="25"/>
       <c r="W1" s="15"/>
       <c r="X1" s="15"/>
       <c r="Y1" s="15"/>
@@ -1981,43 +2039,43 @@
       <c r="AQ1" s="15"/>
       <c r="AR1" s="15"/>
     </row>
-    <row r="2" spans="1:44" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:44" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
       <c r="B2" s="24"/>
       <c r="C2" s="24"/>
       <c r="D2" s="24"/>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="31"/>
-      <c r="M2" s="32">
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="48">
         <v>3</v>
       </c>
-      <c r="N2" s="61"/>
-      <c r="O2" s="62"/>
-      <c r="P2" s="30" t="s">
+      <c r="N2" s="49"/>
+      <c r="O2" s="49"/>
+      <c r="P2" s="50"/>
+      <c r="Q2" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="24"/>
-      <c r="V2" s="24"/>
-      <c r="W2" s="31"/>
-      <c r="X2" s="58">
+      <c r="R2" s="65"/>
+      <c r="S2" s="65"/>
+      <c r="T2" s="65"/>
+      <c r="U2" s="65"/>
+      <c r="V2" s="65"/>
+      <c r="W2" s="43"/>
+      <c r="X2" s="45">
         <v>2026</v>
       </c>
-      <c r="Y2" s="59"/>
-      <c r="Z2" s="60"/>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="15"/>
+      <c r="Y2" s="46"/>
+      <c r="Z2" s="46"/>
+      <c r="AA2" s="46"/>
+      <c r="AB2" s="47"/>
       <c r="AC2" s="15"/>
       <c r="AD2" s="15"/>
       <c r="AE2" s="15"/>
@@ -2037,29 +2095,29 @@
     </row>
     <row r="3" spans="1:44" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="14"/>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="42" t="s">
         <v>3</v>
       </c>
       <c r="C3" s="24"/>
       <c r="D3" s="24"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="23"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="23"/>
-      <c r="R3" s="24"/>
-      <c r="S3" s="24"/>
-      <c r="T3" s="24"/>
-      <c r="U3" s="23"/>
-      <c r="V3" s="24"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
+      <c r="K3" s="25"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="25"/>
+      <c r="R3" s="25"/>
+      <c r="S3" s="25"/>
+      <c r="T3" s="25"/>
+      <c r="U3" s="25"/>
+      <c r="V3" s="25"/>
       <c r="W3" s="15"/>
       <c r="X3" s="15"/>
       <c r="Y3" s="15"/>
@@ -2088,58 +2146,58 @@
       <c r="B4" s="24"/>
       <c r="C4" s="24"/>
       <c r="D4" s="24"/>
-      <c r="E4" s="33" t="s">
+      <c r="E4" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="24"/>
-      <c r="G4" s="24"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="24"/>
-      <c r="K4" s="24"/>
-      <c r="L4" s="24"/>
-      <c r="M4" s="24"/>
-      <c r="N4" s="24"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="24"/>
-      <c r="Q4" s="24"/>
-      <c r="R4" s="24"/>
-      <c r="S4" s="24"/>
-      <c r="T4" s="24"/>
-      <c r="U4" s="24"/>
-      <c r="V4" s="24"/>
-      <c r="W4" s="24"/>
-      <c r="X4" s="24"/>
-      <c r="Y4" s="24"/>
-      <c r="Z4" s="24"/>
-      <c r="AA4" s="24"/>
-      <c r="AB4" s="24"/>
-      <c r="AC4" s="24"/>
-      <c r="AD4" s="24"/>
-      <c r="AE4" s="24"/>
-      <c r="AF4" s="24"/>
-      <c r="AG4" s="24"/>
-      <c r="AH4" s="24"/>
-      <c r="AI4" s="24"/>
-      <c r="AJ4" s="24"/>
-      <c r="AK4" s="24"/>
-      <c r="AL4" s="24"/>
-      <c r="AM4" s="24"/>
-      <c r="AN4" s="24"/>
-      <c r="AO4" s="24"/>
-      <c r="AP4" s="24"/>
-      <c r="AQ4" s="24"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="44"/>
+      <c r="O4" s="44"/>
+      <c r="P4" s="44"/>
+      <c r="Q4" s="44"/>
+      <c r="R4" s="44"/>
+      <c r="S4" s="44"/>
+      <c r="T4" s="44"/>
+      <c r="U4" s="44"/>
+      <c r="V4" s="44"/>
+      <c r="W4" s="44"/>
+      <c r="X4" s="44"/>
+      <c r="Y4" s="44"/>
+      <c r="Z4" s="44"/>
+      <c r="AA4" s="44"/>
+      <c r="AB4" s="44"/>
+      <c r="AC4" s="44"/>
+      <c r="AD4" s="44"/>
+      <c r="AE4" s="44"/>
+      <c r="AF4" s="44"/>
+      <c r="AG4" s="44"/>
+      <c r="AH4" s="44"/>
+      <c r="AI4" s="44"/>
+      <c r="AJ4" s="44"/>
+      <c r="AK4" s="44"/>
+      <c r="AL4" s="44"/>
+      <c r="AM4" s="44"/>
+      <c r="AN4" s="44"/>
+      <c r="AO4" s="44"/>
+      <c r="AP4" s="44"/>
+      <c r="AQ4" s="44"/>
       <c r="AR4" s="16"/>
     </row>
     <row r="5" spans="1:44" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14"/>
-      <c r="B5" s="44" t="s">
+      <c r="B5" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="52" t="s">
+      <c r="C5" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="46"/>
+      <c r="D5" s="40"/>
       <c r="E5" s="1">
         <v>1</v>
       </c>
@@ -2233,39 +2291,39 @@
       <c r="AI5" s="1">
         <v>31</v>
       </c>
-      <c r="AJ5" s="25" t="s">
+      <c r="AJ5" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="AK5" s="25" t="s">
+      <c r="AK5" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="AL5" s="25" t="s">
+      <c r="AL5" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="AM5" s="25" t="s">
+      <c r="AM5" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="AN5" s="25" t="s">
+      <c r="AN5" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="AO5" s="25" t="s">
+      <c r="AO5" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="AP5" s="25" t="s">
+      <c r="AP5" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="AQ5" s="25" t="s">
+      <c r="AQ5" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="AR5" s="25" t="s">
+      <c r="AR5" s="61" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="14"/>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
       <c r="E6" s="2" t="str">
         <f>IFERROR(IF(1&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,1),2),"L","M","M","G","V","S","D")),"")</f>
         <v>D</v>
@@ -2390,22 +2448,22 @@
         <f>IFERROR(IF(31&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,31),2),"L","M","M","G","V","S","D")),"")</f>
         <v>M</v>
       </c>
-      <c r="AJ6" s="26"/>
-      <c r="AK6" s="26"/>
-      <c r="AL6" s="26"/>
-      <c r="AM6" s="26"/>
-      <c r="AN6" s="26"/>
-      <c r="AO6" s="26"/>
-      <c r="AP6" s="26"/>
-      <c r="AQ6" s="26"/>
-      <c r="AR6" s="26"/>
-    </row>
-    <row r="7" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="34"/>
-      <c r="B7" s="42">
+      <c r="AJ6" s="62"/>
+      <c r="AK6" s="62"/>
+      <c r="AL6" s="62"/>
+      <c r="AM6" s="62"/>
+      <c r="AN6" s="62"/>
+      <c r="AO6" s="62"/>
+      <c r="AP6" s="62"/>
+      <c r="AQ6" s="62"/>
+      <c r="AR6" s="62"/>
+    </row>
+    <row r="7" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="36"/>
+      <c r="B7" s="41">
         <v>1</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="26" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -2452,16 +2510,16 @@
       <c r="AN7" s="5"/>
       <c r="AO7" s="5"/>
       <c r="AP7" s="5"/>
-      <c r="AQ7" s="43">
+      <c r="AQ7" s="63">
         <f>COUNTIF(E7:AI7,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR7" s="37"/>
+      <c r="AR7" s="64"/>
     </row>
     <row r="8" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="35"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
+      <c r="A8" s="37"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
       <c r="D8" s="6" t="s">
         <v>17</v>
       </c>
@@ -2506,13 +2564,13 @@
       <c r="AN8" s="5"/>
       <c r="AO8" s="5"/>
       <c r="AP8" s="5"/>
-      <c r="AQ8" s="28"/>
-      <c r="AR8" s="38"/>
+      <c r="AQ8" s="53"/>
+      <c r="AR8" s="56"/>
     </row>
     <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="35"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
+      <c r="A9" s="37"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
       <c r="D9" s="7" t="s">
         <v>18</v>
       </c>
@@ -2557,13 +2615,13 @@
       <c r="AN9" s="5"/>
       <c r="AO9" s="5"/>
       <c r="AP9" s="5"/>
-      <c r="AQ9" s="28"/>
-      <c r="AR9" s="38"/>
+      <c r="AQ9" s="53"/>
+      <c r="AR9" s="56"/>
     </row>
     <row r="10" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="35"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
       <c r="D10" s="8" t="s">
         <v>19</v>
       </c>
@@ -2608,13 +2666,13 @@
       <c r="AN10" s="5"/>
       <c r="AO10" s="5"/>
       <c r="AP10" s="5"/>
-      <c r="AQ10" s="28"/>
-      <c r="AR10" s="38"/>
+      <c r="AQ10" s="53"/>
+      <c r="AR10" s="56"/>
     </row>
     <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="35"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
+      <c r="A11" s="37"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
       <c r="D11" s="9" t="s">
         <v>20</v>
       </c>
@@ -2659,13 +2717,13 @@
       </c>
       <c r="AO11" s="5"/>
       <c r="AP11" s="5"/>
-      <c r="AQ11" s="28"/>
-      <c r="AR11" s="38"/>
+      <c r="AQ11" s="53"/>
+      <c r="AR11" s="56"/>
     </row>
     <row r="12" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="35"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
+      <c r="A12" s="37"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
       <c r="D12" s="9" t="s">
         <v>21</v>
       </c>
@@ -2710,13 +2768,13 @@
         <v>0</v>
       </c>
       <c r="AP12" s="5"/>
-      <c r="AQ12" s="28"/>
-      <c r="AR12" s="38"/>
+      <c r="AQ12" s="53"/>
+      <c r="AR12" s="56"/>
     </row>
     <row r="13" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="35"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
+      <c r="A13" s="37"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
       <c r="D13" s="10" t="s">
         <v>22</v>
       </c>
@@ -2761,15 +2819,15 @@
         <f>SUM(E13:AI13)</f>
         <v>0</v>
       </c>
-      <c r="AQ13" s="29"/>
-      <c r="AR13" s="39"/>
+      <c r="AQ13" s="54"/>
+      <c r="AR13" s="57"/>
     </row>
     <row r="14" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="34"/>
-      <c r="B14" s="40">
+      <c r="A14" s="36"/>
+      <c r="B14" s="31">
         <v>2</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="26" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -2816,16 +2874,16 @@
       <c r="AN14" s="5"/>
       <c r="AO14" s="5"/>
       <c r="AP14" s="5"/>
-      <c r="AQ14" s="27">
+      <c r="AQ14" s="52">
         <f>COUNTIF(E14:AI14,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR14" s="37"/>
+      <c r="AR14" s="55"/>
     </row>
     <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="35"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
+      <c r="A15" s="37"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="27"/>
       <c r="D15" s="6" t="s">
         <v>17</v>
       </c>
@@ -2870,13 +2928,13 @@
       <c r="AN15" s="5"/>
       <c r="AO15" s="5"/>
       <c r="AP15" s="5"/>
-      <c r="AQ15" s="28"/>
-      <c r="AR15" s="38"/>
+      <c r="AQ15" s="53"/>
+      <c r="AR15" s="56"/>
     </row>
     <row r="16" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="35"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
+      <c r="A16" s="37"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
       <c r="D16" s="7" t="s">
         <v>18</v>
       </c>
@@ -2921,13 +2979,13 @@
       <c r="AN16" s="5"/>
       <c r="AO16" s="5"/>
       <c r="AP16" s="5"/>
-      <c r="AQ16" s="28"/>
-      <c r="AR16" s="38"/>
+      <c r="AQ16" s="53"/>
+      <c r="AR16" s="56"/>
     </row>
     <row r="17" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="35"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
+      <c r="A17" s="37"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
       <c r="D17" s="8" t="s">
         <v>19</v>
       </c>
@@ -2972,13 +3030,13 @@
       <c r="AN17" s="5"/>
       <c r="AO17" s="5"/>
       <c r="AP17" s="5"/>
-      <c r="AQ17" s="28"/>
-      <c r="AR17" s="38"/>
+      <c r="AQ17" s="53"/>
+      <c r="AR17" s="56"/>
     </row>
     <row r="18" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="35"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="27"/>
       <c r="D18" s="9" t="s">
         <v>20</v>
       </c>
@@ -3023,13 +3081,13 @@
       </c>
       <c r="AO18" s="5"/>
       <c r="AP18" s="5"/>
-      <c r="AQ18" s="28"/>
-      <c r="AR18" s="38"/>
+      <c r="AQ18" s="53"/>
+      <c r="AR18" s="56"/>
     </row>
     <row r="19" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="35"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
+      <c r="A19" s="37"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27"/>
       <c r="D19" s="9" t="s">
         <v>21</v>
       </c>
@@ -3074,13 +3132,13 @@
         <v>0</v>
       </c>
       <c r="AP19" s="5"/>
-      <c r="AQ19" s="28"/>
-      <c r="AR19" s="38"/>
+      <c r="AQ19" s="53"/>
+      <c r="AR19" s="56"/>
     </row>
     <row r="20" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="35"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
+      <c r="A20" s="37"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
       <c r="D20" s="10" t="s">
         <v>22</v>
       </c>
@@ -3125,15 +3183,15 @@
         <f>SUM(E20:AI20)</f>
         <v>0</v>
       </c>
-      <c r="AQ20" s="29"/>
-      <c r="AR20" s="39"/>
+      <c r="AQ20" s="54"/>
+      <c r="AR20" s="57"/>
     </row>
     <row r="21" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="34"/>
-      <c r="B21" s="40">
+      <c r="A21" s="36"/>
+      <c r="B21" s="31">
         <v>3</v>
       </c>
-      <c r="C21" s="41" t="s">
+      <c r="C21" s="26" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3" t="s">
@@ -3180,16 +3238,16 @@
       <c r="AN21" s="5"/>
       <c r="AO21" s="5"/>
       <c r="AP21" s="5"/>
-      <c r="AQ21" s="27">
+      <c r="AQ21" s="52">
         <f>COUNTIF(E21:AI21,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR21" s="37"/>
+      <c r="AR21" s="55"/>
     </row>
     <row r="22" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="35"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
+      <c r="A22" s="37"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="27"/>
       <c r="D22" s="6" t="s">
         <v>17</v>
       </c>
@@ -3234,13 +3292,13 @@
       <c r="AN22" s="5"/>
       <c r="AO22" s="5"/>
       <c r="AP22" s="5"/>
-      <c r="AQ22" s="28"/>
-      <c r="AR22" s="38"/>
+      <c r="AQ22" s="53"/>
+      <c r="AR22" s="56"/>
     </row>
     <row r="23" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="35"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
+      <c r="A23" s="37"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
       <c r="D23" s="7" t="s">
         <v>18</v>
       </c>
@@ -3285,13 +3343,13 @@
       <c r="AN23" s="5"/>
       <c r="AO23" s="5"/>
       <c r="AP23" s="5"/>
-      <c r="AQ23" s="28"/>
-      <c r="AR23" s="38"/>
+      <c r="AQ23" s="53"/>
+      <c r="AR23" s="56"/>
     </row>
     <row r="24" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="35"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
+      <c r="A24" s="37"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="27"/>
       <c r="D24" s="8" t="s">
         <v>19</v>
       </c>
@@ -3336,13 +3394,13 @@
       <c r="AN24" s="5"/>
       <c r="AO24" s="5"/>
       <c r="AP24" s="5"/>
-      <c r="AQ24" s="28"/>
-      <c r="AR24" s="38"/>
+      <c r="AQ24" s="53"/>
+      <c r="AR24" s="56"/>
     </row>
     <row r="25" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="35"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
+      <c r="A25" s="37"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
       <c r="D25" s="9" t="s">
         <v>20</v>
       </c>
@@ -3387,13 +3445,13 @@
       </c>
       <c r="AO25" s="5"/>
       <c r="AP25" s="5"/>
-      <c r="AQ25" s="28"/>
-      <c r="AR25" s="38"/>
+      <c r="AQ25" s="53"/>
+      <c r="AR25" s="56"/>
     </row>
     <row r="26" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="35"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="27"/>
       <c r="D26" s="9" t="s">
         <v>21</v>
       </c>
@@ -3438,13 +3496,13 @@
         <v>0</v>
       </c>
       <c r="AP26" s="5"/>
-      <c r="AQ26" s="28"/>
-      <c r="AR26" s="38"/>
+      <c r="AQ26" s="53"/>
+      <c r="AR26" s="56"/>
     </row>
     <row r="27" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="35"/>
-      <c r="B27" s="29"/>
-      <c r="C27" s="29"/>
+      <c r="A27" s="37"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
       <c r="D27" s="10" t="s">
         <v>22</v>
       </c>
@@ -3489,15 +3547,15 @@
         <f>SUM(E27:AI27)</f>
         <v>0</v>
       </c>
-      <c r="AQ27" s="29"/>
-      <c r="AR27" s="39"/>
+      <c r="AQ27" s="54"/>
+      <c r="AR27" s="57"/>
     </row>
     <row r="28" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="34"/>
-      <c r="B28" s="40">
+      <c r="A28" s="36"/>
+      <c r="B28" s="31">
         <v>4</v>
       </c>
-      <c r="C28" s="41" t="s">
+      <c r="C28" s="26" t="s">
         <v>15</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -3544,16 +3602,16 @@
       <c r="AN28" s="5"/>
       <c r="AO28" s="5"/>
       <c r="AP28" s="5"/>
-      <c r="AQ28" s="27">
+      <c r="AQ28" s="52">
         <f>COUNTIF(E28:AI28,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR28" s="37"/>
+      <c r="AR28" s="55"/>
     </row>
     <row r="29" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="35"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
+      <c r="A29" s="37"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
       <c r="D29" s="6" t="s">
         <v>17</v>
       </c>
@@ -3598,13 +3656,13 @@
       <c r="AN29" s="5"/>
       <c r="AO29" s="5"/>
       <c r="AP29" s="5"/>
-      <c r="AQ29" s="28"/>
-      <c r="AR29" s="38"/>
+      <c r="AQ29" s="53"/>
+      <c r="AR29" s="56"/>
     </row>
     <row r="30" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="35"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
       <c r="D30" s="7" t="s">
         <v>18</v>
       </c>
@@ -3649,13 +3707,13 @@
       <c r="AN30" s="5"/>
       <c r="AO30" s="5"/>
       <c r="AP30" s="5"/>
-      <c r="AQ30" s="28"/>
-      <c r="AR30" s="38"/>
+      <c r="AQ30" s="53"/>
+      <c r="AR30" s="56"/>
     </row>
     <row r="31" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="35"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
+      <c r="A31" s="37"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="27"/>
       <c r="D31" s="8" t="s">
         <v>19</v>
       </c>
@@ -3700,13 +3758,13 @@
       <c r="AN31" s="5"/>
       <c r="AO31" s="5"/>
       <c r="AP31" s="5"/>
-      <c r="AQ31" s="28"/>
-      <c r="AR31" s="38"/>
+      <c r="AQ31" s="53"/>
+      <c r="AR31" s="56"/>
     </row>
     <row r="32" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="35"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
+      <c r="A32" s="37"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="27"/>
       <c r="D32" s="9" t="s">
         <v>20</v>
       </c>
@@ -3751,13 +3809,13 @@
       </c>
       <c r="AO32" s="5"/>
       <c r="AP32" s="5"/>
-      <c r="AQ32" s="28"/>
-      <c r="AR32" s="38"/>
+      <c r="AQ32" s="53"/>
+      <c r="AR32" s="56"/>
     </row>
     <row r="33" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="35"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
+      <c r="A33" s="37"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="27"/>
       <c r="D33" s="9" t="s">
         <v>21</v>
       </c>
@@ -3802,13 +3860,13 @@
         <v>0</v>
       </c>
       <c r="AP33" s="5"/>
-      <c r="AQ33" s="28"/>
-      <c r="AR33" s="38"/>
+      <c r="AQ33" s="53"/>
+      <c r="AR33" s="56"/>
     </row>
     <row r="34" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="35"/>
-      <c r="B34" s="29"/>
-      <c r="C34" s="29"/>
+      <c r="A34" s="37"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="28"/>
       <c r="D34" s="10" t="s">
         <v>22</v>
       </c>
@@ -3853,15 +3911,15 @@
         <f>SUM(E34:AI34)</f>
         <v>0</v>
       </c>
-      <c r="AQ34" s="29"/>
-      <c r="AR34" s="39"/>
+      <c r="AQ34" s="54"/>
+      <c r="AR34" s="57"/>
     </row>
     <row r="35" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="34"/>
-      <c r="B35" s="40">
+      <c r="A35" s="36"/>
+      <c r="B35" s="31">
         <v>5</v>
       </c>
-      <c r="C35" s="41" t="s">
+      <c r="C35" s="26" t="s">
         <v>15</v>
       </c>
       <c r="D35" s="3" t="s">
@@ -3908,16 +3966,16 @@
       <c r="AN35" s="5"/>
       <c r="AO35" s="5"/>
       <c r="AP35" s="5"/>
-      <c r="AQ35" s="27">
+      <c r="AQ35" s="52">
         <f>COUNTIF(E35:AI35,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR35" s="37"/>
+      <c r="AR35" s="55"/>
     </row>
     <row r="36" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="35"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
+      <c r="A36" s="37"/>
+      <c r="B36" s="27"/>
+      <c r="C36" s="27"/>
       <c r="D36" s="6" t="s">
         <v>17</v>
       </c>
@@ -3962,13 +4020,13 @@
       <c r="AN36" s="5"/>
       <c r="AO36" s="5"/>
       <c r="AP36" s="5"/>
-      <c r="AQ36" s="28"/>
-      <c r="AR36" s="38"/>
+      <c r="AQ36" s="53"/>
+      <c r="AR36" s="56"/>
     </row>
     <row r="37" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="35"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
+      <c r="A37" s="37"/>
+      <c r="B37" s="27"/>
+      <c r="C37" s="27"/>
       <c r="D37" s="7" t="s">
         <v>18</v>
       </c>
@@ -4013,13 +4071,13 @@
       <c r="AN37" s="5"/>
       <c r="AO37" s="5"/>
       <c r="AP37" s="5"/>
-      <c r="AQ37" s="28"/>
-      <c r="AR37" s="38"/>
+      <c r="AQ37" s="53"/>
+      <c r="AR37" s="56"/>
     </row>
     <row r="38" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="35"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
+      <c r="A38" s="37"/>
+      <c r="B38" s="27"/>
+      <c r="C38" s="27"/>
       <c r="D38" s="8" t="s">
         <v>19</v>
       </c>
@@ -4064,13 +4122,13 @@
       <c r="AN38" s="5"/>
       <c r="AO38" s="5"/>
       <c r="AP38" s="5"/>
-      <c r="AQ38" s="28"/>
-      <c r="AR38" s="38"/>
+      <c r="AQ38" s="53"/>
+      <c r="AR38" s="56"/>
     </row>
     <row r="39" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="35"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="28"/>
+      <c r="A39" s="37"/>
+      <c r="B39" s="27"/>
+      <c r="C39" s="27"/>
       <c r="D39" s="9" t="s">
         <v>20</v>
       </c>
@@ -4115,13 +4173,13 @@
       </c>
       <c r="AO39" s="5"/>
       <c r="AP39" s="5"/>
-      <c r="AQ39" s="28"/>
-      <c r="AR39" s="38"/>
+      <c r="AQ39" s="53"/>
+      <c r="AR39" s="56"/>
     </row>
     <row r="40" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="35"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
+      <c r="A40" s="37"/>
+      <c r="B40" s="27"/>
+      <c r="C40" s="27"/>
       <c r="D40" s="9" t="s">
         <v>21</v>
       </c>
@@ -4166,13 +4224,13 @@
         <v>0</v>
       </c>
       <c r="AP40" s="5"/>
-      <c r="AQ40" s="28"/>
-      <c r="AR40" s="38"/>
+      <c r="AQ40" s="53"/>
+      <c r="AR40" s="56"/>
     </row>
     <row r="41" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="35"/>
-      <c r="B41" s="29"/>
-      <c r="C41" s="29"/>
+      <c r="A41" s="37"/>
+      <c r="B41" s="28"/>
+      <c r="C41" s="28"/>
       <c r="D41" s="10" t="s">
         <v>22</v>
       </c>
@@ -4217,15 +4275,15 @@
         <f>SUM(E41:AI41)</f>
         <v>0</v>
       </c>
-      <c r="AQ41" s="29"/>
-      <c r="AR41" s="39"/>
+      <c r="AQ41" s="54"/>
+      <c r="AR41" s="57"/>
     </row>
     <row r="42" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="34"/>
-      <c r="B42" s="40">
+      <c r="A42" s="36"/>
+      <c r="B42" s="31">
         <v>6</v>
       </c>
-      <c r="C42" s="41" t="s">
+      <c r="C42" s="26" t="s">
         <v>15</v>
       </c>
       <c r="D42" s="3" t="s">
@@ -4272,16 +4330,16 @@
       <c r="AN42" s="5"/>
       <c r="AO42" s="5"/>
       <c r="AP42" s="5"/>
-      <c r="AQ42" s="27">
+      <c r="AQ42" s="52">
         <f>COUNTIF(E42:AI42,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR42" s="37"/>
+      <c r="AR42" s="55"/>
     </row>
     <row r="43" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="35"/>
-      <c r="B43" s="28"/>
-      <c r="C43" s="28"/>
+      <c r="A43" s="37"/>
+      <c r="B43" s="27"/>
+      <c r="C43" s="27"/>
       <c r="D43" s="6" t="s">
         <v>17</v>
       </c>
@@ -4326,13 +4384,13 @@
       <c r="AN43" s="5"/>
       <c r="AO43" s="5"/>
       <c r="AP43" s="5"/>
-      <c r="AQ43" s="28"/>
-      <c r="AR43" s="38"/>
+      <c r="AQ43" s="53"/>
+      <c r="AR43" s="56"/>
     </row>
     <row r="44" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="35"/>
-      <c r="B44" s="28"/>
-      <c r="C44" s="28"/>
+      <c r="A44" s="37"/>
+      <c r="B44" s="27"/>
+      <c r="C44" s="27"/>
       <c r="D44" s="7" t="s">
         <v>18</v>
       </c>
@@ -4377,13 +4435,13 @@
       <c r="AN44" s="5"/>
       <c r="AO44" s="5"/>
       <c r="AP44" s="5"/>
-      <c r="AQ44" s="28"/>
-      <c r="AR44" s="38"/>
+      <c r="AQ44" s="53"/>
+      <c r="AR44" s="56"/>
     </row>
     <row r="45" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="35"/>
-      <c r="B45" s="28"/>
-      <c r="C45" s="28"/>
+      <c r="A45" s="37"/>
+      <c r="B45" s="27"/>
+      <c r="C45" s="27"/>
       <c r="D45" s="8" t="s">
         <v>19</v>
       </c>
@@ -4428,13 +4486,13 @@
       <c r="AN45" s="5"/>
       <c r="AO45" s="5"/>
       <c r="AP45" s="5"/>
-      <c r="AQ45" s="28"/>
-      <c r="AR45" s="38"/>
+      <c r="AQ45" s="53"/>
+      <c r="AR45" s="56"/>
     </row>
     <row r="46" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="35"/>
-      <c r="B46" s="28"/>
-      <c r="C46" s="28"/>
+      <c r="A46" s="37"/>
+      <c r="B46" s="27"/>
+      <c r="C46" s="27"/>
       <c r="D46" s="9" t="s">
         <v>20</v>
       </c>
@@ -4479,13 +4537,13 @@
       </c>
       <c r="AO46" s="5"/>
       <c r="AP46" s="5"/>
-      <c r="AQ46" s="28"/>
-      <c r="AR46" s="38"/>
+      <c r="AQ46" s="53"/>
+      <c r="AR46" s="56"/>
     </row>
     <row r="47" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="35"/>
-      <c r="B47" s="28"/>
-      <c r="C47" s="28"/>
+      <c r="A47" s="37"/>
+      <c r="B47" s="27"/>
+      <c r="C47" s="27"/>
       <c r="D47" s="9" t="s">
         <v>21</v>
       </c>
@@ -4530,13 +4588,13 @@
         <v>0</v>
       </c>
       <c r="AP47" s="5"/>
-      <c r="AQ47" s="28"/>
-      <c r="AR47" s="38"/>
+      <c r="AQ47" s="53"/>
+      <c r="AR47" s="56"/>
     </row>
     <row r="48" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="35"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
+      <c r="A48" s="37"/>
+      <c r="B48" s="28"/>
+      <c r="C48" s="28"/>
       <c r="D48" s="10" t="s">
         <v>22</v>
       </c>
@@ -4581,15 +4639,15 @@
         <f>SUM(E48:AI48)</f>
         <v>0</v>
       </c>
-      <c r="AQ48" s="29"/>
-      <c r="AR48" s="39"/>
+      <c r="AQ48" s="54"/>
+      <c r="AR48" s="57"/>
     </row>
     <row r="49" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="34"/>
-      <c r="B49" s="40">
+      <c r="A49" s="36"/>
+      <c r="B49" s="31">
         <v>7</v>
       </c>
-      <c r="C49" s="47" t="s">
+      <c r="C49" s="38" t="s">
         <v>15</v>
       </c>
       <c r="D49" s="3" t="s">
@@ -4636,16 +4694,16 @@
       <c r="AN49" s="5"/>
       <c r="AO49" s="5"/>
       <c r="AP49" s="5"/>
-      <c r="AQ49" s="27">
+      <c r="AQ49" s="52">
         <f>COUNTIF(E49:AI49,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR49" s="37"/>
+      <c r="AR49" s="55"/>
     </row>
     <row r="50" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="35"/>
-      <c r="B50" s="28"/>
-      <c r="C50" s="28"/>
+      <c r="A50" s="37"/>
+      <c r="B50" s="27"/>
+      <c r="C50" s="27"/>
       <c r="D50" s="6" t="s">
         <v>17</v>
       </c>
@@ -4690,13 +4748,13 @@
       <c r="AN50" s="5"/>
       <c r="AO50" s="5"/>
       <c r="AP50" s="5"/>
-      <c r="AQ50" s="28"/>
-      <c r="AR50" s="38"/>
+      <c r="AQ50" s="53"/>
+      <c r="AR50" s="56"/>
     </row>
     <row r="51" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="35"/>
-      <c r="B51" s="28"/>
-      <c r="C51" s="28"/>
+      <c r="A51" s="37"/>
+      <c r="B51" s="27"/>
+      <c r="C51" s="27"/>
       <c r="D51" s="7" t="s">
         <v>18</v>
       </c>
@@ -4741,13 +4799,13 @@
       <c r="AN51" s="5"/>
       <c r="AO51" s="5"/>
       <c r="AP51" s="5"/>
-      <c r="AQ51" s="28"/>
-      <c r="AR51" s="38"/>
+      <c r="AQ51" s="53"/>
+      <c r="AR51" s="56"/>
     </row>
     <row r="52" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="35"/>
-      <c r="B52" s="28"/>
-      <c r="C52" s="28"/>
+      <c r="A52" s="37"/>
+      <c r="B52" s="27"/>
+      <c r="C52" s="27"/>
       <c r="D52" s="8" t="s">
         <v>19</v>
       </c>
@@ -4792,13 +4850,13 @@
       <c r="AN52" s="5"/>
       <c r="AO52" s="5"/>
       <c r="AP52" s="5"/>
-      <c r="AQ52" s="28"/>
-      <c r="AR52" s="38"/>
+      <c r="AQ52" s="53"/>
+      <c r="AR52" s="56"/>
     </row>
     <row r="53" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="35"/>
-      <c r="B53" s="28"/>
-      <c r="C53" s="28"/>
+      <c r="A53" s="37"/>
+      <c r="B53" s="27"/>
+      <c r="C53" s="27"/>
       <c r="D53" s="9" t="s">
         <v>20</v>
       </c>
@@ -4843,13 +4901,13 @@
       </c>
       <c r="AO53" s="5"/>
       <c r="AP53" s="5"/>
-      <c r="AQ53" s="28"/>
-      <c r="AR53" s="38"/>
+      <c r="AQ53" s="53"/>
+      <c r="AR53" s="56"/>
     </row>
     <row r="54" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="35"/>
-      <c r="B54" s="28"/>
-      <c r="C54" s="28"/>
+      <c r="A54" s="37"/>
+      <c r="B54" s="27"/>
+      <c r="C54" s="27"/>
       <c r="D54" s="9" t="s">
         <v>21</v>
       </c>
@@ -4894,13 +4952,13 @@
         <v>0</v>
       </c>
       <c r="AP54" s="5"/>
-      <c r="AQ54" s="28"/>
-      <c r="AR54" s="38"/>
+      <c r="AQ54" s="53"/>
+      <c r="AR54" s="56"/>
     </row>
     <row r="55" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="35"/>
-      <c r="B55" s="29"/>
-      <c r="C55" s="29"/>
+      <c r="A55" s="37"/>
+      <c r="B55" s="28"/>
+      <c r="C55" s="28"/>
       <c r="D55" s="10" t="s">
         <v>22</v>
       </c>
@@ -4945,15 +5003,15 @@
         <f>SUM(E55:AI55)</f>
         <v>0</v>
       </c>
-      <c r="AQ55" s="29"/>
-      <c r="AR55" s="39"/>
+      <c r="AQ55" s="54"/>
+      <c r="AR55" s="57"/>
     </row>
     <row r="56" spans="1:44" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="34"/>
-      <c r="B56" s="40">
+      <c r="A56" s="36"/>
+      <c r="B56" s="31">
         <v>8</v>
       </c>
-      <c r="C56" s="47" t="s">
+      <c r="C56" s="38" t="s">
         <v>15</v>
       </c>
       <c r="D56" s="3" t="s">
@@ -5000,16 +5058,16 @@
       <c r="AN56" s="5"/>
       <c r="AO56" s="5"/>
       <c r="AP56" s="5"/>
-      <c r="AQ56" s="27">
+      <c r="AQ56" s="52">
         <f>COUNTIF(E56:AI56,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR56" s="37"/>
+      <c r="AR56" s="55"/>
     </row>
     <row r="57" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="35"/>
-      <c r="B57" s="28"/>
-      <c r="C57" s="28"/>
+      <c r="A57" s="37"/>
+      <c r="B57" s="27"/>
+      <c r="C57" s="27"/>
       <c r="D57" s="6" t="s">
         <v>17</v>
       </c>
@@ -5054,13 +5112,13 @@
       <c r="AN57" s="5"/>
       <c r="AO57" s="5"/>
       <c r="AP57" s="5"/>
-      <c r="AQ57" s="28"/>
-      <c r="AR57" s="38"/>
+      <c r="AQ57" s="53"/>
+      <c r="AR57" s="56"/>
     </row>
     <row r="58" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="35"/>
-      <c r="B58" s="28"/>
-      <c r="C58" s="28"/>
+      <c r="A58" s="37"/>
+      <c r="B58" s="27"/>
+      <c r="C58" s="27"/>
       <c r="D58" s="7" t="s">
         <v>18</v>
       </c>
@@ -5105,13 +5163,13 @@
       <c r="AN58" s="5"/>
       <c r="AO58" s="5"/>
       <c r="AP58" s="5"/>
-      <c r="AQ58" s="28"/>
-      <c r="AR58" s="38"/>
+      <c r="AQ58" s="53"/>
+      <c r="AR58" s="56"/>
     </row>
     <row r="59" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="35"/>
-      <c r="B59" s="28"/>
-      <c r="C59" s="28"/>
+      <c r="A59" s="37"/>
+      <c r="B59" s="27"/>
+      <c r="C59" s="27"/>
       <c r="D59" s="8" t="s">
         <v>19</v>
       </c>
@@ -5156,13 +5214,13 @@
       <c r="AN59" s="5"/>
       <c r="AO59" s="5"/>
       <c r="AP59" s="5"/>
-      <c r="AQ59" s="28"/>
-      <c r="AR59" s="38"/>
+      <c r="AQ59" s="53"/>
+      <c r="AR59" s="56"/>
     </row>
     <row r="60" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="35"/>
-      <c r="B60" s="28"/>
-      <c r="C60" s="28"/>
+      <c r="A60" s="37"/>
+      <c r="B60" s="27"/>
+      <c r="C60" s="27"/>
       <c r="D60" s="9" t="s">
         <v>20</v>
       </c>
@@ -5207,13 +5265,13 @@
       </c>
       <c r="AO60" s="5"/>
       <c r="AP60" s="5"/>
-      <c r="AQ60" s="28"/>
-      <c r="AR60" s="38"/>
+      <c r="AQ60" s="53"/>
+      <c r="AR60" s="56"/>
     </row>
     <row r="61" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="35"/>
-      <c r="B61" s="28"/>
-      <c r="C61" s="28"/>
+      <c r="A61" s="37"/>
+      <c r="B61" s="27"/>
+      <c r="C61" s="27"/>
       <c r="D61" s="9" t="s">
         <v>21</v>
       </c>
@@ -5258,13 +5316,13 @@
         <v>0</v>
       </c>
       <c r="AP61" s="5"/>
-      <c r="AQ61" s="28"/>
-      <c r="AR61" s="38"/>
+      <c r="AQ61" s="53"/>
+      <c r="AR61" s="56"/>
     </row>
     <row r="62" spans="1:44" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="35"/>
-      <c r="B62" s="29"/>
-      <c r="C62" s="29"/>
+      <c r="A62" s="37"/>
+      <c r="B62" s="28"/>
+      <c r="C62" s="28"/>
       <c r="D62" s="10" t="s">
         <v>22</v>
       </c>
@@ -5309,49 +5367,49 @@
         <f>SUM(E62:AI62)</f>
         <v>0</v>
       </c>
-      <c r="AQ62" s="29"/>
-      <c r="AR62" s="39"/>
+      <c r="AQ62" s="54"/>
+      <c r="AR62" s="57"/>
     </row>
     <row r="63" spans="1:44" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="14"/>
-      <c r="B63" s="53" t="s">
+      <c r="B63" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="C63" s="54"/>
-      <c r="D63" s="55"/>
-      <c r="E63" s="49" t="s">
+      <c r="C63" s="33"/>
+      <c r="D63" s="34"/>
+      <c r="E63" s="58" t="s">
         <v>26</v>
       </c>
-      <c r="F63" s="50"/>
-      <c r="G63" s="50"/>
-      <c r="H63" s="50"/>
-      <c r="I63" s="50"/>
-      <c r="J63" s="50"/>
-      <c r="K63" s="50"/>
-      <c r="L63" s="50"/>
-      <c r="M63" s="50"/>
-      <c r="N63" s="50"/>
-      <c r="O63" s="50"/>
-      <c r="P63" s="50"/>
-      <c r="Q63" s="50"/>
-      <c r="R63" s="50"/>
-      <c r="S63" s="50"/>
-      <c r="T63" s="50"/>
-      <c r="U63" s="50"/>
-      <c r="V63" s="50"/>
-      <c r="W63" s="50"/>
-      <c r="X63" s="50"/>
-      <c r="Y63" s="50"/>
-      <c r="Z63" s="50"/>
-      <c r="AA63" s="50"/>
-      <c r="AB63" s="50"/>
-      <c r="AC63" s="50"/>
-      <c r="AD63" s="50"/>
-      <c r="AE63" s="50"/>
-      <c r="AF63" s="50"/>
-      <c r="AG63" s="50"/>
-      <c r="AH63" s="50"/>
-      <c r="AI63" s="51"/>
+      <c r="F63" s="59"/>
+      <c r="G63" s="59"/>
+      <c r="H63" s="59"/>
+      <c r="I63" s="59"/>
+      <c r="J63" s="59"/>
+      <c r="K63" s="59"/>
+      <c r="L63" s="59"/>
+      <c r="M63" s="59"/>
+      <c r="N63" s="59"/>
+      <c r="O63" s="59"/>
+      <c r="P63" s="59"/>
+      <c r="Q63" s="59"/>
+      <c r="R63" s="59"/>
+      <c r="S63" s="59"/>
+      <c r="T63" s="59"/>
+      <c r="U63" s="59"/>
+      <c r="V63" s="59"/>
+      <c r="W63" s="59"/>
+      <c r="X63" s="59"/>
+      <c r="Y63" s="59"/>
+      <c r="Z63" s="59"/>
+      <c r="AA63" s="59"/>
+      <c r="AB63" s="59"/>
+      <c r="AC63" s="59"/>
+      <c r="AD63" s="59"/>
+      <c r="AE63" s="59"/>
+      <c r="AF63" s="59"/>
+      <c r="AG63" s="59"/>
+      <c r="AH63" s="59"/>
+      <c r="AI63" s="60"/>
       <c r="AJ63" s="13">
         <f t="shared" ref="AJ63:AP63" si="0">SUM(AJ7:AJ55)</f>
         <v>0</v>
@@ -5380,14 +5438,66 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AQ63" s="56" t="s">
+      <c r="AQ63" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="AR63" s="57"/>
+      <c r="AR63" s="51"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="7l2H75vtBAPXuNk3rjxQR/apet362+8gn6pMMFGEbdiJmbGMaSswqqK23Ij0Bor2UOmWYi2XHJRMjhEivPTH3A==" saltValue="tebfZusMGaVWgzqHUaB6Xg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="+ZrADsvjlmIB2UyRAwEHEZ36xwZytVzRwxYKLGDgthMmP2cYinxPW7EpXBzkqA+RbpXOv1Qk11rSa9ksNVGMYA==" saltValue="b6DZVSZt3Hjg6M77pxnAjw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="68">
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="Q2:W2"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="M3:P3"/>
+    <mergeCell ref="AP5:AP6"/>
+    <mergeCell ref="AQ21:AQ27"/>
+    <mergeCell ref="E1:V1"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="E2:L2"/>
+    <mergeCell ref="E4:AQ4"/>
+    <mergeCell ref="AQ5:AQ6"/>
+    <mergeCell ref="X2:AB2"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="A28:A34"/>
+    <mergeCell ref="A14:A20"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="AR42:AR48"/>
+    <mergeCell ref="AQ28:AQ34"/>
+    <mergeCell ref="A35:A41"/>
+    <mergeCell ref="AJ5:AJ6"/>
+    <mergeCell ref="B35:B41"/>
+    <mergeCell ref="AR28:AR34"/>
+    <mergeCell ref="B28:B34"/>
+    <mergeCell ref="A21:A27"/>
+    <mergeCell ref="AQ14:AQ20"/>
+    <mergeCell ref="AK5:AK6"/>
+    <mergeCell ref="AM5:AM6"/>
+    <mergeCell ref="AL5:AL6"/>
+    <mergeCell ref="AQ35:AQ41"/>
+    <mergeCell ref="C7:C13"/>
+    <mergeCell ref="B7:B13"/>
+    <mergeCell ref="AR7:AR13"/>
+    <mergeCell ref="B21:B27"/>
+    <mergeCell ref="AQ7:AQ13"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="AR5:AR6"/>
+    <mergeCell ref="AO5:AO6"/>
+    <mergeCell ref="C21:C27"/>
+    <mergeCell ref="AN5:AN6"/>
+    <mergeCell ref="AR21:AR27"/>
+    <mergeCell ref="B56:B62"/>
+    <mergeCell ref="AR56:AR62"/>
+    <mergeCell ref="A49:A55"/>
+    <mergeCell ref="C42:C48"/>
+    <mergeCell ref="C49:C55"/>
+    <mergeCell ref="AR49:AR55"/>
+    <mergeCell ref="C56:C62"/>
+    <mergeCell ref="A56:A62"/>
+    <mergeCell ref="A42:A48"/>
+    <mergeCell ref="AQ42:AQ48"/>
+    <mergeCell ref="B49:B55"/>
     <mergeCell ref="B1:D2"/>
     <mergeCell ref="AR14:AR20"/>
     <mergeCell ref="I3:L3"/>
@@ -5404,58 +5514,6 @@
     <mergeCell ref="C28:C34"/>
     <mergeCell ref="AQ63:AR63"/>
     <mergeCell ref="E3:H3"/>
-    <mergeCell ref="B56:B62"/>
-    <mergeCell ref="AR56:AR62"/>
-    <mergeCell ref="A49:A55"/>
-    <mergeCell ref="C42:C48"/>
-    <mergeCell ref="C49:C55"/>
-    <mergeCell ref="AR49:AR55"/>
-    <mergeCell ref="C56:C62"/>
-    <mergeCell ref="A56:A62"/>
-    <mergeCell ref="A42:A48"/>
-    <mergeCell ref="AQ42:AQ48"/>
-    <mergeCell ref="B49:B55"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="AR5:AR6"/>
-    <mergeCell ref="AO5:AO6"/>
-    <mergeCell ref="C21:C27"/>
-    <mergeCell ref="AN5:AN6"/>
-    <mergeCell ref="AR21:AR27"/>
-    <mergeCell ref="AQ35:AQ41"/>
-    <mergeCell ref="C7:C13"/>
-    <mergeCell ref="B7:B13"/>
-    <mergeCell ref="AR7:AR13"/>
-    <mergeCell ref="B21:B27"/>
-    <mergeCell ref="AQ7:AQ13"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="A28:A34"/>
-    <mergeCell ref="A14:A20"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="AR42:AR48"/>
-    <mergeCell ref="AQ28:AQ34"/>
-    <mergeCell ref="A35:A41"/>
-    <mergeCell ref="AJ5:AJ6"/>
-    <mergeCell ref="B35:B41"/>
-    <mergeCell ref="AR28:AR34"/>
-    <mergeCell ref="B28:B34"/>
-    <mergeCell ref="A21:A27"/>
-    <mergeCell ref="AQ14:AQ20"/>
-    <mergeCell ref="AK5:AK6"/>
-    <mergeCell ref="AM5:AM6"/>
-    <mergeCell ref="AL5:AL6"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="M3:P3"/>
-    <mergeCell ref="AP5:AP6"/>
-    <mergeCell ref="AQ21:AQ27"/>
-    <mergeCell ref="E1:V1"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="P2:W2"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="E2:L2"/>
-    <mergeCell ref="X2:Z2"/>
-    <mergeCell ref="E4:AQ4"/>
-    <mergeCell ref="AQ5:AQ6"/>
   </mergeCells>
   <conditionalFormatting sqref="E6">
     <cfRule type="expression" dxfId="61" priority="188">

--- a/public/moduli/FoglioPresenze_StudioBaiocco.xlsx
+++ b/public/moduli/FoglioPresenze_StudioBaiocco.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Desktop/sito_mamma/public/moduli/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0E9D341-80FB-5F44-B068-12227D44736B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3141EE94-41B7-F546-A5BB-AE5F9742F4B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="660" windowWidth="30240" windowHeight="17680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -219,13 +219,6 @@
     </font>
     <font>
       <b/>
-      <sz val="22"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
       <color theme="0"/>
       <name val="Calibri"/>
@@ -266,6 +259,13 @@
       <b/>
       <sz val="22"/>
       <color rgb="FF1A2B4A"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -656,9 +656,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -728,59 +728,6 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -793,20 +740,17 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -817,6 +761,30 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="9" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="justify"/>
       <protection locked="0"/>
@@ -829,35 +797,69 @@
       <alignment horizontal="left" vertical="justify"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="9" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="justify"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1602,16 +1604,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>31</xdr:col>
-      <xdr:colOff>88900</xdr:colOff>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>53894</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>12701</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>42</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>203200</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>46385</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1634,8 +1636,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12153900" y="38100"/>
-          <a:ext cx="5067300" cy="1240185"/>
+          <a:off x="13439694" y="12701"/>
+          <a:ext cx="3476706" cy="850899"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1657,8 +1659,8 @@
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>54574</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>369186</xdr:rowOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>242186</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1980,42 +1982,38 @@
     <col min="2" max="2" width="4" customWidth="1"/>
     <col min="3" max="3" width="18.6640625" customWidth="1"/>
     <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="14" width="3.83203125" customWidth="1"/>
-    <col min="15" max="15" width="2.83203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="25" width="3.83203125" customWidth="1"/>
-    <col min="26" max="26" width="2.83203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="35" width="3.83203125" customWidth="1"/>
+    <col min="5" max="35" width="3.83203125" customWidth="1"/>
     <col min="36" max="40" width="7" customWidth="1"/>
     <col min="42" max="42" width="8.33203125" customWidth="1"/>
     <col min="43" max="43" width="6" customWidth="1"/>
     <col min="44" max="44" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:44" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14"/>
-      <c r="B1" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="25"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="25"/>
-      <c r="V1" s="25"/>
+      <c r="B1" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
+      <c r="V1" s="26"/>
       <c r="W1" s="15"/>
       <c r="X1" s="15"/>
       <c r="Y1" s="15"/>
@@ -2039,43 +2037,43 @@
       <c r="AQ1" s="15"/>
       <c r="AR1" s="15"/>
     </row>
-    <row r="2" spans="1:44" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:44" ht="29" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="65" t="s">
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="48">
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
+      <c r="J2" s="67"/>
+      <c r="K2" s="67"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="23">
         <v>3</v>
       </c>
-      <c r="N2" s="49"/>
-      <c r="O2" s="49"/>
-      <c r="P2" s="50"/>
-      <c r="Q2" s="67" t="s">
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="25"/>
+      <c r="Q2" s="66" t="s">
         <v>2</v>
       </c>
-      <c r="R2" s="65"/>
-      <c r="S2" s="65"/>
-      <c r="T2" s="65"/>
-      <c r="U2" s="65"/>
-      <c r="V2" s="65"/>
-      <c r="W2" s="43"/>
-      <c r="X2" s="45">
+      <c r="R2" s="67"/>
+      <c r="S2" s="67"/>
+      <c r="T2" s="67"/>
+      <c r="U2" s="67"/>
+      <c r="V2" s="67"/>
+      <c r="W2" s="68"/>
+      <c r="X2" s="34">
         <v>2026</v>
       </c>
-      <c r="Y2" s="46"/>
-      <c r="Z2" s="46"/>
-      <c r="AA2" s="46"/>
-      <c r="AB2" s="47"/>
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="35"/>
+      <c r="AA2" s="35"/>
+      <c r="AB2" s="36"/>
       <c r="AC2" s="15"/>
       <c r="AD2" s="15"/>
       <c r="AE2" s="15"/>
@@ -2093,31 +2091,31 @@
       <c r="AQ2" s="15"/>
       <c r="AR2" s="15"/>
     </row>
-    <row r="3" spans="1:44" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:44" ht="19" x14ac:dyDescent="0.2">
       <c r="A3" s="14"/>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="25"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="25"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="66"/>
-      <c r="N3" s="66"/>
-      <c r="O3" s="66"/>
-      <c r="P3" s="66"/>
-      <c r="Q3" s="25"/>
-      <c r="R3" s="25"/>
-      <c r="S3" s="25"/>
-      <c r="T3" s="25"/>
-      <c r="U3" s="25"/>
-      <c r="V3" s="25"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="26"/>
+      <c r="U3" s="26"/>
+      <c r="V3" s="26"/>
       <c r="W3" s="15"/>
       <c r="X3" s="15"/>
       <c r="Y3" s="15"/>
@@ -2141,63 +2139,63 @@
       <c r="AQ3" s="15"/>
       <c r="AR3" s="15"/>
     </row>
-    <row r="4" spans="1:44" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:44" ht="24" x14ac:dyDescent="0.2">
       <c r="A4" s="14"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="44" t="s">
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="44"/>
-      <c r="O4" s="44"/>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="44"/>
-      <c r="S4" s="44"/>
-      <c r="T4" s="44"/>
-      <c r="U4" s="44"/>
-      <c r="V4" s="44"/>
-      <c r="W4" s="44"/>
-      <c r="X4" s="44"/>
-      <c r="Y4" s="44"/>
-      <c r="Z4" s="44"/>
-      <c r="AA4" s="44"/>
-      <c r="AB4" s="44"/>
-      <c r="AC4" s="44"/>
-      <c r="AD4" s="44"/>
-      <c r="AE4" s="44"/>
-      <c r="AF4" s="44"/>
-      <c r="AG4" s="44"/>
-      <c r="AH4" s="44"/>
-      <c r="AI4" s="44"/>
-      <c r="AJ4" s="44"/>
-      <c r="AK4" s="44"/>
-      <c r="AL4" s="44"/>
-      <c r="AM4" s="44"/>
-      <c r="AN4" s="44"/>
-      <c r="AO4" s="44"/>
-      <c r="AP4" s="44"/>
-      <c r="AQ4" s="44"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="33"/>
+      <c r="O4" s="33"/>
+      <c r="P4" s="33"/>
+      <c r="Q4" s="33"/>
+      <c r="R4" s="33"/>
+      <c r="S4" s="33"/>
+      <c r="T4" s="33"/>
+      <c r="U4" s="33"/>
+      <c r="V4" s="33"/>
+      <c r="W4" s="33"/>
+      <c r="X4" s="33"/>
+      <c r="Y4" s="33"/>
+      <c r="Z4" s="33"/>
+      <c r="AA4" s="33"/>
+      <c r="AB4" s="33"/>
+      <c r="AC4" s="33"/>
+      <c r="AD4" s="33"/>
+      <c r="AE4" s="33"/>
+      <c r="AF4" s="33"/>
+      <c r="AG4" s="33"/>
+      <c r="AH4" s="33"/>
+      <c r="AI4" s="33"/>
+      <c r="AJ4" s="33"/>
+      <c r="AK4" s="33"/>
+      <c r="AL4" s="33"/>
+      <c r="AM4" s="33"/>
+      <c r="AN4" s="33"/>
+      <c r="AO4" s="33"/>
+      <c r="AP4" s="33"/>
+      <c r="AQ4" s="33"/>
       <c r="AR4" s="16"/>
     </row>
     <row r="5" spans="1:44" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14"/>
-      <c r="B5" s="39" t="s">
+      <c r="B5" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="40"/>
+      <c r="D5" s="52"/>
       <c r="E5" s="1">
         <v>1</v>
       </c>
@@ -2291,39 +2289,39 @@
       <c r="AI5" s="1">
         <v>31</v>
       </c>
-      <c r="AJ5" s="61" t="s">
+      <c r="AJ5" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="AK5" s="61" t="s">
+      <c r="AK5" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="AL5" s="61" t="s">
+      <c r="AL5" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="AM5" s="61" t="s">
+      <c r="AM5" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="AN5" s="61" t="s">
+      <c r="AN5" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="AO5" s="61" t="s">
+      <c r="AO5" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="AP5" s="61" t="s">
+      <c r="AP5" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="AQ5" s="61" t="s">
+      <c r="AQ5" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="AR5" s="61" t="s">
+      <c r="AR5" s="28" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="14"/>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
       <c r="E6" s="2" t="str">
         <f>IFERROR(IF(1&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,1),2),"L","M","M","G","V","S","D")),"")</f>
         <v>D</v>
@@ -2448,22 +2446,22 @@
         <f>IFERROR(IF(31&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,31),2),"L","M","M","G","V","S","D")),"")</f>
         <v>M</v>
       </c>
-      <c r="AJ6" s="62"/>
-      <c r="AK6" s="62"/>
-      <c r="AL6" s="62"/>
-      <c r="AM6" s="62"/>
-      <c r="AN6" s="62"/>
-      <c r="AO6" s="62"/>
-      <c r="AP6" s="62"/>
-      <c r="AQ6" s="62"/>
-      <c r="AR6" s="62"/>
+      <c r="AJ6" s="29"/>
+      <c r="AK6" s="29"/>
+      <c r="AL6" s="29"/>
+      <c r="AM6" s="29"/>
+      <c r="AN6" s="29"/>
+      <c r="AO6" s="29"/>
+      <c r="AP6" s="29"/>
+      <c r="AQ6" s="29"/>
+      <c r="AR6" s="29"/>
     </row>
     <row r="7" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="36"/>
-      <c r="B7" s="41">
+      <c r="A7" s="37"/>
+      <c r="B7" s="47">
         <v>1</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="63" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -2510,16 +2508,16 @@
       <c r="AN7" s="5"/>
       <c r="AO7" s="5"/>
       <c r="AP7" s="5"/>
-      <c r="AQ7" s="63">
+      <c r="AQ7" s="49">
         <f>COUNTIF(E7:AI7,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR7" s="64"/>
+      <c r="AR7" s="48"/>
     </row>
     <row r="8" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="37"/>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
+      <c r="A8" s="38"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="64"/>
       <c r="D8" s="6" t="s">
         <v>17</v>
       </c>
@@ -2564,13 +2562,13 @@
       <c r="AN8" s="5"/>
       <c r="AO8" s="5"/>
       <c r="AP8" s="5"/>
-      <c r="AQ8" s="53"/>
-      <c r="AR8" s="56"/>
+      <c r="AQ8" s="31"/>
+      <c r="AR8" s="42"/>
     </row>
     <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="37"/>
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
+      <c r="A9" s="38"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="64"/>
       <c r="D9" s="7" t="s">
         <v>18</v>
       </c>
@@ -2615,13 +2613,13 @@
       <c r="AN9" s="5"/>
       <c r="AO9" s="5"/>
       <c r="AP9" s="5"/>
-      <c r="AQ9" s="53"/>
-      <c r="AR9" s="56"/>
+      <c r="AQ9" s="31"/>
+      <c r="AR9" s="42"/>
     </row>
     <row r="10" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="37"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
+      <c r="A10" s="38"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="64"/>
       <c r="D10" s="8" t="s">
         <v>19</v>
       </c>
@@ -2666,13 +2664,13 @@
       <c r="AN10" s="5"/>
       <c r="AO10" s="5"/>
       <c r="AP10" s="5"/>
-      <c r="AQ10" s="53"/>
-      <c r="AR10" s="56"/>
+      <c r="AQ10" s="31"/>
+      <c r="AR10" s="42"/>
     </row>
     <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="37"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
+      <c r="A11" s="38"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="64"/>
       <c r="D11" s="9" t="s">
         <v>20</v>
       </c>
@@ -2717,13 +2715,13 @@
       </c>
       <c r="AO11" s="5"/>
       <c r="AP11" s="5"/>
-      <c r="AQ11" s="53"/>
-      <c r="AR11" s="56"/>
+      <c r="AQ11" s="31"/>
+      <c r="AR11" s="42"/>
     </row>
     <row r="12" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="37"/>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
+      <c r="A12" s="38"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="64"/>
       <c r="D12" s="9" t="s">
         <v>21</v>
       </c>
@@ -2768,13 +2766,13 @@
         <v>0</v>
       </c>
       <c r="AP12" s="5"/>
-      <c r="AQ12" s="53"/>
-      <c r="AR12" s="56"/>
+      <c r="AQ12" s="31"/>
+      <c r="AR12" s="42"/>
     </row>
     <row r="13" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="37"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
+      <c r="A13" s="38"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="65"/>
       <c r="D13" s="10" t="s">
         <v>22</v>
       </c>
@@ -2819,15 +2817,15 @@
         <f>SUM(E13:AI13)</f>
         <v>0</v>
       </c>
-      <c r="AQ13" s="54"/>
-      <c r="AR13" s="57"/>
+      <c r="AQ13" s="32"/>
+      <c r="AR13" s="43"/>
     </row>
     <row r="14" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="36"/>
-      <c r="B14" s="31">
+      <c r="A14" s="37"/>
+      <c r="B14" s="44">
         <v>2</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="63" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -2874,16 +2872,16 @@
       <c r="AN14" s="5"/>
       <c r="AO14" s="5"/>
       <c r="AP14" s="5"/>
-      <c r="AQ14" s="52">
+      <c r="AQ14" s="30">
         <f>COUNTIF(E14:AI14,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR14" s="55"/>
+      <c r="AR14" s="41"/>
     </row>
     <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="37"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
+      <c r="A15" s="38"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="64"/>
       <c r="D15" s="6" t="s">
         <v>17</v>
       </c>
@@ -2928,13 +2926,13 @@
       <c r="AN15" s="5"/>
       <c r="AO15" s="5"/>
       <c r="AP15" s="5"/>
-      <c r="AQ15" s="53"/>
-      <c r="AR15" s="56"/>
+      <c r="AQ15" s="31"/>
+      <c r="AR15" s="42"/>
     </row>
     <row r="16" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="37"/>
-      <c r="B16" s="27"/>
-      <c r="C16" s="27"/>
+      <c r="A16" s="38"/>
+      <c r="B16" s="45"/>
+      <c r="C16" s="64"/>
       <c r="D16" s="7" t="s">
         <v>18</v>
       </c>
@@ -2979,13 +2977,13 @@
       <c r="AN16" s="5"/>
       <c r="AO16" s="5"/>
       <c r="AP16" s="5"/>
-      <c r="AQ16" s="53"/>
-      <c r="AR16" s="56"/>
+      <c r="AQ16" s="31"/>
+      <c r="AR16" s="42"/>
     </row>
     <row r="17" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="37"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="64"/>
       <c r="D17" s="8" t="s">
         <v>19</v>
       </c>
@@ -3030,13 +3028,13 @@
       <c r="AN17" s="5"/>
       <c r="AO17" s="5"/>
       <c r="AP17" s="5"/>
-      <c r="AQ17" s="53"/>
-      <c r="AR17" s="56"/>
+      <c r="AQ17" s="31"/>
+      <c r="AR17" s="42"/>
     </row>
     <row r="18" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="37"/>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
+      <c r="A18" s="38"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="64"/>
       <c r="D18" s="9" t="s">
         <v>20</v>
       </c>
@@ -3081,13 +3079,13 @@
       </c>
       <c r="AO18" s="5"/>
       <c r="AP18" s="5"/>
-      <c r="AQ18" s="53"/>
-      <c r="AR18" s="56"/>
+      <c r="AQ18" s="31"/>
+      <c r="AR18" s="42"/>
     </row>
     <row r="19" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="37"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="27"/>
+      <c r="A19" s="38"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="64"/>
       <c r="D19" s="9" t="s">
         <v>21</v>
       </c>
@@ -3132,13 +3130,13 @@
         <v>0</v>
       </c>
       <c r="AP19" s="5"/>
-      <c r="AQ19" s="53"/>
-      <c r="AR19" s="56"/>
+      <c r="AQ19" s="31"/>
+      <c r="AR19" s="42"/>
     </row>
     <row r="20" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="37"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
+      <c r="A20" s="38"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="65"/>
       <c r="D20" s="10" t="s">
         <v>22</v>
       </c>
@@ -3183,15 +3181,15 @@
         <f>SUM(E20:AI20)</f>
         <v>0</v>
       </c>
-      <c r="AQ20" s="54"/>
-      <c r="AR20" s="57"/>
+      <c r="AQ20" s="32"/>
+      <c r="AR20" s="43"/>
     </row>
     <row r="21" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="36"/>
-      <c r="B21" s="31">
+      <c r="A21" s="37"/>
+      <c r="B21" s="44">
         <v>3</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C21" s="63" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3" t="s">
@@ -3238,16 +3236,16 @@
       <c r="AN21" s="5"/>
       <c r="AO21" s="5"/>
       <c r="AP21" s="5"/>
-      <c r="AQ21" s="52">
+      <c r="AQ21" s="30">
         <f>COUNTIF(E21:AI21,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR21" s="55"/>
+      <c r="AR21" s="41"/>
     </row>
     <row r="22" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="37"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
+      <c r="A22" s="38"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="64"/>
       <c r="D22" s="6" t="s">
         <v>17</v>
       </c>
@@ -3292,13 +3290,13 @@
       <c r="AN22" s="5"/>
       <c r="AO22" s="5"/>
       <c r="AP22" s="5"/>
-      <c r="AQ22" s="53"/>
-      <c r="AR22" s="56"/>
+      <c r="AQ22" s="31"/>
+      <c r="AR22" s="42"/>
     </row>
     <row r="23" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="37"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
+      <c r="A23" s="38"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="64"/>
       <c r="D23" s="7" t="s">
         <v>18</v>
       </c>
@@ -3343,13 +3341,13 @@
       <c r="AN23" s="5"/>
       <c r="AO23" s="5"/>
       <c r="AP23" s="5"/>
-      <c r="AQ23" s="53"/>
-      <c r="AR23" s="56"/>
+      <c r="AQ23" s="31"/>
+      <c r="AR23" s="42"/>
     </row>
     <row r="24" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="37"/>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
+      <c r="A24" s="38"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="64"/>
       <c r="D24" s="8" t="s">
         <v>19</v>
       </c>
@@ -3394,13 +3392,13 @@
       <c r="AN24" s="5"/>
       <c r="AO24" s="5"/>
       <c r="AP24" s="5"/>
-      <c r="AQ24" s="53"/>
-      <c r="AR24" s="56"/>
+      <c r="AQ24" s="31"/>
+      <c r="AR24" s="42"/>
     </row>
     <row r="25" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="37"/>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
+      <c r="A25" s="38"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="64"/>
       <c r="D25" s="9" t="s">
         <v>20</v>
       </c>
@@ -3445,13 +3443,13 @@
       </c>
       <c r="AO25" s="5"/>
       <c r="AP25" s="5"/>
-      <c r="AQ25" s="53"/>
-      <c r="AR25" s="56"/>
+      <c r="AQ25" s="31"/>
+      <c r="AR25" s="42"/>
     </row>
     <row r="26" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="37"/>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
+      <c r="A26" s="38"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="64"/>
       <c r="D26" s="9" t="s">
         <v>21</v>
       </c>
@@ -3496,13 +3494,13 @@
         <v>0</v>
       </c>
       <c r="AP26" s="5"/>
-      <c r="AQ26" s="53"/>
-      <c r="AR26" s="56"/>
+      <c r="AQ26" s="31"/>
+      <c r="AR26" s="42"/>
     </row>
     <row r="27" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="37"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
+      <c r="A27" s="38"/>
+      <c r="B27" s="46"/>
+      <c r="C27" s="65"/>
       <c r="D27" s="10" t="s">
         <v>22</v>
       </c>
@@ -3547,15 +3545,15 @@
         <f>SUM(E27:AI27)</f>
         <v>0</v>
       </c>
-      <c r="AQ27" s="54"/>
-      <c r="AR27" s="57"/>
+      <c r="AQ27" s="32"/>
+      <c r="AR27" s="43"/>
     </row>
     <row r="28" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="36"/>
-      <c r="B28" s="31">
+      <c r="A28" s="37"/>
+      <c r="B28" s="44">
         <v>4</v>
       </c>
-      <c r="C28" s="26" t="s">
+      <c r="C28" s="63" t="s">
         <v>15</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -3602,16 +3600,16 @@
       <c r="AN28" s="5"/>
       <c r="AO28" s="5"/>
       <c r="AP28" s="5"/>
-      <c r="AQ28" s="52">
+      <c r="AQ28" s="30">
         <f>COUNTIF(E28:AI28,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR28" s="55"/>
+      <c r="AR28" s="41"/>
     </row>
     <row r="29" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="37"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
+      <c r="A29" s="38"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="64"/>
       <c r="D29" s="6" t="s">
         <v>17</v>
       </c>
@@ -3656,13 +3654,13 @@
       <c r="AN29" s="5"/>
       <c r="AO29" s="5"/>
       <c r="AP29" s="5"/>
-      <c r="AQ29" s="53"/>
-      <c r="AR29" s="56"/>
+      <c r="AQ29" s="31"/>
+      <c r="AR29" s="42"/>
     </row>
     <row r="30" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="37"/>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
+      <c r="A30" s="38"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="64"/>
       <c r="D30" s="7" t="s">
         <v>18</v>
       </c>
@@ -3707,13 +3705,13 @@
       <c r="AN30" s="5"/>
       <c r="AO30" s="5"/>
       <c r="AP30" s="5"/>
-      <c r="AQ30" s="53"/>
-      <c r="AR30" s="56"/>
+      <c r="AQ30" s="31"/>
+      <c r="AR30" s="42"/>
     </row>
     <row r="31" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="37"/>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
+      <c r="A31" s="38"/>
+      <c r="B31" s="45"/>
+      <c r="C31" s="64"/>
       <c r="D31" s="8" t="s">
         <v>19</v>
       </c>
@@ -3758,13 +3756,13 @@
       <c r="AN31" s="5"/>
       <c r="AO31" s="5"/>
       <c r="AP31" s="5"/>
-      <c r="AQ31" s="53"/>
-      <c r="AR31" s="56"/>
+      <c r="AQ31" s="31"/>
+      <c r="AR31" s="42"/>
     </row>
     <row r="32" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="37"/>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
+      <c r="A32" s="38"/>
+      <c r="B32" s="45"/>
+      <c r="C32" s="64"/>
       <c r="D32" s="9" t="s">
         <v>20</v>
       </c>
@@ -3809,13 +3807,13 @@
       </c>
       <c r="AO32" s="5"/>
       <c r="AP32" s="5"/>
-      <c r="AQ32" s="53"/>
-      <c r="AR32" s="56"/>
+      <c r="AQ32" s="31"/>
+      <c r="AR32" s="42"/>
     </row>
     <row r="33" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="37"/>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
+      <c r="A33" s="38"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="64"/>
       <c r="D33" s="9" t="s">
         <v>21</v>
       </c>
@@ -3860,13 +3858,13 @@
         <v>0</v>
       </c>
       <c r="AP33" s="5"/>
-      <c r="AQ33" s="53"/>
-      <c r="AR33" s="56"/>
+      <c r="AQ33" s="31"/>
+      <c r="AR33" s="42"/>
     </row>
     <row r="34" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="37"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
+      <c r="A34" s="38"/>
+      <c r="B34" s="46"/>
+      <c r="C34" s="65"/>
       <c r="D34" s="10" t="s">
         <v>22</v>
       </c>
@@ -3911,15 +3909,15 @@
         <f>SUM(E34:AI34)</f>
         <v>0</v>
       </c>
-      <c r="AQ34" s="54"/>
-      <c r="AR34" s="57"/>
+      <c r="AQ34" s="32"/>
+      <c r="AR34" s="43"/>
     </row>
     <row r="35" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="36"/>
-      <c r="B35" s="31">
+      <c r="A35" s="37"/>
+      <c r="B35" s="44">
         <v>5</v>
       </c>
-      <c r="C35" s="26" t="s">
+      <c r="C35" s="63" t="s">
         <v>15</v>
       </c>
       <c r="D35" s="3" t="s">
@@ -3966,16 +3964,16 @@
       <c r="AN35" s="5"/>
       <c r="AO35" s="5"/>
       <c r="AP35" s="5"/>
-      <c r="AQ35" s="52">
+      <c r="AQ35" s="30">
         <f>COUNTIF(E35:AI35,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR35" s="55"/>
+      <c r="AR35" s="41"/>
     </row>
     <row r="36" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="37"/>
-      <c r="B36" s="27"/>
-      <c r="C36" s="27"/>
+      <c r="A36" s="38"/>
+      <c r="B36" s="45"/>
+      <c r="C36" s="64"/>
       <c r="D36" s="6" t="s">
         <v>17</v>
       </c>
@@ -4020,13 +4018,13 @@
       <c r="AN36" s="5"/>
       <c r="AO36" s="5"/>
       <c r="AP36" s="5"/>
-      <c r="AQ36" s="53"/>
-      <c r="AR36" s="56"/>
+      <c r="AQ36" s="31"/>
+      <c r="AR36" s="42"/>
     </row>
     <row r="37" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="37"/>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
+      <c r="A37" s="38"/>
+      <c r="B37" s="45"/>
+      <c r="C37" s="64"/>
       <c r="D37" s="7" t="s">
         <v>18</v>
       </c>
@@ -4071,13 +4069,13 @@
       <c r="AN37" s="5"/>
       <c r="AO37" s="5"/>
       <c r="AP37" s="5"/>
-      <c r="AQ37" s="53"/>
-      <c r="AR37" s="56"/>
+      <c r="AQ37" s="31"/>
+      <c r="AR37" s="42"/>
     </row>
     <row r="38" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="37"/>
-      <c r="B38" s="27"/>
-      <c r="C38" s="27"/>
+      <c r="A38" s="38"/>
+      <c r="B38" s="45"/>
+      <c r="C38" s="64"/>
       <c r="D38" s="8" t="s">
         <v>19</v>
       </c>
@@ -4122,13 +4120,13 @@
       <c r="AN38" s="5"/>
       <c r="AO38" s="5"/>
       <c r="AP38" s="5"/>
-      <c r="AQ38" s="53"/>
-      <c r="AR38" s="56"/>
+      <c r="AQ38" s="31"/>
+      <c r="AR38" s="42"/>
     </row>
     <row r="39" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="37"/>
-      <c r="B39" s="27"/>
-      <c r="C39" s="27"/>
+      <c r="A39" s="38"/>
+      <c r="B39" s="45"/>
+      <c r="C39" s="64"/>
       <c r="D39" s="9" t="s">
         <v>20</v>
       </c>
@@ -4173,13 +4171,13 @@
       </c>
       <c r="AO39" s="5"/>
       <c r="AP39" s="5"/>
-      <c r="AQ39" s="53"/>
-      <c r="AR39" s="56"/>
+      <c r="AQ39" s="31"/>
+      <c r="AR39" s="42"/>
     </row>
     <row r="40" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="37"/>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
+      <c r="A40" s="38"/>
+      <c r="B40" s="45"/>
+      <c r="C40" s="64"/>
       <c r="D40" s="9" t="s">
         <v>21</v>
       </c>
@@ -4224,13 +4222,13 @@
         <v>0</v>
       </c>
       <c r="AP40" s="5"/>
-      <c r="AQ40" s="53"/>
-      <c r="AR40" s="56"/>
+      <c r="AQ40" s="31"/>
+      <c r="AR40" s="42"/>
     </row>
     <row r="41" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="37"/>
-      <c r="B41" s="28"/>
-      <c r="C41" s="28"/>
+      <c r="A41" s="38"/>
+      <c r="B41" s="46"/>
+      <c r="C41" s="65"/>
       <c r="D41" s="10" t="s">
         <v>22</v>
       </c>
@@ -4275,15 +4273,15 @@
         <f>SUM(E41:AI41)</f>
         <v>0</v>
       </c>
-      <c r="AQ41" s="54"/>
-      <c r="AR41" s="57"/>
+      <c r="AQ41" s="32"/>
+      <c r="AR41" s="43"/>
     </row>
     <row r="42" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="36"/>
-      <c r="B42" s="31">
+      <c r="A42" s="37"/>
+      <c r="B42" s="44">
         <v>6</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C42" s="63" t="s">
         <v>15</v>
       </c>
       <c r="D42" s="3" t="s">
@@ -4330,16 +4328,16 @@
       <c r="AN42" s="5"/>
       <c r="AO42" s="5"/>
       <c r="AP42" s="5"/>
-      <c r="AQ42" s="52">
+      <c r="AQ42" s="30">
         <f>COUNTIF(E42:AI42,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR42" s="55"/>
+      <c r="AR42" s="41"/>
     </row>
     <row r="43" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="37"/>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
+      <c r="A43" s="38"/>
+      <c r="B43" s="45"/>
+      <c r="C43" s="64"/>
       <c r="D43" s="6" t="s">
         <v>17</v>
       </c>
@@ -4384,13 +4382,13 @@
       <c r="AN43" s="5"/>
       <c r="AO43" s="5"/>
       <c r="AP43" s="5"/>
-      <c r="AQ43" s="53"/>
-      <c r="AR43" s="56"/>
+      <c r="AQ43" s="31"/>
+      <c r="AR43" s="42"/>
     </row>
     <row r="44" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="37"/>
-      <c r="B44" s="27"/>
-      <c r="C44" s="27"/>
+      <c r="A44" s="38"/>
+      <c r="B44" s="45"/>
+      <c r="C44" s="64"/>
       <c r="D44" s="7" t="s">
         <v>18</v>
       </c>
@@ -4435,13 +4433,13 @@
       <c r="AN44" s="5"/>
       <c r="AO44" s="5"/>
       <c r="AP44" s="5"/>
-      <c r="AQ44" s="53"/>
-      <c r="AR44" s="56"/>
+      <c r="AQ44" s="31"/>
+      <c r="AR44" s="42"/>
     </row>
     <row r="45" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="37"/>
-      <c r="B45" s="27"/>
-      <c r="C45" s="27"/>
+      <c r="A45" s="38"/>
+      <c r="B45" s="45"/>
+      <c r="C45" s="64"/>
       <c r="D45" s="8" t="s">
         <v>19</v>
       </c>
@@ -4486,13 +4484,13 @@
       <c r="AN45" s="5"/>
       <c r="AO45" s="5"/>
       <c r="AP45" s="5"/>
-      <c r="AQ45" s="53"/>
-      <c r="AR45" s="56"/>
+      <c r="AQ45" s="31"/>
+      <c r="AR45" s="42"/>
     </row>
     <row r="46" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="37"/>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
+      <c r="A46" s="38"/>
+      <c r="B46" s="45"/>
+      <c r="C46" s="64"/>
       <c r="D46" s="9" t="s">
         <v>20</v>
       </c>
@@ -4537,13 +4535,13 @@
       </c>
       <c r="AO46" s="5"/>
       <c r="AP46" s="5"/>
-      <c r="AQ46" s="53"/>
-      <c r="AR46" s="56"/>
+      <c r="AQ46" s="31"/>
+      <c r="AR46" s="42"/>
     </row>
     <row r="47" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="37"/>
-      <c r="B47" s="27"/>
-      <c r="C47" s="27"/>
+      <c r="A47" s="38"/>
+      <c r="B47" s="45"/>
+      <c r="C47" s="64"/>
       <c r="D47" s="9" t="s">
         <v>21</v>
       </c>
@@ -4588,13 +4586,13 @@
         <v>0</v>
       </c>
       <c r="AP47" s="5"/>
-      <c r="AQ47" s="53"/>
-      <c r="AR47" s="56"/>
+      <c r="AQ47" s="31"/>
+      <c r="AR47" s="42"/>
     </row>
     <row r="48" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="37"/>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28"/>
+      <c r="A48" s="38"/>
+      <c r="B48" s="46"/>
+      <c r="C48" s="65"/>
       <c r="D48" s="10" t="s">
         <v>22</v>
       </c>
@@ -4639,15 +4637,15 @@
         <f>SUM(E48:AI48)</f>
         <v>0</v>
       </c>
-      <c r="AQ48" s="54"/>
-      <c r="AR48" s="57"/>
+      <c r="AQ48" s="32"/>
+      <c r="AR48" s="43"/>
     </row>
     <row r="49" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="36"/>
-      <c r="B49" s="31">
+      <c r="A49" s="37"/>
+      <c r="B49" s="44">
         <v>7</v>
       </c>
-      <c r="C49" s="38" t="s">
+      <c r="C49" s="63" t="s">
         <v>15</v>
       </c>
       <c r="D49" s="3" t="s">
@@ -4694,16 +4692,16 @@
       <c r="AN49" s="5"/>
       <c r="AO49" s="5"/>
       <c r="AP49" s="5"/>
-      <c r="AQ49" s="52">
+      <c r="AQ49" s="30">
         <f>COUNTIF(E49:AI49,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR49" s="55"/>
+      <c r="AR49" s="41"/>
     </row>
     <row r="50" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="37"/>
-      <c r="B50" s="27"/>
-      <c r="C50" s="27"/>
+      <c r="A50" s="38"/>
+      <c r="B50" s="45"/>
+      <c r="C50" s="64"/>
       <c r="D50" s="6" t="s">
         <v>17</v>
       </c>
@@ -4748,13 +4746,13 @@
       <c r="AN50" s="5"/>
       <c r="AO50" s="5"/>
       <c r="AP50" s="5"/>
-      <c r="AQ50" s="53"/>
-      <c r="AR50" s="56"/>
+      <c r="AQ50" s="31"/>
+      <c r="AR50" s="42"/>
     </row>
     <row r="51" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="37"/>
-      <c r="B51" s="27"/>
-      <c r="C51" s="27"/>
+      <c r="A51" s="38"/>
+      <c r="B51" s="45"/>
+      <c r="C51" s="64"/>
       <c r="D51" s="7" t="s">
         <v>18</v>
       </c>
@@ -4799,13 +4797,13 @@
       <c r="AN51" s="5"/>
       <c r="AO51" s="5"/>
       <c r="AP51" s="5"/>
-      <c r="AQ51" s="53"/>
-      <c r="AR51" s="56"/>
+      <c r="AQ51" s="31"/>
+      <c r="AR51" s="42"/>
     </row>
     <row r="52" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="37"/>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
+      <c r="A52" s="38"/>
+      <c r="B52" s="45"/>
+      <c r="C52" s="64"/>
       <c r="D52" s="8" t="s">
         <v>19</v>
       </c>
@@ -4850,13 +4848,13 @@
       <c r="AN52" s="5"/>
       <c r="AO52" s="5"/>
       <c r="AP52" s="5"/>
-      <c r="AQ52" s="53"/>
-      <c r="AR52" s="56"/>
+      <c r="AQ52" s="31"/>
+      <c r="AR52" s="42"/>
     </row>
     <row r="53" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="37"/>
-      <c r="B53" s="27"/>
-      <c r="C53" s="27"/>
+      <c r="A53" s="38"/>
+      <c r="B53" s="45"/>
+      <c r="C53" s="64"/>
       <c r="D53" s="9" t="s">
         <v>20</v>
       </c>
@@ -4901,13 +4899,13 @@
       </c>
       <c r="AO53" s="5"/>
       <c r="AP53" s="5"/>
-      <c r="AQ53" s="53"/>
-      <c r="AR53" s="56"/>
+      <c r="AQ53" s="31"/>
+      <c r="AR53" s="42"/>
     </row>
     <row r="54" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="37"/>
-      <c r="B54" s="27"/>
-      <c r="C54" s="27"/>
+      <c r="A54" s="38"/>
+      <c r="B54" s="45"/>
+      <c r="C54" s="64"/>
       <c r="D54" s="9" t="s">
         <v>21</v>
       </c>
@@ -4952,13 +4950,13 @@
         <v>0</v>
       </c>
       <c r="AP54" s="5"/>
-      <c r="AQ54" s="53"/>
-      <c r="AR54" s="56"/>
+      <c r="AQ54" s="31"/>
+      <c r="AR54" s="42"/>
     </row>
     <row r="55" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="37"/>
-      <c r="B55" s="28"/>
-      <c r="C55" s="28"/>
+      <c r="A55" s="38"/>
+      <c r="B55" s="46"/>
+      <c r="C55" s="65"/>
       <c r="D55" s="10" t="s">
         <v>22</v>
       </c>
@@ -5003,15 +5001,15 @@
         <f>SUM(E55:AI55)</f>
         <v>0</v>
       </c>
-      <c r="AQ55" s="54"/>
-      <c r="AR55" s="57"/>
+      <c r="AQ55" s="32"/>
+      <c r="AR55" s="43"/>
     </row>
     <row r="56" spans="1:44" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="36"/>
-      <c r="B56" s="31">
+      <c r="A56" s="37"/>
+      <c r="B56" s="44">
         <v>8</v>
       </c>
-      <c r="C56" s="38" t="s">
+      <c r="C56" s="63" t="s">
         <v>15</v>
       </c>
       <c r="D56" s="3" t="s">
@@ -5058,16 +5056,16 @@
       <c r="AN56" s="5"/>
       <c r="AO56" s="5"/>
       <c r="AP56" s="5"/>
-      <c r="AQ56" s="52">
+      <c r="AQ56" s="30">
         <f>COUNTIF(E56:AI56,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR56" s="55"/>
+      <c r="AR56" s="41"/>
     </row>
     <row r="57" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="37"/>
-      <c r="B57" s="27"/>
-      <c r="C57" s="27"/>
+      <c r="A57" s="38"/>
+      <c r="B57" s="45"/>
+      <c r="C57" s="64"/>
       <c r="D57" s="6" t="s">
         <v>17</v>
       </c>
@@ -5112,13 +5110,13 @@
       <c r="AN57" s="5"/>
       <c r="AO57" s="5"/>
       <c r="AP57" s="5"/>
-      <c r="AQ57" s="53"/>
-      <c r="AR57" s="56"/>
+      <c r="AQ57" s="31"/>
+      <c r="AR57" s="42"/>
     </row>
     <row r="58" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="37"/>
-      <c r="B58" s="27"/>
-      <c r="C58" s="27"/>
+      <c r="A58" s="38"/>
+      <c r="B58" s="45"/>
+      <c r="C58" s="64"/>
       <c r="D58" s="7" t="s">
         <v>18</v>
       </c>
@@ -5163,13 +5161,13 @@
       <c r="AN58" s="5"/>
       <c r="AO58" s="5"/>
       <c r="AP58" s="5"/>
-      <c r="AQ58" s="53"/>
-      <c r="AR58" s="56"/>
+      <c r="AQ58" s="31"/>
+      <c r="AR58" s="42"/>
     </row>
     <row r="59" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="37"/>
-      <c r="B59" s="27"/>
-      <c r="C59" s="27"/>
+      <c r="A59" s="38"/>
+      <c r="B59" s="45"/>
+      <c r="C59" s="64"/>
       <c r="D59" s="8" t="s">
         <v>19</v>
       </c>
@@ -5214,13 +5212,13 @@
       <c r="AN59" s="5"/>
       <c r="AO59" s="5"/>
       <c r="AP59" s="5"/>
-      <c r="AQ59" s="53"/>
-      <c r="AR59" s="56"/>
+      <c r="AQ59" s="31"/>
+      <c r="AR59" s="42"/>
     </row>
     <row r="60" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="37"/>
-      <c r="B60" s="27"/>
-      <c r="C60" s="27"/>
+      <c r="A60" s="38"/>
+      <c r="B60" s="45"/>
+      <c r="C60" s="64"/>
       <c r="D60" s="9" t="s">
         <v>20</v>
       </c>
@@ -5265,13 +5263,13 @@
       </c>
       <c r="AO60" s="5"/>
       <c r="AP60" s="5"/>
-      <c r="AQ60" s="53"/>
-      <c r="AR60" s="56"/>
+      <c r="AQ60" s="31"/>
+      <c r="AR60" s="42"/>
     </row>
     <row r="61" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="37"/>
-      <c r="B61" s="27"/>
-      <c r="C61" s="27"/>
+      <c r="A61" s="38"/>
+      <c r="B61" s="45"/>
+      <c r="C61" s="64"/>
       <c r="D61" s="9" t="s">
         <v>21</v>
       </c>
@@ -5316,13 +5314,13 @@
         <v>0</v>
       </c>
       <c r="AP61" s="5"/>
-      <c r="AQ61" s="53"/>
-      <c r="AR61" s="56"/>
+      <c r="AQ61" s="31"/>
+      <c r="AR61" s="42"/>
     </row>
     <row r="62" spans="1:44" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="37"/>
-      <c r="B62" s="28"/>
-      <c r="C62" s="28"/>
+      <c r="A62" s="38"/>
+      <c r="B62" s="46"/>
+      <c r="C62" s="65"/>
       <c r="D62" s="10" t="s">
         <v>22</v>
       </c>
@@ -5367,49 +5365,49 @@
         <f>SUM(E62:AI62)</f>
         <v>0</v>
       </c>
-      <c r="AQ62" s="54"/>
-      <c r="AR62" s="57"/>
+      <c r="AQ62" s="32"/>
+      <c r="AR62" s="43"/>
     </row>
     <row r="63" spans="1:44" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="14"/>
-      <c r="B63" s="32" t="s">
+      <c r="B63" s="58" t="s">
         <v>23</v>
       </c>
-      <c r="C63" s="33"/>
-      <c r="D63" s="34"/>
-      <c r="E63" s="58" t="s">
+      <c r="C63" s="59"/>
+      <c r="D63" s="60"/>
+      <c r="E63" s="54" t="s">
         <v>26</v>
       </c>
-      <c r="F63" s="59"/>
-      <c r="G63" s="59"/>
-      <c r="H63" s="59"/>
-      <c r="I63" s="59"/>
-      <c r="J63" s="59"/>
-      <c r="K63" s="59"/>
-      <c r="L63" s="59"/>
-      <c r="M63" s="59"/>
-      <c r="N63" s="59"/>
-      <c r="O63" s="59"/>
-      <c r="P63" s="59"/>
-      <c r="Q63" s="59"/>
-      <c r="R63" s="59"/>
-      <c r="S63" s="59"/>
-      <c r="T63" s="59"/>
-      <c r="U63" s="59"/>
-      <c r="V63" s="59"/>
-      <c r="W63" s="59"/>
-      <c r="X63" s="59"/>
-      <c r="Y63" s="59"/>
-      <c r="Z63" s="59"/>
-      <c r="AA63" s="59"/>
-      <c r="AB63" s="59"/>
-      <c r="AC63" s="59"/>
-      <c r="AD63" s="59"/>
-      <c r="AE63" s="59"/>
-      <c r="AF63" s="59"/>
-      <c r="AG63" s="59"/>
-      <c r="AH63" s="59"/>
-      <c r="AI63" s="60"/>
+      <c r="F63" s="55"/>
+      <c r="G63" s="55"/>
+      <c r="H63" s="55"/>
+      <c r="I63" s="55"/>
+      <c r="J63" s="55"/>
+      <c r="K63" s="55"/>
+      <c r="L63" s="55"/>
+      <c r="M63" s="55"/>
+      <c r="N63" s="55"/>
+      <c r="O63" s="55"/>
+      <c r="P63" s="55"/>
+      <c r="Q63" s="55"/>
+      <c r="R63" s="55"/>
+      <c r="S63" s="55"/>
+      <c r="T63" s="55"/>
+      <c r="U63" s="55"/>
+      <c r="V63" s="55"/>
+      <c r="W63" s="55"/>
+      <c r="X63" s="55"/>
+      <c r="Y63" s="55"/>
+      <c r="Z63" s="55"/>
+      <c r="AA63" s="55"/>
+      <c r="AB63" s="55"/>
+      <c r="AC63" s="55"/>
+      <c r="AD63" s="55"/>
+      <c r="AE63" s="55"/>
+      <c r="AF63" s="55"/>
+      <c r="AG63" s="55"/>
+      <c r="AH63" s="55"/>
+      <c r="AI63" s="56"/>
       <c r="AJ63" s="13">
         <f t="shared" ref="AJ63:AP63" si="0">SUM(AJ7:AJ55)</f>
         <v>0</v>
@@ -5438,26 +5436,53 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AQ63" s="35" t="s">
+      <c r="AQ63" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="AR63" s="51"/>
+      <c r="AR63" s="62"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="+ZrADsvjlmIB2UyRAwEHEZ36xwZytVzRwxYKLGDgthMmP2cYinxPW7EpXBzkqA+RbpXOv1Qk11rSa9ksNVGMYA==" saltValue="b6DZVSZt3Hjg6M77pxnAjw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="68">
-    <mergeCell ref="M2:P2"/>
-    <mergeCell ref="Q2:W2"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="M3:P3"/>
-    <mergeCell ref="AP5:AP6"/>
-    <mergeCell ref="AQ21:AQ27"/>
-    <mergeCell ref="E1:V1"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="E2:L2"/>
-    <mergeCell ref="E4:AQ4"/>
-    <mergeCell ref="AQ5:AQ6"/>
-    <mergeCell ref="X2:AB2"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="AR14:AR20"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="C14:C20"/>
+    <mergeCell ref="E63:AI63"/>
+    <mergeCell ref="AQ56:AQ62"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="B42:B48"/>
+    <mergeCell ref="B14:B20"/>
+    <mergeCell ref="C35:C41"/>
+    <mergeCell ref="AR35:AR41"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="AQ49:AQ55"/>
+    <mergeCell ref="C28:C34"/>
+    <mergeCell ref="AQ63:AR63"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="B56:B62"/>
+    <mergeCell ref="AR56:AR62"/>
+    <mergeCell ref="A49:A55"/>
+    <mergeCell ref="C42:C48"/>
+    <mergeCell ref="C49:C55"/>
+    <mergeCell ref="AR49:AR55"/>
+    <mergeCell ref="C56:C62"/>
+    <mergeCell ref="A56:A62"/>
+    <mergeCell ref="A42:A48"/>
+    <mergeCell ref="AQ42:AQ48"/>
+    <mergeCell ref="B49:B55"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="AR5:AR6"/>
+    <mergeCell ref="AO5:AO6"/>
+    <mergeCell ref="C21:C27"/>
+    <mergeCell ref="AN5:AN6"/>
+    <mergeCell ref="AR21:AR27"/>
+    <mergeCell ref="AQ35:AQ41"/>
+    <mergeCell ref="C7:C13"/>
+    <mergeCell ref="B7:B13"/>
+    <mergeCell ref="AR7:AR13"/>
+    <mergeCell ref="B21:B27"/>
+    <mergeCell ref="AQ7:AQ13"/>
     <mergeCell ref="A7:A13"/>
     <mergeCell ref="A28:A34"/>
     <mergeCell ref="A14:A20"/>
@@ -5474,46 +5499,18 @@
     <mergeCell ref="AK5:AK6"/>
     <mergeCell ref="AM5:AM6"/>
     <mergeCell ref="AL5:AL6"/>
-    <mergeCell ref="AQ35:AQ41"/>
-    <mergeCell ref="C7:C13"/>
-    <mergeCell ref="B7:B13"/>
-    <mergeCell ref="AR7:AR13"/>
-    <mergeCell ref="B21:B27"/>
-    <mergeCell ref="AQ7:AQ13"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="AR5:AR6"/>
-    <mergeCell ref="AO5:AO6"/>
-    <mergeCell ref="C21:C27"/>
-    <mergeCell ref="AN5:AN6"/>
-    <mergeCell ref="AR21:AR27"/>
-    <mergeCell ref="B56:B62"/>
-    <mergeCell ref="AR56:AR62"/>
-    <mergeCell ref="A49:A55"/>
-    <mergeCell ref="C42:C48"/>
-    <mergeCell ref="C49:C55"/>
-    <mergeCell ref="AR49:AR55"/>
-    <mergeCell ref="C56:C62"/>
-    <mergeCell ref="A56:A62"/>
-    <mergeCell ref="A42:A48"/>
-    <mergeCell ref="AQ42:AQ48"/>
-    <mergeCell ref="B49:B55"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="AR14:AR20"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="C14:C20"/>
-    <mergeCell ref="E63:AI63"/>
-    <mergeCell ref="AQ56:AQ62"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="B42:B48"/>
-    <mergeCell ref="B14:B20"/>
-    <mergeCell ref="C35:C41"/>
-    <mergeCell ref="AR35:AR41"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="AQ49:AQ55"/>
-    <mergeCell ref="C28:C34"/>
-    <mergeCell ref="AQ63:AR63"/>
-    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="AQ21:AQ27"/>
+    <mergeCell ref="E1:V1"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="E2:L2"/>
+    <mergeCell ref="E4:AQ4"/>
+    <mergeCell ref="AQ5:AQ6"/>
+    <mergeCell ref="X2:AB2"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="Q2:W2"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="M3:P3"/>
+    <mergeCell ref="AP5:AP6"/>
   </mergeCells>
   <conditionalFormatting sqref="E6">
     <cfRule type="expression" dxfId="61" priority="188">

--- a/public/moduli/FoglioPresenze_StudioBaiocco.xlsx
+++ b/public/moduli/FoglioPresenze_StudioBaiocco.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Desktop/sito_mamma/public/moduli/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3141EE94-41B7-F546-A5BB-AE5F9742F4B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A740E29-DE19-8E4C-A1AA-C834A5EAA825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="660" windowWidth="30240" windowHeight="17680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Presenze" sheetId="1" r:id="rId1"/>
@@ -728,29 +728,43 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="justify"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="justify"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="justify"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -759,6 +773,60 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="justify"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -776,90 +844,22 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="justify"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="justify"/>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="justify"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="justify"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="15" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1991,29 +1991,29 @@
   <sheetData>
     <row r="1" spans="1:44" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14"/>
-      <c r="B1" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-      <c r="U1" s="26"/>
-      <c r="V1" s="26"/>
+      <c r="B1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
       <c r="W1" s="15"/>
       <c r="X1" s="15"/>
       <c r="Y1" s="15"/>
@@ -2039,41 +2039,41 @@
     </row>
     <row r="2" spans="1:44" ht="29" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="67" t="s">
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="67"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="23">
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="59"/>
+      <c r="M2" s="64">
         <v>3</v>
       </c>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="25"/>
-      <c r="Q2" s="66" t="s">
+      <c r="N2" s="65"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="66"/>
+      <c r="Q2" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
-      <c r="V2" s="67"/>
-      <c r="W2" s="68"/>
-      <c r="X2" s="34">
+      <c r="R2" s="58"/>
+      <c r="S2" s="58"/>
+      <c r="T2" s="58"/>
+      <c r="U2" s="58"/>
+      <c r="V2" s="58"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="61">
         <v>2026</v>
       </c>
-      <c r="Y2" s="35"/>
-      <c r="Z2" s="35"/>
-      <c r="AA2" s="35"/>
-      <c r="AB2" s="36"/>
+      <c r="Y2" s="62"/>
+      <c r="Z2" s="62"/>
+      <c r="AA2" s="62"/>
+      <c r="AB2" s="63"/>
       <c r="AC2" s="15"/>
       <c r="AD2" s="15"/>
       <c r="AE2" s="15"/>
@@ -2093,29 +2093,29 @@
     </row>
     <row r="3" spans="1:44" ht="19" x14ac:dyDescent="0.2">
       <c r="A3" s="14"/>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="27"/>
-      <c r="N3" s="27"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26"/>
-      <c r="U3" s="26"/>
-      <c r="V3" s="26"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="68"/>
+      <c r="N3" s="68"/>
+      <c r="O3" s="68"/>
+      <c r="P3" s="68"/>
+      <c r="Q3" s="28"/>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
+      <c r="V3" s="28"/>
       <c r="W3" s="15"/>
       <c r="X3" s="15"/>
       <c r="Y3" s="15"/>
@@ -2141,50 +2141,50 @@
     </row>
     <row r="4" spans="1:44" ht="24" x14ac:dyDescent="0.2">
       <c r="A4" s="14"/>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="33" t="s">
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="60" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="33"/>
-      <c r="S4" s="33"/>
-      <c r="T4" s="33"/>
-      <c r="U4" s="33"/>
-      <c r="V4" s="33"/>
-      <c r="W4" s="33"/>
-      <c r="X4" s="33"/>
-      <c r="Y4" s="33"/>
-      <c r="Z4" s="33"/>
-      <c r="AA4" s="33"/>
-      <c r="AB4" s="33"/>
-      <c r="AC4" s="33"/>
-      <c r="AD4" s="33"/>
-      <c r="AE4" s="33"/>
-      <c r="AF4" s="33"/>
-      <c r="AG4" s="33"/>
-      <c r="AH4" s="33"/>
-      <c r="AI4" s="33"/>
-      <c r="AJ4" s="33"/>
-      <c r="AK4" s="33"/>
-      <c r="AL4" s="33"/>
-      <c r="AM4" s="33"/>
-      <c r="AN4" s="33"/>
-      <c r="AO4" s="33"/>
-      <c r="AP4" s="33"/>
-      <c r="AQ4" s="33"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="60"/>
+      <c r="I4" s="60"/>
+      <c r="J4" s="60"/>
+      <c r="K4" s="60"/>
+      <c r="L4" s="60"/>
+      <c r="M4" s="60"/>
+      <c r="N4" s="60"/>
+      <c r="O4" s="60"/>
+      <c r="P4" s="60"/>
+      <c r="Q4" s="60"/>
+      <c r="R4" s="60"/>
+      <c r="S4" s="60"/>
+      <c r="T4" s="60"/>
+      <c r="U4" s="60"/>
+      <c r="V4" s="60"/>
+      <c r="W4" s="60"/>
+      <c r="X4" s="60"/>
+      <c r="Y4" s="60"/>
+      <c r="Z4" s="60"/>
+      <c r="AA4" s="60"/>
+      <c r="AB4" s="60"/>
+      <c r="AC4" s="60"/>
+      <c r="AD4" s="60"/>
+      <c r="AE4" s="60"/>
+      <c r="AF4" s="60"/>
+      <c r="AG4" s="60"/>
+      <c r="AH4" s="60"/>
+      <c r="AI4" s="60"/>
+      <c r="AJ4" s="60"/>
+      <c r="AK4" s="60"/>
+      <c r="AL4" s="60"/>
+      <c r="AM4" s="60"/>
+      <c r="AN4" s="60"/>
+      <c r="AO4" s="60"/>
+      <c r="AP4" s="60"/>
+      <c r="AQ4" s="60"/>
       <c r="AR4" s="16"/>
     </row>
     <row r="5" spans="1:44" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2192,10 +2192,10 @@
       <c r="B5" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="57" t="s">
+      <c r="C5" s="38" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="52"/>
+      <c r="D5" s="51"/>
       <c r="E5" s="1">
         <v>1</v>
       </c>
@@ -2289,39 +2289,39 @@
       <c r="AI5" s="1">
         <v>31</v>
       </c>
-      <c r="AJ5" s="28" t="s">
+      <c r="AJ5" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="AK5" s="28" t="s">
+      <c r="AK5" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="AL5" s="28" t="s">
+      <c r="AL5" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="AM5" s="28" t="s">
+      <c r="AM5" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="AN5" s="28" t="s">
+      <c r="AN5" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="AO5" s="28" t="s">
+      <c r="AO5" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="AP5" s="28" t="s">
+      <c r="AP5" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="AQ5" s="28" t="s">
+      <c r="AQ5" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="AR5" s="28" t="s">
+      <c r="AR5" s="52" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="14"/>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
       <c r="E6" s="2" t="str">
         <f>IFERROR(IF(1&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,1),2),"L","M","M","G","V","S","D")),"")</f>
         <v>D</v>
@@ -2446,22 +2446,22 @@
         <f>IFERROR(IF(31&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,31),2),"L","M","M","G","V","S","D")),"")</f>
         <v>M</v>
       </c>
-      <c r="AJ6" s="29"/>
-      <c r="AK6" s="29"/>
-      <c r="AL6" s="29"/>
-      <c r="AM6" s="29"/>
-      <c r="AN6" s="29"/>
-      <c r="AO6" s="29"/>
-      <c r="AP6" s="29"/>
-      <c r="AQ6" s="29"/>
-      <c r="AR6" s="29"/>
+      <c r="AJ6" s="53"/>
+      <c r="AK6" s="53"/>
+      <c r="AL6" s="53"/>
+      <c r="AM6" s="53"/>
+      <c r="AN6" s="53"/>
+      <c r="AO6" s="53"/>
+      <c r="AP6" s="53"/>
+      <c r="AQ6" s="53"/>
+      <c r="AR6" s="53"/>
     </row>
     <row r="7" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="37"/>
-      <c r="B7" s="47">
+      <c r="A7" s="48"/>
+      <c r="B7" s="54">
         <v>1</v>
       </c>
-      <c r="C7" s="63" t="s">
+      <c r="C7" s="29" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -2508,16 +2508,16 @@
       <c r="AN7" s="5"/>
       <c r="AO7" s="5"/>
       <c r="AP7" s="5"/>
-      <c r="AQ7" s="49">
+      <c r="AQ7" s="56">
         <f>COUNTIF(E7:AI7,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR7" s="48"/>
+      <c r="AR7" s="55"/>
     </row>
     <row r="8" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="38"/>
-      <c r="B8" s="45"/>
-      <c r="C8" s="64"/>
+      <c r="A8" s="49"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="30"/>
       <c r="D8" s="6" t="s">
         <v>17</v>
       </c>
@@ -2562,13 +2562,13 @@
       <c r="AN8" s="5"/>
       <c r="AO8" s="5"/>
       <c r="AP8" s="5"/>
-      <c r="AQ8" s="31"/>
-      <c r="AR8" s="42"/>
+      <c r="AQ8" s="36"/>
+      <c r="AR8" s="26"/>
     </row>
     <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="38"/>
-      <c r="B9" s="45"/>
-      <c r="C9" s="64"/>
+      <c r="A9" s="49"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="30"/>
       <c r="D9" s="7" t="s">
         <v>18</v>
       </c>
@@ -2613,13 +2613,13 @@
       <c r="AN9" s="5"/>
       <c r="AO9" s="5"/>
       <c r="AP9" s="5"/>
-      <c r="AQ9" s="31"/>
-      <c r="AR9" s="42"/>
+      <c r="AQ9" s="36"/>
+      <c r="AR9" s="26"/>
     </row>
     <row r="10" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="38"/>
-      <c r="B10" s="45"/>
-      <c r="C10" s="64"/>
+      <c r="A10" s="49"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="30"/>
       <c r="D10" s="8" t="s">
         <v>19</v>
       </c>
@@ -2664,13 +2664,13 @@
       <c r="AN10" s="5"/>
       <c r="AO10" s="5"/>
       <c r="AP10" s="5"/>
-      <c r="AQ10" s="31"/>
-      <c r="AR10" s="42"/>
+      <c r="AQ10" s="36"/>
+      <c r="AR10" s="26"/>
     </row>
     <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="38"/>
-      <c r="B11" s="45"/>
-      <c r="C11" s="64"/>
+      <c r="A11" s="49"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="30"/>
       <c r="D11" s="9" t="s">
         <v>20</v>
       </c>
@@ -2715,13 +2715,13 @@
       </c>
       <c r="AO11" s="5"/>
       <c r="AP11" s="5"/>
-      <c r="AQ11" s="31"/>
-      <c r="AR11" s="42"/>
+      <c r="AQ11" s="36"/>
+      <c r="AR11" s="26"/>
     </row>
     <row r="12" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="38"/>
-      <c r="B12" s="45"/>
-      <c r="C12" s="64"/>
+      <c r="A12" s="49"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="30"/>
       <c r="D12" s="9" t="s">
         <v>21</v>
       </c>
@@ -2766,13 +2766,13 @@
         <v>0</v>
       </c>
       <c r="AP12" s="5"/>
-      <c r="AQ12" s="31"/>
-      <c r="AR12" s="42"/>
+      <c r="AQ12" s="36"/>
+      <c r="AR12" s="26"/>
     </row>
     <row r="13" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="38"/>
-      <c r="B13" s="46"/>
-      <c r="C13" s="65"/>
+      <c r="A13" s="49"/>
+      <c r="B13" s="42"/>
+      <c r="C13" s="31"/>
       <c r="D13" s="10" t="s">
         <v>22</v>
       </c>
@@ -2817,15 +2817,15 @@
         <f>SUM(E13:AI13)</f>
         <v>0</v>
       </c>
-      <c r="AQ13" s="32"/>
-      <c r="AR13" s="43"/>
+      <c r="AQ13" s="37"/>
+      <c r="AR13" s="27"/>
     </row>
     <row r="14" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="37"/>
-      <c r="B14" s="44">
+      <c r="A14" s="48"/>
+      <c r="B14" s="40">
         <v>2</v>
       </c>
-      <c r="C14" s="63" t="s">
+      <c r="C14" s="29" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -2872,16 +2872,16 @@
       <c r="AN14" s="5"/>
       <c r="AO14" s="5"/>
       <c r="AP14" s="5"/>
-      <c r="AQ14" s="30">
+      <c r="AQ14" s="35">
         <f>COUNTIF(E14:AI14,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR14" s="41"/>
+      <c r="AR14" s="25"/>
     </row>
     <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="38"/>
-      <c r="B15" s="45"/>
-      <c r="C15" s="64"/>
+      <c r="A15" s="49"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="30"/>
       <c r="D15" s="6" t="s">
         <v>17</v>
       </c>
@@ -2926,13 +2926,13 @@
       <c r="AN15" s="5"/>
       <c r="AO15" s="5"/>
       <c r="AP15" s="5"/>
-      <c r="AQ15" s="31"/>
-      <c r="AR15" s="42"/>
+      <c r="AQ15" s="36"/>
+      <c r="AR15" s="26"/>
     </row>
     <row r="16" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="38"/>
-      <c r="B16" s="45"/>
-      <c r="C16" s="64"/>
+      <c r="A16" s="49"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="30"/>
       <c r="D16" s="7" t="s">
         <v>18</v>
       </c>
@@ -2977,13 +2977,13 @@
       <c r="AN16" s="5"/>
       <c r="AO16" s="5"/>
       <c r="AP16" s="5"/>
-      <c r="AQ16" s="31"/>
-      <c r="AR16" s="42"/>
+      <c r="AQ16" s="36"/>
+      <c r="AR16" s="26"/>
     </row>
     <row r="17" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="38"/>
-      <c r="B17" s="45"/>
-      <c r="C17" s="64"/>
+      <c r="A17" s="49"/>
+      <c r="B17" s="41"/>
+      <c r="C17" s="30"/>
       <c r="D17" s="8" t="s">
         <v>19</v>
       </c>
@@ -3028,13 +3028,13 @@
       <c r="AN17" s="5"/>
       <c r="AO17" s="5"/>
       <c r="AP17" s="5"/>
-      <c r="AQ17" s="31"/>
-      <c r="AR17" s="42"/>
+      <c r="AQ17" s="36"/>
+      <c r="AR17" s="26"/>
     </row>
     <row r="18" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="38"/>
-      <c r="B18" s="45"/>
-      <c r="C18" s="64"/>
+      <c r="A18" s="49"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="30"/>
       <c r="D18" s="9" t="s">
         <v>20</v>
       </c>
@@ -3079,13 +3079,13 @@
       </c>
       <c r="AO18" s="5"/>
       <c r="AP18" s="5"/>
-      <c r="AQ18" s="31"/>
-      <c r="AR18" s="42"/>
+      <c r="AQ18" s="36"/>
+      <c r="AR18" s="26"/>
     </row>
     <row r="19" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="38"/>
-      <c r="B19" s="45"/>
-      <c r="C19" s="64"/>
+      <c r="A19" s="49"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="30"/>
       <c r="D19" s="9" t="s">
         <v>21</v>
       </c>
@@ -3130,13 +3130,13 @@
         <v>0</v>
       </c>
       <c r="AP19" s="5"/>
-      <c r="AQ19" s="31"/>
-      <c r="AR19" s="42"/>
+      <c r="AQ19" s="36"/>
+      <c r="AR19" s="26"/>
     </row>
     <row r="20" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="38"/>
-      <c r="B20" s="46"/>
-      <c r="C20" s="65"/>
+      <c r="A20" s="49"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="31"/>
       <c r="D20" s="10" t="s">
         <v>22</v>
       </c>
@@ -3181,15 +3181,15 @@
         <f>SUM(E20:AI20)</f>
         <v>0</v>
       </c>
-      <c r="AQ20" s="32"/>
-      <c r="AR20" s="43"/>
+      <c r="AQ20" s="37"/>
+      <c r="AR20" s="27"/>
     </row>
     <row r="21" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="37"/>
-      <c r="B21" s="44">
+      <c r="A21" s="48"/>
+      <c r="B21" s="40">
         <v>3</v>
       </c>
-      <c r="C21" s="63" t="s">
+      <c r="C21" s="29" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3" t="s">
@@ -3236,16 +3236,16 @@
       <c r="AN21" s="5"/>
       <c r="AO21" s="5"/>
       <c r="AP21" s="5"/>
-      <c r="AQ21" s="30">
+      <c r="AQ21" s="35">
         <f>COUNTIF(E21:AI21,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR21" s="41"/>
+      <c r="AR21" s="25"/>
     </row>
     <row r="22" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="38"/>
-      <c r="B22" s="45"/>
-      <c r="C22" s="64"/>
+      <c r="A22" s="49"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="30"/>
       <c r="D22" s="6" t="s">
         <v>17</v>
       </c>
@@ -3290,13 +3290,13 @@
       <c r="AN22" s="5"/>
       <c r="AO22" s="5"/>
       <c r="AP22" s="5"/>
-      <c r="AQ22" s="31"/>
-      <c r="AR22" s="42"/>
+      <c r="AQ22" s="36"/>
+      <c r="AR22" s="26"/>
     </row>
     <row r="23" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="38"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="64"/>
+      <c r="A23" s="49"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="30"/>
       <c r="D23" s="7" t="s">
         <v>18</v>
       </c>
@@ -3341,13 +3341,13 @@
       <c r="AN23" s="5"/>
       <c r="AO23" s="5"/>
       <c r="AP23" s="5"/>
-      <c r="AQ23" s="31"/>
-      <c r="AR23" s="42"/>
+      <c r="AQ23" s="36"/>
+      <c r="AR23" s="26"/>
     </row>
     <row r="24" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="38"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="64"/>
+      <c r="A24" s="49"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="30"/>
       <c r="D24" s="8" t="s">
         <v>19</v>
       </c>
@@ -3392,13 +3392,13 @@
       <c r="AN24" s="5"/>
       <c r="AO24" s="5"/>
       <c r="AP24" s="5"/>
-      <c r="AQ24" s="31"/>
-      <c r="AR24" s="42"/>
+      <c r="AQ24" s="36"/>
+      <c r="AR24" s="26"/>
     </row>
     <row r="25" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="38"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="64"/>
+      <c r="A25" s="49"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="30"/>
       <c r="D25" s="9" t="s">
         <v>20</v>
       </c>
@@ -3443,13 +3443,13 @@
       </c>
       <c r="AO25" s="5"/>
       <c r="AP25" s="5"/>
-      <c r="AQ25" s="31"/>
-      <c r="AR25" s="42"/>
+      <c r="AQ25" s="36"/>
+      <c r="AR25" s="26"/>
     </row>
     <row r="26" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="38"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="64"/>
+      <c r="A26" s="49"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="30"/>
       <c r="D26" s="9" t="s">
         <v>21</v>
       </c>
@@ -3494,13 +3494,13 @@
         <v>0</v>
       </c>
       <c r="AP26" s="5"/>
-      <c r="AQ26" s="31"/>
-      <c r="AR26" s="42"/>
+      <c r="AQ26" s="36"/>
+      <c r="AR26" s="26"/>
     </row>
     <row r="27" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="38"/>
-      <c r="B27" s="46"/>
-      <c r="C27" s="65"/>
+      <c r="A27" s="49"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="31"/>
       <c r="D27" s="10" t="s">
         <v>22</v>
       </c>
@@ -3545,15 +3545,15 @@
         <f>SUM(E27:AI27)</f>
         <v>0</v>
       </c>
-      <c r="AQ27" s="32"/>
-      <c r="AR27" s="43"/>
+      <c r="AQ27" s="37"/>
+      <c r="AR27" s="27"/>
     </row>
     <row r="28" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="37"/>
-      <c r="B28" s="44">
+      <c r="A28" s="48"/>
+      <c r="B28" s="40">
         <v>4</v>
       </c>
-      <c r="C28" s="63" t="s">
+      <c r="C28" s="29" t="s">
         <v>15</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -3600,16 +3600,16 @@
       <c r="AN28" s="5"/>
       <c r="AO28" s="5"/>
       <c r="AP28" s="5"/>
-      <c r="AQ28" s="30">
+      <c r="AQ28" s="35">
         <f>COUNTIF(E28:AI28,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR28" s="41"/>
+      <c r="AR28" s="25"/>
     </row>
     <row r="29" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="38"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="64"/>
+      <c r="A29" s="49"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="30"/>
       <c r="D29" s="6" t="s">
         <v>17</v>
       </c>
@@ -3654,13 +3654,13 @@
       <c r="AN29" s="5"/>
       <c r="AO29" s="5"/>
       <c r="AP29" s="5"/>
-      <c r="AQ29" s="31"/>
-      <c r="AR29" s="42"/>
+      <c r="AQ29" s="36"/>
+      <c r="AR29" s="26"/>
     </row>
     <row r="30" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="38"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="64"/>
+      <c r="A30" s="49"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="30"/>
       <c r="D30" s="7" t="s">
         <v>18</v>
       </c>
@@ -3705,13 +3705,13 @@
       <c r="AN30" s="5"/>
       <c r="AO30" s="5"/>
       <c r="AP30" s="5"/>
-      <c r="AQ30" s="31"/>
-      <c r="AR30" s="42"/>
+      <c r="AQ30" s="36"/>
+      <c r="AR30" s="26"/>
     </row>
     <row r="31" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="38"/>
-      <c r="B31" s="45"/>
-      <c r="C31" s="64"/>
+      <c r="A31" s="49"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="30"/>
       <c r="D31" s="8" t="s">
         <v>19</v>
       </c>
@@ -3756,13 +3756,13 @@
       <c r="AN31" s="5"/>
       <c r="AO31" s="5"/>
       <c r="AP31" s="5"/>
-      <c r="AQ31" s="31"/>
-      <c r="AR31" s="42"/>
+      <c r="AQ31" s="36"/>
+      <c r="AR31" s="26"/>
     </row>
     <row r="32" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="38"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="64"/>
+      <c r="A32" s="49"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="30"/>
       <c r="D32" s="9" t="s">
         <v>20</v>
       </c>
@@ -3807,13 +3807,13 @@
       </c>
       <c r="AO32" s="5"/>
       <c r="AP32" s="5"/>
-      <c r="AQ32" s="31"/>
-      <c r="AR32" s="42"/>
+      <c r="AQ32" s="36"/>
+      <c r="AR32" s="26"/>
     </row>
     <row r="33" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="38"/>
-      <c r="B33" s="45"/>
-      <c r="C33" s="64"/>
+      <c r="A33" s="49"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="30"/>
       <c r="D33" s="9" t="s">
         <v>21</v>
       </c>
@@ -3858,13 +3858,13 @@
         <v>0</v>
       </c>
       <c r="AP33" s="5"/>
-      <c r="AQ33" s="31"/>
-      <c r="AR33" s="42"/>
+      <c r="AQ33" s="36"/>
+      <c r="AR33" s="26"/>
     </row>
     <row r="34" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="38"/>
-      <c r="B34" s="46"/>
-      <c r="C34" s="65"/>
+      <c r="A34" s="49"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="31"/>
       <c r="D34" s="10" t="s">
         <v>22</v>
       </c>
@@ -3909,15 +3909,15 @@
         <f>SUM(E34:AI34)</f>
         <v>0</v>
       </c>
-      <c r="AQ34" s="32"/>
-      <c r="AR34" s="43"/>
+      <c r="AQ34" s="37"/>
+      <c r="AR34" s="27"/>
     </row>
     <row r="35" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="37"/>
-      <c r="B35" s="44">
+      <c r="A35" s="48"/>
+      <c r="B35" s="40">
         <v>5</v>
       </c>
-      <c r="C35" s="63" t="s">
+      <c r="C35" s="29" t="s">
         <v>15</v>
       </c>
       <c r="D35" s="3" t="s">
@@ -3964,16 +3964,16 @@
       <c r="AN35" s="5"/>
       <c r="AO35" s="5"/>
       <c r="AP35" s="5"/>
-      <c r="AQ35" s="30">
+      <c r="AQ35" s="35">
         <f>COUNTIF(E35:AI35,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR35" s="41"/>
+      <c r="AR35" s="25"/>
     </row>
     <row r="36" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="38"/>
-      <c r="B36" s="45"/>
-      <c r="C36" s="64"/>
+      <c r="A36" s="49"/>
+      <c r="B36" s="41"/>
+      <c r="C36" s="30"/>
       <c r="D36" s="6" t="s">
         <v>17</v>
       </c>
@@ -4018,13 +4018,13 @@
       <c r="AN36" s="5"/>
       <c r="AO36" s="5"/>
       <c r="AP36" s="5"/>
-      <c r="AQ36" s="31"/>
-      <c r="AR36" s="42"/>
+      <c r="AQ36" s="36"/>
+      <c r="AR36" s="26"/>
     </row>
     <row r="37" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="38"/>
-      <c r="B37" s="45"/>
-      <c r="C37" s="64"/>
+      <c r="A37" s="49"/>
+      <c r="B37" s="41"/>
+      <c r="C37" s="30"/>
       <c r="D37" s="7" t="s">
         <v>18</v>
       </c>
@@ -4069,13 +4069,13 @@
       <c r="AN37" s="5"/>
       <c r="AO37" s="5"/>
       <c r="AP37" s="5"/>
-      <c r="AQ37" s="31"/>
-      <c r="AR37" s="42"/>
+      <c r="AQ37" s="36"/>
+      <c r="AR37" s="26"/>
     </row>
     <row r="38" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="38"/>
-      <c r="B38" s="45"/>
-      <c r="C38" s="64"/>
+      <c r="A38" s="49"/>
+      <c r="B38" s="41"/>
+      <c r="C38" s="30"/>
       <c r="D38" s="8" t="s">
         <v>19</v>
       </c>
@@ -4120,13 +4120,13 @@
       <c r="AN38" s="5"/>
       <c r="AO38" s="5"/>
       <c r="AP38" s="5"/>
-      <c r="AQ38" s="31"/>
-      <c r="AR38" s="42"/>
+      <c r="AQ38" s="36"/>
+      <c r="AR38" s="26"/>
     </row>
     <row r="39" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="38"/>
-      <c r="B39" s="45"/>
-      <c r="C39" s="64"/>
+      <c r="A39" s="49"/>
+      <c r="B39" s="41"/>
+      <c r="C39" s="30"/>
       <c r="D39" s="9" t="s">
         <v>20</v>
       </c>
@@ -4171,13 +4171,13 @@
       </c>
       <c r="AO39" s="5"/>
       <c r="AP39" s="5"/>
-      <c r="AQ39" s="31"/>
-      <c r="AR39" s="42"/>
+      <c r="AQ39" s="36"/>
+      <c r="AR39" s="26"/>
     </row>
     <row r="40" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="38"/>
-      <c r="B40" s="45"/>
-      <c r="C40" s="64"/>
+      <c r="A40" s="49"/>
+      <c r="B40" s="41"/>
+      <c r="C40" s="30"/>
       <c r="D40" s="9" t="s">
         <v>21</v>
       </c>
@@ -4222,13 +4222,13 @@
         <v>0</v>
       </c>
       <c r="AP40" s="5"/>
-      <c r="AQ40" s="31"/>
-      <c r="AR40" s="42"/>
+      <c r="AQ40" s="36"/>
+      <c r="AR40" s="26"/>
     </row>
     <row r="41" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="38"/>
-      <c r="B41" s="46"/>
-      <c r="C41" s="65"/>
+      <c r="A41" s="49"/>
+      <c r="B41" s="42"/>
+      <c r="C41" s="31"/>
       <c r="D41" s="10" t="s">
         <v>22</v>
       </c>
@@ -4273,15 +4273,15 @@
         <f>SUM(E41:AI41)</f>
         <v>0</v>
       </c>
-      <c r="AQ41" s="32"/>
-      <c r="AR41" s="43"/>
+      <c r="AQ41" s="37"/>
+      <c r="AR41" s="27"/>
     </row>
     <row r="42" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="37"/>
-      <c r="B42" s="44">
+      <c r="A42" s="48"/>
+      <c r="B42" s="40">
         <v>6</v>
       </c>
-      <c r="C42" s="63" t="s">
+      <c r="C42" s="29" t="s">
         <v>15</v>
       </c>
       <c r="D42" s="3" t="s">
@@ -4328,16 +4328,16 @@
       <c r="AN42" s="5"/>
       <c r="AO42" s="5"/>
       <c r="AP42" s="5"/>
-      <c r="AQ42" s="30">
+      <c r="AQ42" s="35">
         <f>COUNTIF(E42:AI42,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR42" s="41"/>
+      <c r="AR42" s="25"/>
     </row>
     <row r="43" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="38"/>
-      <c r="B43" s="45"/>
-      <c r="C43" s="64"/>
+      <c r="A43" s="49"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="30"/>
       <c r="D43" s="6" t="s">
         <v>17</v>
       </c>
@@ -4382,13 +4382,13 @@
       <c r="AN43" s="5"/>
       <c r="AO43" s="5"/>
       <c r="AP43" s="5"/>
-      <c r="AQ43" s="31"/>
-      <c r="AR43" s="42"/>
+      <c r="AQ43" s="36"/>
+      <c r="AR43" s="26"/>
     </row>
     <row r="44" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="38"/>
-      <c r="B44" s="45"/>
-      <c r="C44" s="64"/>
+      <c r="A44" s="49"/>
+      <c r="B44" s="41"/>
+      <c r="C44" s="30"/>
       <c r="D44" s="7" t="s">
         <v>18</v>
       </c>
@@ -4433,13 +4433,13 @@
       <c r="AN44" s="5"/>
       <c r="AO44" s="5"/>
       <c r="AP44" s="5"/>
-      <c r="AQ44" s="31"/>
-      <c r="AR44" s="42"/>
+      <c r="AQ44" s="36"/>
+      <c r="AR44" s="26"/>
     </row>
     <row r="45" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="38"/>
-      <c r="B45" s="45"/>
-      <c r="C45" s="64"/>
+      <c r="A45" s="49"/>
+      <c r="B45" s="41"/>
+      <c r="C45" s="30"/>
       <c r="D45" s="8" t="s">
         <v>19</v>
       </c>
@@ -4484,13 +4484,13 @@
       <c r="AN45" s="5"/>
       <c r="AO45" s="5"/>
       <c r="AP45" s="5"/>
-      <c r="AQ45" s="31"/>
-      <c r="AR45" s="42"/>
+      <c r="AQ45" s="36"/>
+      <c r="AR45" s="26"/>
     </row>
     <row r="46" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="38"/>
-      <c r="B46" s="45"/>
-      <c r="C46" s="64"/>
+      <c r="A46" s="49"/>
+      <c r="B46" s="41"/>
+      <c r="C46" s="30"/>
       <c r="D46" s="9" t="s">
         <v>20</v>
       </c>
@@ -4535,13 +4535,13 @@
       </c>
       <c r="AO46" s="5"/>
       <c r="AP46" s="5"/>
-      <c r="AQ46" s="31"/>
-      <c r="AR46" s="42"/>
+      <c r="AQ46" s="36"/>
+      <c r="AR46" s="26"/>
     </row>
     <row r="47" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="38"/>
-      <c r="B47" s="45"/>
-      <c r="C47" s="64"/>
+      <c r="A47" s="49"/>
+      <c r="B47" s="41"/>
+      <c r="C47" s="30"/>
       <c r="D47" s="9" t="s">
         <v>21</v>
       </c>
@@ -4586,13 +4586,13 @@
         <v>0</v>
       </c>
       <c r="AP47" s="5"/>
-      <c r="AQ47" s="31"/>
-      <c r="AR47" s="42"/>
+      <c r="AQ47" s="36"/>
+      <c r="AR47" s="26"/>
     </row>
     <row r="48" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="38"/>
-      <c r="B48" s="46"/>
-      <c r="C48" s="65"/>
+      <c r="A48" s="49"/>
+      <c r="B48" s="42"/>
+      <c r="C48" s="31"/>
       <c r="D48" s="10" t="s">
         <v>22</v>
       </c>
@@ -4637,15 +4637,15 @@
         <f>SUM(E48:AI48)</f>
         <v>0</v>
       </c>
-      <c r="AQ48" s="32"/>
-      <c r="AR48" s="43"/>
+      <c r="AQ48" s="37"/>
+      <c r="AR48" s="27"/>
     </row>
     <row r="49" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="37"/>
-      <c r="B49" s="44">
+      <c r="A49" s="48"/>
+      <c r="B49" s="40">
         <v>7</v>
       </c>
-      <c r="C49" s="63" t="s">
+      <c r="C49" s="29" t="s">
         <v>15</v>
       </c>
       <c r="D49" s="3" t="s">
@@ -4692,16 +4692,16 @@
       <c r="AN49" s="5"/>
       <c r="AO49" s="5"/>
       <c r="AP49" s="5"/>
-      <c r="AQ49" s="30">
+      <c r="AQ49" s="35">
         <f>COUNTIF(E49:AI49,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR49" s="41"/>
+      <c r="AR49" s="25"/>
     </row>
     <row r="50" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="38"/>
-      <c r="B50" s="45"/>
-      <c r="C50" s="64"/>
+      <c r="A50" s="49"/>
+      <c r="B50" s="41"/>
+      <c r="C50" s="30"/>
       <c r="D50" s="6" t="s">
         <v>17</v>
       </c>
@@ -4746,13 +4746,13 @@
       <c r="AN50" s="5"/>
       <c r="AO50" s="5"/>
       <c r="AP50" s="5"/>
-      <c r="AQ50" s="31"/>
-      <c r="AR50" s="42"/>
+      <c r="AQ50" s="36"/>
+      <c r="AR50" s="26"/>
     </row>
     <row r="51" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="38"/>
-      <c r="B51" s="45"/>
-      <c r="C51" s="64"/>
+      <c r="A51" s="49"/>
+      <c r="B51" s="41"/>
+      <c r="C51" s="30"/>
       <c r="D51" s="7" t="s">
         <v>18</v>
       </c>
@@ -4797,13 +4797,13 @@
       <c r="AN51" s="5"/>
       <c r="AO51" s="5"/>
       <c r="AP51" s="5"/>
-      <c r="AQ51" s="31"/>
-      <c r="AR51" s="42"/>
+      <c r="AQ51" s="36"/>
+      <c r="AR51" s="26"/>
     </row>
     <row r="52" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="38"/>
-      <c r="B52" s="45"/>
-      <c r="C52" s="64"/>
+      <c r="A52" s="49"/>
+      <c r="B52" s="41"/>
+      <c r="C52" s="30"/>
       <c r="D52" s="8" t="s">
         <v>19</v>
       </c>
@@ -4848,13 +4848,13 @@
       <c r="AN52" s="5"/>
       <c r="AO52" s="5"/>
       <c r="AP52" s="5"/>
-      <c r="AQ52" s="31"/>
-      <c r="AR52" s="42"/>
+      <c r="AQ52" s="36"/>
+      <c r="AR52" s="26"/>
     </row>
     <row r="53" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="38"/>
-      <c r="B53" s="45"/>
-      <c r="C53" s="64"/>
+      <c r="A53" s="49"/>
+      <c r="B53" s="41"/>
+      <c r="C53" s="30"/>
       <c r="D53" s="9" t="s">
         <v>20</v>
       </c>
@@ -4899,13 +4899,13 @@
       </c>
       <c r="AO53" s="5"/>
       <c r="AP53" s="5"/>
-      <c r="AQ53" s="31"/>
-      <c r="AR53" s="42"/>
+      <c r="AQ53" s="36"/>
+      <c r="AR53" s="26"/>
     </row>
     <row r="54" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="38"/>
-      <c r="B54" s="45"/>
-      <c r="C54" s="64"/>
+      <c r="A54" s="49"/>
+      <c r="B54" s="41"/>
+      <c r="C54" s="30"/>
       <c r="D54" s="9" t="s">
         <v>21</v>
       </c>
@@ -4950,13 +4950,13 @@
         <v>0</v>
       </c>
       <c r="AP54" s="5"/>
-      <c r="AQ54" s="31"/>
-      <c r="AR54" s="42"/>
+      <c r="AQ54" s="36"/>
+      <c r="AR54" s="26"/>
     </row>
     <row r="55" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="38"/>
-      <c r="B55" s="46"/>
-      <c r="C55" s="65"/>
+      <c r="A55" s="49"/>
+      <c r="B55" s="42"/>
+      <c r="C55" s="31"/>
       <c r="D55" s="10" t="s">
         <v>22</v>
       </c>
@@ -5001,15 +5001,15 @@
         <f>SUM(E55:AI55)</f>
         <v>0</v>
       </c>
-      <c r="AQ55" s="32"/>
-      <c r="AR55" s="43"/>
+      <c r="AQ55" s="37"/>
+      <c r="AR55" s="27"/>
     </row>
     <row r="56" spans="1:44" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="37"/>
-      <c r="B56" s="44">
+      <c r="A56" s="48"/>
+      <c r="B56" s="40">
         <v>8</v>
       </c>
-      <c r="C56" s="63" t="s">
+      <c r="C56" s="29" t="s">
         <v>15</v>
       </c>
       <c r="D56" s="3" t="s">
@@ -5056,16 +5056,16 @@
       <c r="AN56" s="5"/>
       <c r="AO56" s="5"/>
       <c r="AP56" s="5"/>
-      <c r="AQ56" s="30">
+      <c r="AQ56" s="35">
         <f>COUNTIF(E56:AI56,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR56" s="41"/>
+      <c r="AR56" s="25"/>
     </row>
     <row r="57" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="38"/>
-      <c r="B57" s="45"/>
-      <c r="C57" s="64"/>
+      <c r="A57" s="49"/>
+      <c r="B57" s="41"/>
+      <c r="C57" s="30"/>
       <c r="D57" s="6" t="s">
         <v>17</v>
       </c>
@@ -5110,13 +5110,13 @@
       <c r="AN57" s="5"/>
       <c r="AO57" s="5"/>
       <c r="AP57" s="5"/>
-      <c r="AQ57" s="31"/>
-      <c r="AR57" s="42"/>
+      <c r="AQ57" s="36"/>
+      <c r="AR57" s="26"/>
     </row>
     <row r="58" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="38"/>
-      <c r="B58" s="45"/>
-      <c r="C58" s="64"/>
+      <c r="A58" s="49"/>
+      <c r="B58" s="41"/>
+      <c r="C58" s="30"/>
       <c r="D58" s="7" t="s">
         <v>18</v>
       </c>
@@ -5161,13 +5161,13 @@
       <c r="AN58" s="5"/>
       <c r="AO58" s="5"/>
       <c r="AP58" s="5"/>
-      <c r="AQ58" s="31"/>
-      <c r="AR58" s="42"/>
+      <c r="AQ58" s="36"/>
+      <c r="AR58" s="26"/>
     </row>
     <row r="59" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="38"/>
-      <c r="B59" s="45"/>
-      <c r="C59" s="64"/>
+      <c r="A59" s="49"/>
+      <c r="B59" s="41"/>
+      <c r="C59" s="30"/>
       <c r="D59" s="8" t="s">
         <v>19</v>
       </c>
@@ -5212,13 +5212,13 @@
       <c r="AN59" s="5"/>
       <c r="AO59" s="5"/>
       <c r="AP59" s="5"/>
-      <c r="AQ59" s="31"/>
-      <c r="AR59" s="42"/>
+      <c r="AQ59" s="36"/>
+      <c r="AR59" s="26"/>
     </row>
     <row r="60" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="38"/>
-      <c r="B60" s="45"/>
-      <c r="C60" s="64"/>
+      <c r="A60" s="49"/>
+      <c r="B60" s="41"/>
+      <c r="C60" s="30"/>
       <c r="D60" s="9" t="s">
         <v>20</v>
       </c>
@@ -5263,13 +5263,13 @@
       </c>
       <c r="AO60" s="5"/>
       <c r="AP60" s="5"/>
-      <c r="AQ60" s="31"/>
-      <c r="AR60" s="42"/>
+      <c r="AQ60" s="36"/>
+      <c r="AR60" s="26"/>
     </row>
     <row r="61" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="38"/>
-      <c r="B61" s="45"/>
-      <c r="C61" s="64"/>
+      <c r="A61" s="49"/>
+      <c r="B61" s="41"/>
+      <c r="C61" s="30"/>
       <c r="D61" s="9" t="s">
         <v>21</v>
       </c>
@@ -5314,13 +5314,13 @@
         <v>0</v>
       </c>
       <c r="AP61" s="5"/>
-      <c r="AQ61" s="31"/>
-      <c r="AR61" s="42"/>
+      <c r="AQ61" s="36"/>
+      <c r="AR61" s="26"/>
     </row>
     <row r="62" spans="1:44" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="38"/>
-      <c r="B62" s="46"/>
-      <c r="C62" s="65"/>
+      <c r="A62" s="49"/>
+      <c r="B62" s="42"/>
+      <c r="C62" s="31"/>
       <c r="D62" s="10" t="s">
         <v>22</v>
       </c>
@@ -5365,49 +5365,49 @@
         <f>SUM(E62:AI62)</f>
         <v>0</v>
       </c>
-      <c r="AQ62" s="32"/>
-      <c r="AR62" s="43"/>
+      <c r="AQ62" s="37"/>
+      <c r="AR62" s="27"/>
     </row>
     <row r="63" spans="1:44" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="14"/>
-      <c r="B63" s="58" t="s">
+      <c r="B63" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="C63" s="59"/>
-      <c r="D63" s="60"/>
-      <c r="E63" s="54" t="s">
+      <c r="C63" s="44"/>
+      <c r="D63" s="45"/>
+      <c r="E63" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="F63" s="55"/>
-      <c r="G63" s="55"/>
-      <c r="H63" s="55"/>
-      <c r="I63" s="55"/>
-      <c r="J63" s="55"/>
-      <c r="K63" s="55"/>
-      <c r="L63" s="55"/>
-      <c r="M63" s="55"/>
-      <c r="N63" s="55"/>
-      <c r="O63" s="55"/>
-      <c r="P63" s="55"/>
-      <c r="Q63" s="55"/>
-      <c r="R63" s="55"/>
-      <c r="S63" s="55"/>
-      <c r="T63" s="55"/>
-      <c r="U63" s="55"/>
-      <c r="V63" s="55"/>
-      <c r="W63" s="55"/>
-      <c r="X63" s="55"/>
-      <c r="Y63" s="55"/>
-      <c r="Z63" s="55"/>
-      <c r="AA63" s="55"/>
-      <c r="AB63" s="55"/>
-      <c r="AC63" s="55"/>
-      <c r="AD63" s="55"/>
-      <c r="AE63" s="55"/>
-      <c r="AF63" s="55"/>
-      <c r="AG63" s="55"/>
-      <c r="AH63" s="55"/>
-      <c r="AI63" s="56"/>
+      <c r="F63" s="33"/>
+      <c r="G63" s="33"/>
+      <c r="H63" s="33"/>
+      <c r="I63" s="33"/>
+      <c r="J63" s="33"/>
+      <c r="K63" s="33"/>
+      <c r="L63" s="33"/>
+      <c r="M63" s="33"/>
+      <c r="N63" s="33"/>
+      <c r="O63" s="33"/>
+      <c r="P63" s="33"/>
+      <c r="Q63" s="33"/>
+      <c r="R63" s="33"/>
+      <c r="S63" s="33"/>
+      <c r="T63" s="33"/>
+      <c r="U63" s="33"/>
+      <c r="V63" s="33"/>
+      <c r="W63" s="33"/>
+      <c r="X63" s="33"/>
+      <c r="Y63" s="33"/>
+      <c r="Z63" s="33"/>
+      <c r="AA63" s="33"/>
+      <c r="AB63" s="33"/>
+      <c r="AC63" s="33"/>
+      <c r="AD63" s="33"/>
+      <c r="AE63" s="33"/>
+      <c r="AF63" s="33"/>
+      <c r="AG63" s="33"/>
+      <c r="AH63" s="33"/>
+      <c r="AI63" s="34"/>
       <c r="AJ63" s="13">
         <f t="shared" ref="AJ63:AP63" si="0">SUM(AJ7:AJ55)</f>
         <v>0</v>
@@ -5436,13 +5436,66 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AQ63" s="61" t="s">
+      <c r="AQ63" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="AR63" s="62"/>
+      <c r="AR63" s="47"/>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="w6+d9vq8zxqtwz/8oCCG3BYbliNfWePL8hHRwEiEML+sUltfeBK5YuPzjAH7ITn1+ejY8h++fEUHCYBUW55TsA==" saltValue="JcN4p5PNyCVpkOl5Pyg2uQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="68">
+    <mergeCell ref="E1:V1"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="E2:L2"/>
+    <mergeCell ref="E4:AQ4"/>
+    <mergeCell ref="AQ5:AQ6"/>
+    <mergeCell ref="X2:AB2"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="Q2:W2"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="M3:P3"/>
+    <mergeCell ref="AP5:AP6"/>
+    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="A28:A34"/>
+    <mergeCell ref="A14:A20"/>
+    <mergeCell ref="B3:D4"/>
+    <mergeCell ref="AR42:AR48"/>
+    <mergeCell ref="AQ28:AQ34"/>
+    <mergeCell ref="A35:A41"/>
+    <mergeCell ref="AJ5:AJ6"/>
+    <mergeCell ref="B35:B41"/>
+    <mergeCell ref="AR28:AR34"/>
+    <mergeCell ref="B28:B34"/>
+    <mergeCell ref="A21:A27"/>
+    <mergeCell ref="AQ14:AQ20"/>
+    <mergeCell ref="AK5:AK6"/>
+    <mergeCell ref="AM5:AM6"/>
+    <mergeCell ref="AL5:AL6"/>
+    <mergeCell ref="AQ35:AQ41"/>
+    <mergeCell ref="C7:C13"/>
+    <mergeCell ref="B7:B13"/>
+    <mergeCell ref="AR7:AR13"/>
+    <mergeCell ref="B21:B27"/>
+    <mergeCell ref="AQ7:AQ13"/>
+    <mergeCell ref="AQ21:AQ27"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="AR5:AR6"/>
+    <mergeCell ref="AO5:AO6"/>
+    <mergeCell ref="C21:C27"/>
+    <mergeCell ref="AN5:AN6"/>
+    <mergeCell ref="AR21:AR27"/>
+    <mergeCell ref="B56:B62"/>
+    <mergeCell ref="AR56:AR62"/>
+    <mergeCell ref="A49:A55"/>
+    <mergeCell ref="C42:C48"/>
+    <mergeCell ref="C49:C55"/>
+    <mergeCell ref="AR49:AR55"/>
+    <mergeCell ref="C56:C62"/>
+    <mergeCell ref="A56:A62"/>
+    <mergeCell ref="A42:A48"/>
+    <mergeCell ref="AQ42:AQ48"/>
+    <mergeCell ref="B49:B55"/>
     <mergeCell ref="B1:D2"/>
     <mergeCell ref="AR14:AR20"/>
     <mergeCell ref="I3:L3"/>
@@ -5459,58 +5512,6 @@
     <mergeCell ref="C28:C34"/>
     <mergeCell ref="AQ63:AR63"/>
     <mergeCell ref="E3:H3"/>
-    <mergeCell ref="B56:B62"/>
-    <mergeCell ref="AR56:AR62"/>
-    <mergeCell ref="A49:A55"/>
-    <mergeCell ref="C42:C48"/>
-    <mergeCell ref="C49:C55"/>
-    <mergeCell ref="AR49:AR55"/>
-    <mergeCell ref="C56:C62"/>
-    <mergeCell ref="A56:A62"/>
-    <mergeCell ref="A42:A48"/>
-    <mergeCell ref="AQ42:AQ48"/>
-    <mergeCell ref="B49:B55"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="AR5:AR6"/>
-    <mergeCell ref="AO5:AO6"/>
-    <mergeCell ref="C21:C27"/>
-    <mergeCell ref="AN5:AN6"/>
-    <mergeCell ref="AR21:AR27"/>
-    <mergeCell ref="AQ35:AQ41"/>
-    <mergeCell ref="C7:C13"/>
-    <mergeCell ref="B7:B13"/>
-    <mergeCell ref="AR7:AR13"/>
-    <mergeCell ref="B21:B27"/>
-    <mergeCell ref="AQ7:AQ13"/>
-    <mergeCell ref="A7:A13"/>
-    <mergeCell ref="A28:A34"/>
-    <mergeCell ref="A14:A20"/>
-    <mergeCell ref="B3:D4"/>
-    <mergeCell ref="AR42:AR48"/>
-    <mergeCell ref="AQ28:AQ34"/>
-    <mergeCell ref="A35:A41"/>
-    <mergeCell ref="AJ5:AJ6"/>
-    <mergeCell ref="B35:B41"/>
-    <mergeCell ref="AR28:AR34"/>
-    <mergeCell ref="B28:B34"/>
-    <mergeCell ref="A21:A27"/>
-    <mergeCell ref="AQ14:AQ20"/>
-    <mergeCell ref="AK5:AK6"/>
-    <mergeCell ref="AM5:AM6"/>
-    <mergeCell ref="AL5:AL6"/>
-    <mergeCell ref="AQ21:AQ27"/>
-    <mergeCell ref="E1:V1"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="E2:L2"/>
-    <mergeCell ref="E4:AQ4"/>
-    <mergeCell ref="AQ5:AQ6"/>
-    <mergeCell ref="X2:AB2"/>
-    <mergeCell ref="M2:P2"/>
-    <mergeCell ref="Q2:W2"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="M3:P3"/>
-    <mergeCell ref="AP5:AP6"/>
   </mergeCells>
   <conditionalFormatting sqref="E6">
     <cfRule type="expression" dxfId="61" priority="188">

--- a/public/moduli/FoglioPresenze_StudioBaiocco.xlsx
+++ b/public/moduli/FoglioPresenze_StudioBaiocco.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Desktop/sito_mamma/public/moduli/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A740E29-DE19-8E4C-A1AA-C834A5EAA825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D70AA98-2877-1445-8444-B70B592AFA2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -728,100 +728,8 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="justify"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="justify"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="justify"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="9" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="justify"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -831,6 +739,12 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -861,6 +775,92 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="justify"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="justify"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="justify"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="23" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="justify"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1991,29 +1991,29 @@
   <sheetData>
     <row r="1" spans="1:44" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14"/>
-      <c r="B1" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
-      <c r="S1" s="28"/>
-      <c r="T1" s="28"/>
-      <c r="U1" s="28"/>
-      <c r="V1" s="28"/>
+      <c r="B1" s="59" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
+      <c r="T1" s="23"/>
+      <c r="U1" s="23"/>
+      <c r="V1" s="23"/>
       <c r="W1" s="15"/>
       <c r="X1" s="15"/>
       <c r="Y1" s="15"/>
@@ -2039,41 +2039,41 @@
     </row>
     <row r="2" spans="1:44" ht="29" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="58" t="s">
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="64">
-        <v>3</v>
-      </c>
-      <c r="N2" s="65"/>
-      <c r="O2" s="65"/>
-      <c r="P2" s="66"/>
-      <c r="Q2" s="67" t="s">
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="25"/>
+      <c r="M2" s="32">
+        <v>4</v>
+      </c>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="34"/>
+      <c r="Q2" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="R2" s="58"/>
-      <c r="S2" s="58"/>
-      <c r="T2" s="58"/>
-      <c r="U2" s="58"/>
-      <c r="V2" s="58"/>
-      <c r="W2" s="59"/>
-      <c r="X2" s="61">
+      <c r="R2" s="24"/>
+      <c r="S2" s="24"/>
+      <c r="T2" s="24"/>
+      <c r="U2" s="24"/>
+      <c r="V2" s="24"/>
+      <c r="W2" s="25"/>
+      <c r="X2" s="29">
         <v>2026</v>
       </c>
-      <c r="Y2" s="62"/>
-      <c r="Z2" s="62"/>
-      <c r="AA2" s="62"/>
-      <c r="AB2" s="63"/>
+      <c r="Y2" s="30"/>
+      <c r="Z2" s="30"/>
+      <c r="AA2" s="30"/>
+      <c r="AB2" s="31"/>
       <c r="AC2" s="15"/>
       <c r="AD2" s="15"/>
       <c r="AE2" s="15"/>
@@ -2093,29 +2093,29 @@
     </row>
     <row r="3" spans="1:44" ht="19" x14ac:dyDescent="0.2">
       <c r="A3" s="14"/>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-      <c r="O3" s="68"/>
-      <c r="P3" s="68"/>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
-      <c r="V3" s="28"/>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+      <c r="O3" s="36"/>
+      <c r="P3" s="36"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
+      <c r="V3" s="23"/>
       <c r="W3" s="15"/>
       <c r="X3" s="15"/>
       <c r="Y3" s="15"/>
@@ -2141,61 +2141,61 @@
     </row>
     <row r="4" spans="1:44" ht="24" x14ac:dyDescent="0.2">
       <c r="A4" s="14"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="60" t="s">
+      <c r="B4" s="40"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="60"/>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="60"/>
-      <c r="R4" s="60"/>
-      <c r="S4" s="60"/>
-      <c r="T4" s="60"/>
-      <c r="U4" s="60"/>
-      <c r="V4" s="60"/>
-      <c r="W4" s="60"/>
-      <c r="X4" s="60"/>
-      <c r="Y4" s="60"/>
-      <c r="Z4" s="60"/>
-      <c r="AA4" s="60"/>
-      <c r="AB4" s="60"/>
-      <c r="AC4" s="60"/>
-      <c r="AD4" s="60"/>
-      <c r="AE4" s="60"/>
-      <c r="AF4" s="60"/>
-      <c r="AG4" s="60"/>
-      <c r="AH4" s="60"/>
-      <c r="AI4" s="60"/>
-      <c r="AJ4" s="60"/>
-      <c r="AK4" s="60"/>
-      <c r="AL4" s="60"/>
-      <c r="AM4" s="60"/>
-      <c r="AN4" s="60"/>
-      <c r="AO4" s="60"/>
-      <c r="AP4" s="60"/>
-      <c r="AQ4" s="60"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+      <c r="J4" s="26"/>
+      <c r="K4" s="26"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="26"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
+      <c r="R4" s="26"/>
+      <c r="S4" s="26"/>
+      <c r="T4" s="26"/>
+      <c r="U4" s="26"/>
+      <c r="V4" s="26"/>
+      <c r="W4" s="26"/>
+      <c r="X4" s="26"/>
+      <c r="Y4" s="26"/>
+      <c r="Z4" s="26"/>
+      <c r="AA4" s="26"/>
+      <c r="AB4" s="26"/>
+      <c r="AC4" s="26"/>
+      <c r="AD4" s="26"/>
+      <c r="AE4" s="26"/>
+      <c r="AF4" s="26"/>
+      <c r="AG4" s="26"/>
+      <c r="AH4" s="26"/>
+      <c r="AI4" s="26"/>
+      <c r="AJ4" s="26"/>
+      <c r="AK4" s="26"/>
+      <c r="AL4" s="26"/>
+      <c r="AM4" s="26"/>
+      <c r="AN4" s="26"/>
+      <c r="AO4" s="26"/>
+      <c r="AP4" s="26"/>
+      <c r="AQ4" s="26"/>
       <c r="AR4" s="16"/>
     </row>
     <row r="5" spans="1:44" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="14"/>
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="51"/>
+      <c r="D5" s="58"/>
       <c r="E5" s="1">
         <v>1</v>
       </c>
@@ -2289,179 +2289,179 @@
       <c r="AI5" s="1">
         <v>31</v>
       </c>
-      <c r="AJ5" s="52" t="s">
+      <c r="AJ5" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="AK5" s="52" t="s">
+      <c r="AK5" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="AL5" s="52" t="s">
+      <c r="AL5" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="AM5" s="52" t="s">
+      <c r="AM5" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="AN5" s="52" t="s">
+      <c r="AN5" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="AO5" s="52" t="s">
+      <c r="AO5" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="AP5" s="52" t="s">
+      <c r="AP5" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="AQ5" s="52" t="s">
+      <c r="AQ5" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="AR5" s="52" t="s">
+      <c r="AR5" s="27" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:44" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="14"/>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
+      <c r="B6" s="57"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
       <c r="E6" s="2" t="str">
         <f>IFERROR(IF(1&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,1),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>D</v>
+        <v>M</v>
       </c>
       <c r="F6" s="2" t="str">
         <f>IFERROR(IF(2&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,2),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>L</v>
+        <v>G</v>
       </c>
       <c r="G6" s="2" t="str">
         <f>IFERROR(IF(3&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,3),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>M</v>
+        <v>V</v>
       </c>
       <c r="H6" s="2" t="str">
         <f>IFERROR(IF(4&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,4),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="I6" s="2" t="str">
         <f>IFERROR(IF(5&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,5),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>G</v>
+        <v>D</v>
       </c>
       <c r="J6" s="2" t="str">
         <f>IFERROR(IF(6&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,6),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>V</v>
+        <v>L</v>
       </c>
       <c r="K6" s="2" t="str">
         <f>IFERROR(IF(7&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,7),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="L6" s="2" t="str">
         <f>IFERROR(IF(8&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,8),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>D</v>
+        <v>M</v>
       </c>
       <c r="M6" s="2" t="str">
         <f>IFERROR(IF(9&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,9),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>L</v>
+        <v>G</v>
       </c>
       <c r="N6" s="2" t="str">
         <f>IFERROR(IF(10&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,10),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>M</v>
+        <v>V</v>
       </c>
       <c r="O6" s="2" t="str">
         <f>IFERROR(IF(11&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,11),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="P6" s="2" t="str">
         <f>IFERROR(IF(12&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,12),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>G</v>
+        <v>D</v>
       </c>
       <c r="Q6" s="2" t="str">
         <f>IFERROR(IF(13&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,13),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>V</v>
+        <v>L</v>
       </c>
       <c r="R6" s="2" t="str">
         <f>IFERROR(IF(14&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,14),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="S6" s="2" t="str">
         <f>IFERROR(IF(15&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,15),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>D</v>
+        <v>M</v>
       </c>
       <c r="T6" s="2" t="str">
         <f>IFERROR(IF(16&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,16),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>L</v>
+        <v>G</v>
       </c>
       <c r="U6" s="2" t="str">
         <f>IFERROR(IF(17&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,17),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>M</v>
+        <v>V</v>
       </c>
       <c r="V6" s="2" t="str">
         <f>IFERROR(IF(18&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,18),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="W6" s="2" t="str">
         <f>IFERROR(IF(19&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,19),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>G</v>
+        <v>D</v>
       </c>
       <c r="X6" s="2" t="str">
         <f>IFERROR(IF(20&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,20),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>V</v>
+        <v>L</v>
       </c>
       <c r="Y6" s="2" t="str">
         <f>IFERROR(IF(21&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,21),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="Z6" s="2" t="str">
         <f>IFERROR(IF(22&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,22),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>D</v>
+        <v>M</v>
       </c>
       <c r="AA6" s="2" t="str">
         <f>IFERROR(IF(23&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,23),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>L</v>
+        <v>G</v>
       </c>
       <c r="AB6" s="2" t="str">
         <f>IFERROR(IF(24&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,24),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>M</v>
+        <v>V</v>
       </c>
       <c r="AC6" s="2" t="str">
         <f>IFERROR(IF(25&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,25),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>M</v>
+        <v>S</v>
       </c>
       <c r="AD6" s="2" t="str">
         <f>IFERROR(IF(26&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,26),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>G</v>
+        <v>D</v>
       </c>
       <c r="AE6" s="2" t="str">
         <f>IFERROR(IF(27&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,27),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>V</v>
+        <v>L</v>
       </c>
       <c r="AF6" s="2" t="str">
         <f>IFERROR(IF(28&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,28),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>S</v>
+        <v>M</v>
       </c>
       <c r="AG6" s="2" t="str">
         <f>IFERROR(IF(29&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,29),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>D</v>
+        <v>M</v>
       </c>
       <c r="AH6" s="2" t="str">
         <f>IFERROR(IF(30&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,30),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>L</v>
+        <v>G</v>
       </c>
       <c r="AI6" s="2" t="str">
         <f>IFERROR(IF(31&gt;DAY(EOMONTH(DATE($X$2,$M$2,1),0)),"",CHOOSE(WEEKDAY(DATE($X$2,$M$2,31),2),"L","M","M","G","V","S","D")),"")</f>
-        <v>M</v>
-      </c>
-      <c r="AJ6" s="53"/>
-      <c r="AK6" s="53"/>
-      <c r="AL6" s="53"/>
-      <c r="AM6" s="53"/>
-      <c r="AN6" s="53"/>
-      <c r="AO6" s="53"/>
-      <c r="AP6" s="53"/>
-      <c r="AQ6" s="53"/>
-      <c r="AR6" s="53"/>
+        <v/>
+      </c>
+      <c r="AJ6" s="28"/>
+      <c r="AK6" s="28"/>
+      <c r="AL6" s="28"/>
+      <c r="AM6" s="28"/>
+      <c r="AN6" s="28"/>
+      <c r="AO6" s="28"/>
+      <c r="AP6" s="28"/>
+      <c r="AQ6" s="28"/>
+      <c r="AR6" s="28"/>
     </row>
     <row r="7" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="48"/>
-      <c r="B7" s="54">
+      <c r="A7" s="37"/>
+      <c r="B7" s="53">
         <v>1</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="50" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="3" t="s">
@@ -2508,16 +2508,16 @@
       <c r="AN7" s="5"/>
       <c r="AO7" s="5"/>
       <c r="AP7" s="5"/>
-      <c r="AQ7" s="56">
+      <c r="AQ7" s="55">
         <f>COUNTIF(E7:AI7,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR7" s="55"/>
+      <c r="AR7" s="54"/>
     </row>
     <row r="8" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="49"/>
-      <c r="B8" s="41"/>
-      <c r="C8" s="30"/>
+      <c r="A8" s="38"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="51"/>
       <c r="D8" s="6" t="s">
         <v>17</v>
       </c>
@@ -2562,13 +2562,13 @@
       <c r="AN8" s="5"/>
       <c r="AO8" s="5"/>
       <c r="AP8" s="5"/>
-      <c r="AQ8" s="36"/>
-      <c r="AR8" s="26"/>
+      <c r="AQ8" s="45"/>
+      <c r="AR8" s="42"/>
     </row>
     <row r="9" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="49"/>
-      <c r="B9" s="41"/>
-      <c r="C9" s="30"/>
+      <c r="A9" s="38"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="51"/>
       <c r="D9" s="7" t="s">
         <v>18</v>
       </c>
@@ -2613,13 +2613,13 @@
       <c r="AN9" s="5"/>
       <c r="AO9" s="5"/>
       <c r="AP9" s="5"/>
-      <c r="AQ9" s="36"/>
-      <c r="AR9" s="26"/>
+      <c r="AQ9" s="45"/>
+      <c r="AR9" s="42"/>
     </row>
     <row r="10" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="49"/>
-      <c r="B10" s="41"/>
-      <c r="C10" s="30"/>
+      <c r="A10" s="38"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="51"/>
       <c r="D10" s="8" t="s">
         <v>19</v>
       </c>
@@ -2664,13 +2664,13 @@
       <c r="AN10" s="5"/>
       <c r="AO10" s="5"/>
       <c r="AP10" s="5"/>
-      <c r="AQ10" s="36"/>
-      <c r="AR10" s="26"/>
+      <c r="AQ10" s="45"/>
+      <c r="AR10" s="42"/>
     </row>
     <row r="11" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="49"/>
-      <c r="B11" s="41"/>
-      <c r="C11" s="30"/>
+      <c r="A11" s="38"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="51"/>
       <c r="D11" s="9" t="s">
         <v>20</v>
       </c>
@@ -2715,13 +2715,13 @@
       </c>
       <c r="AO11" s="5"/>
       <c r="AP11" s="5"/>
-      <c r="AQ11" s="36"/>
-      <c r="AR11" s="26"/>
+      <c r="AQ11" s="45"/>
+      <c r="AR11" s="42"/>
     </row>
     <row r="12" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="49"/>
-      <c r="B12" s="41"/>
-      <c r="C12" s="30"/>
+      <c r="A12" s="38"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="51"/>
       <c r="D12" s="9" t="s">
         <v>21</v>
       </c>
@@ -2766,13 +2766,13 @@
         <v>0</v>
       </c>
       <c r="AP12" s="5"/>
-      <c r="AQ12" s="36"/>
-      <c r="AR12" s="26"/>
+      <c r="AQ12" s="45"/>
+      <c r="AR12" s="42"/>
     </row>
     <row r="13" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="49"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="31"/>
+      <c r="A13" s="38"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="52"/>
       <c r="D13" s="10" t="s">
         <v>22</v>
       </c>
@@ -2817,15 +2817,15 @@
         <f>SUM(E13:AI13)</f>
         <v>0</v>
       </c>
-      <c r="AQ13" s="37"/>
-      <c r="AR13" s="27"/>
+      <c r="AQ13" s="46"/>
+      <c r="AR13" s="43"/>
     </row>
     <row r="14" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="48"/>
-      <c r="B14" s="40">
+      <c r="A14" s="37"/>
+      <c r="B14" s="47">
         <v>2</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" s="50" t="s">
         <v>15</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -2872,16 +2872,16 @@
       <c r="AN14" s="5"/>
       <c r="AO14" s="5"/>
       <c r="AP14" s="5"/>
-      <c r="AQ14" s="35">
+      <c r="AQ14" s="44">
         <f>COUNTIF(E14:AI14,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR14" s="25"/>
+      <c r="AR14" s="41"/>
     </row>
     <row r="15" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="49"/>
-      <c r="B15" s="41"/>
-      <c r="C15" s="30"/>
+      <c r="A15" s="38"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="51"/>
       <c r="D15" s="6" t="s">
         <v>17</v>
       </c>
@@ -2926,13 +2926,13 @@
       <c r="AN15" s="5"/>
       <c r="AO15" s="5"/>
       <c r="AP15" s="5"/>
-      <c r="AQ15" s="36"/>
-      <c r="AR15" s="26"/>
+      <c r="AQ15" s="45"/>
+      <c r="AR15" s="42"/>
     </row>
     <row r="16" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="49"/>
-      <c r="B16" s="41"/>
-      <c r="C16" s="30"/>
+      <c r="A16" s="38"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="51"/>
       <c r="D16" s="7" t="s">
         <v>18</v>
       </c>
@@ -2977,13 +2977,13 @@
       <c r="AN16" s="5"/>
       <c r="AO16" s="5"/>
       <c r="AP16" s="5"/>
-      <c r="AQ16" s="36"/>
-      <c r="AR16" s="26"/>
+      <c r="AQ16" s="45"/>
+      <c r="AR16" s="42"/>
     </row>
     <row r="17" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="49"/>
-      <c r="B17" s="41"/>
-      <c r="C17" s="30"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="51"/>
       <c r="D17" s="8" t="s">
         <v>19</v>
       </c>
@@ -3028,13 +3028,13 @@
       <c r="AN17" s="5"/>
       <c r="AO17" s="5"/>
       <c r="AP17" s="5"/>
-      <c r="AQ17" s="36"/>
-      <c r="AR17" s="26"/>
+      <c r="AQ17" s="45"/>
+      <c r="AR17" s="42"/>
     </row>
     <row r="18" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="49"/>
-      <c r="B18" s="41"/>
-      <c r="C18" s="30"/>
+      <c r="A18" s="38"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="51"/>
       <c r="D18" s="9" t="s">
         <v>20</v>
       </c>
@@ -3079,13 +3079,13 @@
       </c>
       <c r="AO18" s="5"/>
       <c r="AP18" s="5"/>
-      <c r="AQ18" s="36"/>
-      <c r="AR18" s="26"/>
+      <c r="AQ18" s="45"/>
+      <c r="AR18" s="42"/>
     </row>
     <row r="19" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="49"/>
-      <c r="B19" s="41"/>
-      <c r="C19" s="30"/>
+      <c r="A19" s="38"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="51"/>
       <c r="D19" s="9" t="s">
         <v>21</v>
       </c>
@@ -3130,13 +3130,13 @@
         <v>0</v>
       </c>
       <c r="AP19" s="5"/>
-      <c r="AQ19" s="36"/>
-      <c r="AR19" s="26"/>
+      <c r="AQ19" s="45"/>
+      <c r="AR19" s="42"/>
     </row>
     <row r="20" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="49"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="31"/>
+      <c r="A20" s="38"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="52"/>
       <c r="D20" s="10" t="s">
         <v>22</v>
       </c>
@@ -3181,15 +3181,15 @@
         <f>SUM(E20:AI20)</f>
         <v>0</v>
       </c>
-      <c r="AQ20" s="37"/>
-      <c r="AR20" s="27"/>
+      <c r="AQ20" s="46"/>
+      <c r="AR20" s="43"/>
     </row>
     <row r="21" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="48"/>
-      <c r="B21" s="40">
+      <c r="A21" s="37"/>
+      <c r="B21" s="47">
         <v>3</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="50" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3" t="s">
@@ -3236,16 +3236,16 @@
       <c r="AN21" s="5"/>
       <c r="AO21" s="5"/>
       <c r="AP21" s="5"/>
-      <c r="AQ21" s="35">
+      <c r="AQ21" s="44">
         <f>COUNTIF(E21:AI21,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR21" s="25"/>
+      <c r="AR21" s="41"/>
     </row>
     <row r="22" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="49"/>
-      <c r="B22" s="41"/>
-      <c r="C22" s="30"/>
+      <c r="A22" s="38"/>
+      <c r="B22" s="48"/>
+      <c r="C22" s="51"/>
       <c r="D22" s="6" t="s">
         <v>17</v>
       </c>
@@ -3290,13 +3290,13 @@
       <c r="AN22" s="5"/>
       <c r="AO22" s="5"/>
       <c r="AP22" s="5"/>
-      <c r="AQ22" s="36"/>
-      <c r="AR22" s="26"/>
+      <c r="AQ22" s="45"/>
+      <c r="AR22" s="42"/>
     </row>
     <row r="23" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="49"/>
-      <c r="B23" s="41"/>
-      <c r="C23" s="30"/>
+      <c r="A23" s="38"/>
+      <c r="B23" s="48"/>
+      <c r="C23" s="51"/>
       <c r="D23" s="7" t="s">
         <v>18</v>
       </c>
@@ -3341,13 +3341,13 @@
       <c r="AN23" s="5"/>
       <c r="AO23" s="5"/>
       <c r="AP23" s="5"/>
-      <c r="AQ23" s="36"/>
-      <c r="AR23" s="26"/>
+      <c r="AQ23" s="45"/>
+      <c r="AR23" s="42"/>
     </row>
     <row r="24" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="49"/>
-      <c r="B24" s="41"/>
-      <c r="C24" s="30"/>
+      <c r="A24" s="38"/>
+      <c r="B24" s="48"/>
+      <c r="C24" s="51"/>
       <c r="D24" s="8" t="s">
         <v>19</v>
       </c>
@@ -3392,13 +3392,13 @@
       <c r="AN24" s="5"/>
       <c r="AO24" s="5"/>
       <c r="AP24" s="5"/>
-      <c r="AQ24" s="36"/>
-      <c r="AR24" s="26"/>
+      <c r="AQ24" s="45"/>
+      <c r="AR24" s="42"/>
     </row>
     <row r="25" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="49"/>
-      <c r="B25" s="41"/>
-      <c r="C25" s="30"/>
+      <c r="A25" s="38"/>
+      <c r="B25" s="48"/>
+      <c r="C25" s="51"/>
       <c r="D25" s="9" t="s">
         <v>20</v>
       </c>
@@ -3443,13 +3443,13 @@
       </c>
       <c r="AO25" s="5"/>
       <c r="AP25" s="5"/>
-      <c r="AQ25" s="36"/>
-      <c r="AR25" s="26"/>
+      <c r="AQ25" s="45"/>
+      <c r="AR25" s="42"/>
     </row>
     <row r="26" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="49"/>
-      <c r="B26" s="41"/>
-      <c r="C26" s="30"/>
+      <c r="A26" s="38"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="51"/>
       <c r="D26" s="9" t="s">
         <v>21</v>
       </c>
@@ -3494,13 +3494,13 @@
         <v>0</v>
       </c>
       <c r="AP26" s="5"/>
-      <c r="AQ26" s="36"/>
-      <c r="AR26" s="26"/>
+      <c r="AQ26" s="45"/>
+      <c r="AR26" s="42"/>
     </row>
     <row r="27" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="49"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="31"/>
+      <c r="A27" s="38"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="52"/>
       <c r="D27" s="10" t="s">
         <v>22</v>
       </c>
@@ -3545,15 +3545,15 @@
         <f>SUM(E27:AI27)</f>
         <v>0</v>
       </c>
-      <c r="AQ27" s="37"/>
-      <c r="AR27" s="27"/>
+      <c r="AQ27" s="46"/>
+      <c r="AR27" s="43"/>
     </row>
     <row r="28" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="48"/>
-      <c r="B28" s="40">
+      <c r="A28" s="37"/>
+      <c r="B28" s="47">
         <v>4</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="50" t="s">
         <v>15</v>
       </c>
       <c r="D28" s="3" t="s">
@@ -3600,16 +3600,16 @@
       <c r="AN28" s="5"/>
       <c r="AO28" s="5"/>
       <c r="AP28" s="5"/>
-      <c r="AQ28" s="35">
+      <c r="AQ28" s="44">
         <f>COUNTIF(E28:AI28,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR28" s="25"/>
+      <c r="AR28" s="41"/>
     </row>
     <row r="29" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="49"/>
-      <c r="B29" s="41"/>
-      <c r="C29" s="30"/>
+      <c r="A29" s="38"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="51"/>
       <c r="D29" s="6" t="s">
         <v>17</v>
       </c>
@@ -3654,13 +3654,13 @@
       <c r="AN29" s="5"/>
       <c r="AO29" s="5"/>
       <c r="AP29" s="5"/>
-      <c r="AQ29" s="36"/>
-      <c r="AR29" s="26"/>
+      <c r="AQ29" s="45"/>
+      <c r="AR29" s="42"/>
     </row>
     <row r="30" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="49"/>
-      <c r="B30" s="41"/>
-      <c r="C30" s="30"/>
+      <c r="A30" s="38"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="51"/>
       <c r="D30" s="7" t="s">
         <v>18</v>
       </c>
@@ -3705,13 +3705,13 @@
       <c r="AN30" s="5"/>
       <c r="AO30" s="5"/>
       <c r="AP30" s="5"/>
-      <c r="AQ30" s="36"/>
-      <c r="AR30" s="26"/>
+      <c r="AQ30" s="45"/>
+      <c r="AR30" s="42"/>
     </row>
     <row r="31" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="49"/>
-      <c r="B31" s="41"/>
-      <c r="C31" s="30"/>
+      <c r="A31" s="38"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="51"/>
       <c r="D31" s="8" t="s">
         <v>19</v>
       </c>
@@ -3756,13 +3756,13 @@
       <c r="AN31" s="5"/>
       <c r="AO31" s="5"/>
       <c r="AP31" s="5"/>
-      <c r="AQ31" s="36"/>
-      <c r="AR31" s="26"/>
+      <c r="AQ31" s="45"/>
+      <c r="AR31" s="42"/>
     </row>
     <row r="32" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="49"/>
-      <c r="B32" s="41"/>
-      <c r="C32" s="30"/>
+      <c r="A32" s="38"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="51"/>
       <c r="D32" s="9" t="s">
         <v>20</v>
       </c>
@@ -3807,13 +3807,13 @@
       </c>
       <c r="AO32" s="5"/>
       <c r="AP32" s="5"/>
-      <c r="AQ32" s="36"/>
-      <c r="AR32" s="26"/>
+      <c r="AQ32" s="45"/>
+      <c r="AR32" s="42"/>
     </row>
     <row r="33" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="49"/>
-      <c r="B33" s="41"/>
-      <c r="C33" s="30"/>
+      <c r="A33" s="38"/>
+      <c r="B33" s="48"/>
+      <c r="C33" s="51"/>
       <c r="D33" s="9" t="s">
         <v>21</v>
       </c>
@@ -3858,13 +3858,13 @@
         <v>0</v>
       </c>
       <c r="AP33" s="5"/>
-      <c r="AQ33" s="36"/>
-      <c r="AR33" s="26"/>
+      <c r="AQ33" s="45"/>
+      <c r="AR33" s="42"/>
     </row>
     <row r="34" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="49"/>
-      <c r="B34" s="42"/>
-      <c r="C34" s="31"/>
+      <c r="A34" s="38"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="52"/>
       <c r="D34" s="10" t="s">
         <v>22</v>
       </c>
@@ -3909,15 +3909,15 @@
         <f>SUM(E34:AI34)</f>
         <v>0</v>
       </c>
-      <c r="AQ34" s="37"/>
-      <c r="AR34" s="27"/>
+      <c r="AQ34" s="46"/>
+      <c r="AR34" s="43"/>
     </row>
     <row r="35" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="48"/>
-      <c r="B35" s="40">
+      <c r="A35" s="37"/>
+      <c r="B35" s="47">
         <v>5</v>
       </c>
-      <c r="C35" s="29" t="s">
+      <c r="C35" s="50" t="s">
         <v>15</v>
       </c>
       <c r="D35" s="3" t="s">
@@ -3964,16 +3964,16 @@
       <c r="AN35" s="5"/>
       <c r="AO35" s="5"/>
       <c r="AP35" s="5"/>
-      <c r="AQ35" s="35">
+      <c r="AQ35" s="44">
         <f>COUNTIF(E35:AI35,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR35" s="25"/>
+      <c r="AR35" s="41"/>
     </row>
     <row r="36" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="49"/>
-      <c r="B36" s="41"/>
-      <c r="C36" s="30"/>
+      <c r="A36" s="38"/>
+      <c r="B36" s="48"/>
+      <c r="C36" s="51"/>
       <c r="D36" s="6" t="s">
         <v>17</v>
       </c>
@@ -4018,13 +4018,13 @@
       <c r="AN36" s="5"/>
       <c r="AO36" s="5"/>
       <c r="AP36" s="5"/>
-      <c r="AQ36" s="36"/>
-      <c r="AR36" s="26"/>
+      <c r="AQ36" s="45"/>
+      <c r="AR36" s="42"/>
     </row>
     <row r="37" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="49"/>
-      <c r="B37" s="41"/>
-      <c r="C37" s="30"/>
+      <c r="A37" s="38"/>
+      <c r="B37" s="48"/>
+      <c r="C37" s="51"/>
       <c r="D37" s="7" t="s">
         <v>18</v>
       </c>
@@ -4069,13 +4069,13 @@
       <c r="AN37" s="5"/>
       <c r="AO37" s="5"/>
       <c r="AP37" s="5"/>
-      <c r="AQ37" s="36"/>
-      <c r="AR37" s="26"/>
+      <c r="AQ37" s="45"/>
+      <c r="AR37" s="42"/>
     </row>
     <row r="38" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="49"/>
-      <c r="B38" s="41"/>
-      <c r="C38" s="30"/>
+      <c r="A38" s="38"/>
+      <c r="B38" s="48"/>
+      <c r="C38" s="51"/>
       <c r="D38" s="8" t="s">
         <v>19</v>
       </c>
@@ -4120,13 +4120,13 @@
       <c r="AN38" s="5"/>
       <c r="AO38" s="5"/>
       <c r="AP38" s="5"/>
-      <c r="AQ38" s="36"/>
-      <c r="AR38" s="26"/>
+      <c r="AQ38" s="45"/>
+      <c r="AR38" s="42"/>
     </row>
     <row r="39" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="49"/>
-      <c r="B39" s="41"/>
-      <c r="C39" s="30"/>
+      <c r="A39" s="38"/>
+      <c r="B39" s="48"/>
+      <c r="C39" s="51"/>
       <c r="D39" s="9" t="s">
         <v>20</v>
       </c>
@@ -4171,13 +4171,13 @@
       </c>
       <c r="AO39" s="5"/>
       <c r="AP39" s="5"/>
-      <c r="AQ39" s="36"/>
-      <c r="AR39" s="26"/>
+      <c r="AQ39" s="45"/>
+      <c r="AR39" s="42"/>
     </row>
     <row r="40" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="49"/>
-      <c r="B40" s="41"/>
-      <c r="C40" s="30"/>
+      <c r="A40" s="38"/>
+      <c r="B40" s="48"/>
+      <c r="C40" s="51"/>
       <c r="D40" s="9" t="s">
         <v>21</v>
       </c>
@@ -4222,13 +4222,13 @@
         <v>0</v>
       </c>
       <c r="AP40" s="5"/>
-      <c r="AQ40" s="36"/>
-      <c r="AR40" s="26"/>
+      <c r="AQ40" s="45"/>
+      <c r="AR40" s="42"/>
     </row>
     <row r="41" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="49"/>
-      <c r="B41" s="42"/>
-      <c r="C41" s="31"/>
+      <c r="A41" s="38"/>
+      <c r="B41" s="49"/>
+      <c r="C41" s="52"/>
       <c r="D41" s="10" t="s">
         <v>22</v>
       </c>
@@ -4273,15 +4273,15 @@
         <f>SUM(E41:AI41)</f>
         <v>0</v>
       </c>
-      <c r="AQ41" s="37"/>
-      <c r="AR41" s="27"/>
+      <c r="AQ41" s="46"/>
+      <c r="AR41" s="43"/>
     </row>
     <row r="42" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="48"/>
-      <c r="B42" s="40">
+      <c r="A42" s="37"/>
+      <c r="B42" s="47">
         <v>6</v>
       </c>
-      <c r="C42" s="29" t="s">
+      <c r="C42" s="50" t="s">
         <v>15</v>
       </c>
       <c r="D42" s="3" t="s">
@@ -4328,16 +4328,16 @@
       <c r="AN42" s="5"/>
       <c r="AO42" s="5"/>
       <c r="AP42" s="5"/>
-      <c r="AQ42" s="35">
+      <c r="AQ42" s="44">
         <f>COUNTIF(E42:AI42,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR42" s="25"/>
+      <c r="AR42" s="41"/>
     </row>
     <row r="43" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="49"/>
-      <c r="B43" s="41"/>
-      <c r="C43" s="30"/>
+      <c r="A43" s="38"/>
+      <c r="B43" s="48"/>
+      <c r="C43" s="51"/>
       <c r="D43" s="6" t="s">
         <v>17</v>
       </c>
@@ -4382,13 +4382,13 @@
       <c r="AN43" s="5"/>
       <c r="AO43" s="5"/>
       <c r="AP43" s="5"/>
-      <c r="AQ43" s="36"/>
-      <c r="AR43" s="26"/>
+      <c r="AQ43" s="45"/>
+      <c r="AR43" s="42"/>
     </row>
     <row r="44" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="49"/>
-      <c r="B44" s="41"/>
-      <c r="C44" s="30"/>
+      <c r="A44" s="38"/>
+      <c r="B44" s="48"/>
+      <c r="C44" s="51"/>
       <c r="D44" s="7" t="s">
         <v>18</v>
       </c>
@@ -4433,13 +4433,13 @@
       <c r="AN44" s="5"/>
       <c r="AO44" s="5"/>
       <c r="AP44" s="5"/>
-      <c r="AQ44" s="36"/>
-      <c r="AR44" s="26"/>
+      <c r="AQ44" s="45"/>
+      <c r="AR44" s="42"/>
     </row>
     <row r="45" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="49"/>
-      <c r="B45" s="41"/>
-      <c r="C45" s="30"/>
+      <c r="A45" s="38"/>
+      <c r="B45" s="48"/>
+      <c r="C45" s="51"/>
       <c r="D45" s="8" t="s">
         <v>19</v>
       </c>
@@ -4484,13 +4484,13 @@
       <c r="AN45" s="5"/>
       <c r="AO45" s="5"/>
       <c r="AP45" s="5"/>
-      <c r="AQ45" s="36"/>
-      <c r="AR45" s="26"/>
+      <c r="AQ45" s="45"/>
+      <c r="AR45" s="42"/>
     </row>
     <row r="46" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="49"/>
-      <c r="B46" s="41"/>
-      <c r="C46" s="30"/>
+      <c r="A46" s="38"/>
+      <c r="B46" s="48"/>
+      <c r="C46" s="51"/>
       <c r="D46" s="9" t="s">
         <v>20</v>
       </c>
@@ -4535,13 +4535,13 @@
       </c>
       <c r="AO46" s="5"/>
       <c r="AP46" s="5"/>
-      <c r="AQ46" s="36"/>
-      <c r="AR46" s="26"/>
+      <c r="AQ46" s="45"/>
+      <c r="AR46" s="42"/>
     </row>
     <row r="47" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="49"/>
-      <c r="B47" s="41"/>
-      <c r="C47" s="30"/>
+      <c r="A47" s="38"/>
+      <c r="B47" s="48"/>
+      <c r="C47" s="51"/>
       <c r="D47" s="9" t="s">
         <v>21</v>
       </c>
@@ -4586,13 +4586,13 @@
         <v>0</v>
       </c>
       <c r="AP47" s="5"/>
-      <c r="AQ47" s="36"/>
-      <c r="AR47" s="26"/>
+      <c r="AQ47" s="45"/>
+      <c r="AR47" s="42"/>
     </row>
     <row r="48" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="49"/>
-      <c r="B48" s="42"/>
-      <c r="C48" s="31"/>
+      <c r="A48" s="38"/>
+      <c r="B48" s="49"/>
+      <c r="C48" s="52"/>
       <c r="D48" s="10" t="s">
         <v>22</v>
       </c>
@@ -4637,15 +4637,15 @@
         <f>SUM(E48:AI48)</f>
         <v>0</v>
       </c>
-      <c r="AQ48" s="37"/>
-      <c r="AR48" s="27"/>
+      <c r="AQ48" s="46"/>
+      <c r="AR48" s="43"/>
     </row>
     <row r="49" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="48"/>
-      <c r="B49" s="40">
+      <c r="A49" s="37"/>
+      <c r="B49" s="47">
         <v>7</v>
       </c>
-      <c r="C49" s="29" t="s">
+      <c r="C49" s="50" t="s">
         <v>15</v>
       </c>
       <c r="D49" s="3" t="s">
@@ -4692,16 +4692,16 @@
       <c r="AN49" s="5"/>
       <c r="AO49" s="5"/>
       <c r="AP49" s="5"/>
-      <c r="AQ49" s="35">
+      <c r="AQ49" s="44">
         <f>COUNTIF(E49:AI49,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR49" s="25"/>
+      <c r="AR49" s="41"/>
     </row>
     <row r="50" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="49"/>
-      <c r="B50" s="41"/>
-      <c r="C50" s="30"/>
+      <c r="A50" s="38"/>
+      <c r="B50" s="48"/>
+      <c r="C50" s="51"/>
       <c r="D50" s="6" t="s">
         <v>17</v>
       </c>
@@ -4746,13 +4746,13 @@
       <c r="AN50" s="5"/>
       <c r="AO50" s="5"/>
       <c r="AP50" s="5"/>
-      <c r="AQ50" s="36"/>
-      <c r="AR50" s="26"/>
+      <c r="AQ50" s="45"/>
+      <c r="AR50" s="42"/>
     </row>
     <row r="51" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="49"/>
-      <c r="B51" s="41"/>
-      <c r="C51" s="30"/>
+      <c r="A51" s="38"/>
+      <c r="B51" s="48"/>
+      <c r="C51" s="51"/>
       <c r="D51" s="7" t="s">
         <v>18</v>
       </c>
@@ -4797,13 +4797,13 @@
       <c r="AN51" s="5"/>
       <c r="AO51" s="5"/>
       <c r="AP51" s="5"/>
-      <c r="AQ51" s="36"/>
-      <c r="AR51" s="26"/>
+      <c r="AQ51" s="45"/>
+      <c r="AR51" s="42"/>
     </row>
     <row r="52" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="49"/>
-      <c r="B52" s="41"/>
-      <c r="C52" s="30"/>
+      <c r="A52" s="38"/>
+      <c r="B52" s="48"/>
+      <c r="C52" s="51"/>
       <c r="D52" s="8" t="s">
         <v>19</v>
       </c>
@@ -4848,13 +4848,13 @@
       <c r="AN52" s="5"/>
       <c r="AO52" s="5"/>
       <c r="AP52" s="5"/>
-      <c r="AQ52" s="36"/>
-      <c r="AR52" s="26"/>
+      <c r="AQ52" s="45"/>
+      <c r="AR52" s="42"/>
     </row>
     <row r="53" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="49"/>
-      <c r="B53" s="41"/>
-      <c r="C53" s="30"/>
+      <c r="A53" s="38"/>
+      <c r="B53" s="48"/>
+      <c r="C53" s="51"/>
       <c r="D53" s="9" t="s">
         <v>20</v>
       </c>
@@ -4899,13 +4899,13 @@
       </c>
       <c r="AO53" s="5"/>
       <c r="AP53" s="5"/>
-      <c r="AQ53" s="36"/>
-      <c r="AR53" s="26"/>
+      <c r="AQ53" s="45"/>
+      <c r="AR53" s="42"/>
     </row>
     <row r="54" spans="1:44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="49"/>
-      <c r="B54" s="41"/>
-      <c r="C54" s="30"/>
+      <c r="A54" s="38"/>
+      <c r="B54" s="48"/>
+      <c r="C54" s="51"/>
       <c r="D54" s="9" t="s">
         <v>21</v>
       </c>
@@ -4950,13 +4950,13 @@
         <v>0</v>
       </c>
       <c r="AP54" s="5"/>
-      <c r="AQ54" s="36"/>
-      <c r="AR54" s="26"/>
+      <c r="AQ54" s="45"/>
+      <c r="AR54" s="42"/>
     </row>
     <row r="55" spans="1:44" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="49"/>
-      <c r="B55" s="42"/>
-      <c r="C55" s="31"/>
+      <c r="A55" s="38"/>
+      <c r="B55" s="49"/>
+      <c r="C55" s="52"/>
       <c r="D55" s="10" t="s">
         <v>22</v>
       </c>
@@ -5001,15 +5001,15 @@
         <f>SUM(E55:AI55)</f>
         <v>0</v>
       </c>
-      <c r="AQ55" s="37"/>
-      <c r="AR55" s="27"/>
+      <c r="AQ55" s="46"/>
+      <c r="AR55" s="43"/>
     </row>
     <row r="56" spans="1:44" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="48"/>
-      <c r="B56" s="40">
+      <c r="A56" s="37"/>
+      <c r="B56" s="47">
         <v>8</v>
       </c>
-      <c r="C56" s="29" t="s">
+      <c r="C56" s="50" t="s">
         <v>15</v>
       </c>
       <c r="D56" s="3" t="s">
@@ -5056,16 +5056,16 @@
       <c r="AN56" s="5"/>
       <c r="AO56" s="5"/>
       <c r="AP56" s="5"/>
-      <c r="AQ56" s="35">
+      <c r="AQ56" s="44">
         <f>COUNTIF(E56:AI56,"&gt;0")</f>
         <v>0</v>
       </c>
-      <c r="AR56" s="25"/>
+      <c r="AR56" s="41"/>
     </row>
     <row r="57" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="49"/>
-      <c r="B57" s="41"/>
-      <c r="C57" s="30"/>
+      <c r="A57" s="38"/>
+      <c r="B57" s="48"/>
+      <c r="C57" s="51"/>
       <c r="D57" s="6" t="s">
         <v>17</v>
       </c>
@@ -5110,13 +5110,13 @@
       <c r="AN57" s="5"/>
       <c r="AO57" s="5"/>
       <c r="AP57" s="5"/>
-      <c r="AQ57" s="36"/>
-      <c r="AR57" s="26"/>
+      <c r="AQ57" s="45"/>
+      <c r="AR57" s="42"/>
     </row>
     <row r="58" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="49"/>
-      <c r="B58" s="41"/>
-      <c r="C58" s="30"/>
+      <c r="A58" s="38"/>
+      <c r="B58" s="48"/>
+      <c r="C58" s="51"/>
       <c r="D58" s="7" t="s">
         <v>18</v>
       </c>
@@ -5161,13 +5161,13 @@
       <c r="AN58" s="5"/>
       <c r="AO58" s="5"/>
       <c r="AP58" s="5"/>
-      <c r="AQ58" s="36"/>
-      <c r="AR58" s="26"/>
+      <c r="AQ58" s="45"/>
+      <c r="AR58" s="42"/>
     </row>
     <row r="59" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="49"/>
-      <c r="B59" s="41"/>
-      <c r="C59" s="30"/>
+      <c r="A59" s="38"/>
+      <c r="B59" s="48"/>
+      <c r="C59" s="51"/>
       <c r="D59" s="8" t="s">
         <v>19</v>
       </c>
@@ -5212,13 +5212,13 @@
       <c r="AN59" s="5"/>
       <c r="AO59" s="5"/>
       <c r="AP59" s="5"/>
-      <c r="AQ59" s="36"/>
-      <c r="AR59" s="26"/>
+      <c r="AQ59" s="45"/>
+      <c r="AR59" s="42"/>
     </row>
     <row r="60" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="49"/>
-      <c r="B60" s="41"/>
-      <c r="C60" s="30"/>
+      <c r="A60" s="38"/>
+      <c r="B60" s="48"/>
+      <c r="C60" s="51"/>
       <c r="D60" s="9" t="s">
         <v>20</v>
       </c>
@@ -5263,13 +5263,13 @@
       </c>
       <c r="AO60" s="5"/>
       <c r="AP60" s="5"/>
-      <c r="AQ60" s="36"/>
-      <c r="AR60" s="26"/>
+      <c r="AQ60" s="45"/>
+      <c r="AR60" s="42"/>
     </row>
     <row r="61" spans="1:44" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="49"/>
-      <c r="B61" s="41"/>
-      <c r="C61" s="30"/>
+      <c r="A61" s="38"/>
+      <c r="B61" s="48"/>
+      <c r="C61" s="51"/>
       <c r="D61" s="9" t="s">
         <v>21</v>
       </c>
@@ -5314,13 +5314,13 @@
         <v>0</v>
       </c>
       <c r="AP61" s="5"/>
-      <c r="AQ61" s="36"/>
-      <c r="AR61" s="26"/>
+      <c r="AQ61" s="45"/>
+      <c r="AR61" s="42"/>
     </row>
     <row r="62" spans="1:44" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="49"/>
-      <c r="B62" s="42"/>
-      <c r="C62" s="31"/>
+      <c r="A62" s="38"/>
+      <c r="B62" s="49"/>
+      <c r="C62" s="52"/>
       <c r="D62" s="10" t="s">
         <v>22</v>
       </c>
@@ -5365,49 +5365,49 @@
         <f>SUM(E62:AI62)</f>
         <v>0</v>
       </c>
-      <c r="AQ62" s="37"/>
-      <c r="AR62" s="27"/>
+      <c r="AQ62" s="46"/>
+      <c r="AR62" s="43"/>
     </row>
     <row r="63" spans="1:44" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="14"/>
-      <c r="B63" s="43" t="s">
+      <c r="B63" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="C63" s="44"/>
-      <c r="D63" s="45"/>
-      <c r="E63" s="32" t="s">
+      <c r="C63" s="65"/>
+      <c r="D63" s="66"/>
+      <c r="E63" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="F63" s="33"/>
-      <c r="G63" s="33"/>
-      <c r="H63" s="33"/>
-      <c r="I63" s="33"/>
-      <c r="J63" s="33"/>
-      <c r="K63" s="33"/>
-      <c r="L63" s="33"/>
-      <c r="M63" s="33"/>
-      <c r="N63" s="33"/>
-      <c r="O63" s="33"/>
-      <c r="P63" s="33"/>
-      <c r="Q63" s="33"/>
-      <c r="R63" s="33"/>
-      <c r="S63" s="33"/>
-      <c r="T63" s="33"/>
-      <c r="U63" s="33"/>
-      <c r="V63" s="33"/>
-      <c r="W63" s="33"/>
-      <c r="X63" s="33"/>
-      <c r="Y63" s="33"/>
-      <c r="Z63" s="33"/>
-      <c r="AA63" s="33"/>
-      <c r="AB63" s="33"/>
-      <c r="AC63" s="33"/>
-      <c r="AD63" s="33"/>
-      <c r="AE63" s="33"/>
-      <c r="AF63" s="33"/>
-      <c r="AG63" s="33"/>
-      <c r="AH63" s="33"/>
-      <c r="AI63" s="34"/>
+      <c r="F63" s="61"/>
+      <c r="G63" s="61"/>
+      <c r="H63" s="61"/>
+      <c r="I63" s="61"/>
+      <c r="J63" s="61"/>
+      <c r="K63" s="61"/>
+      <c r="L63" s="61"/>
+      <c r="M63" s="61"/>
+      <c r="N63" s="61"/>
+      <c r="O63" s="61"/>
+      <c r="P63" s="61"/>
+      <c r="Q63" s="61"/>
+      <c r="R63" s="61"/>
+      <c r="S63" s="61"/>
+      <c r="T63" s="61"/>
+      <c r="U63" s="61"/>
+      <c r="V63" s="61"/>
+      <c r="W63" s="61"/>
+      <c r="X63" s="61"/>
+      <c r="Y63" s="61"/>
+      <c r="Z63" s="61"/>
+      <c r="AA63" s="61"/>
+      <c r="AB63" s="61"/>
+      <c r="AC63" s="61"/>
+      <c r="AD63" s="61"/>
+      <c r="AE63" s="61"/>
+      <c r="AF63" s="61"/>
+      <c r="AG63" s="61"/>
+      <c r="AH63" s="61"/>
+      <c r="AI63" s="62"/>
       <c r="AJ63" s="13">
         <f t="shared" ref="AJ63:AP63" si="0">SUM(AJ7:AJ55)</f>
         <v>0</v>
@@ -5436,25 +5436,55 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AQ63" s="46" t="s">
+      <c r="AQ63" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="AR63" s="47"/>
+      <c r="AR63" s="68"/>
     </row>
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="w6+d9vq8zxqtwz/8oCCG3BYbliNfWePL8hHRwEiEML+sUltfeBK5YuPzjAH7ITn1+ejY8h++fEUHCYBUW55TsA==" saltValue="JcN4p5PNyCVpkOl5Pyg2uQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="68">
-    <mergeCell ref="E1:V1"/>
-    <mergeCell ref="U3:V3"/>
-    <mergeCell ref="E2:L2"/>
-    <mergeCell ref="E4:AQ4"/>
-    <mergeCell ref="AQ5:AQ6"/>
-    <mergeCell ref="X2:AB2"/>
-    <mergeCell ref="M2:P2"/>
-    <mergeCell ref="Q2:W2"/>
-    <mergeCell ref="Q3:T3"/>
-    <mergeCell ref="M3:P3"/>
-    <mergeCell ref="AP5:AP6"/>
+    <mergeCell ref="B1:D2"/>
+    <mergeCell ref="AR14:AR20"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="C14:C20"/>
+    <mergeCell ref="E63:AI63"/>
+    <mergeCell ref="AQ56:AQ62"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="B42:B48"/>
+    <mergeCell ref="B14:B20"/>
+    <mergeCell ref="C35:C41"/>
+    <mergeCell ref="AR35:AR41"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="AQ49:AQ55"/>
+    <mergeCell ref="C28:C34"/>
+    <mergeCell ref="AQ63:AR63"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="B56:B62"/>
+    <mergeCell ref="AR56:AR62"/>
+    <mergeCell ref="A49:A55"/>
+    <mergeCell ref="C42:C48"/>
+    <mergeCell ref="C49:C55"/>
+    <mergeCell ref="AR49:AR55"/>
+    <mergeCell ref="C56:C62"/>
+    <mergeCell ref="A56:A62"/>
+    <mergeCell ref="A42:A48"/>
+    <mergeCell ref="AQ42:AQ48"/>
+    <mergeCell ref="B49:B55"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="AR5:AR6"/>
+    <mergeCell ref="AO5:AO6"/>
+    <mergeCell ref="C21:C27"/>
+    <mergeCell ref="AN5:AN6"/>
+    <mergeCell ref="AR21:AR27"/>
+    <mergeCell ref="AQ35:AQ41"/>
+    <mergeCell ref="C7:C13"/>
+    <mergeCell ref="B7:B13"/>
+    <mergeCell ref="AR7:AR13"/>
+    <mergeCell ref="B21:B27"/>
+    <mergeCell ref="AQ7:AQ13"/>
+    <mergeCell ref="AQ21:AQ27"/>
     <mergeCell ref="A7:A13"/>
     <mergeCell ref="A28:A34"/>
     <mergeCell ref="A14:A20"/>
@@ -5471,47 +5501,17 @@
     <mergeCell ref="AK5:AK6"/>
     <mergeCell ref="AM5:AM6"/>
     <mergeCell ref="AL5:AL6"/>
-    <mergeCell ref="AQ35:AQ41"/>
-    <mergeCell ref="C7:C13"/>
-    <mergeCell ref="B7:B13"/>
-    <mergeCell ref="AR7:AR13"/>
-    <mergeCell ref="B21:B27"/>
-    <mergeCell ref="AQ7:AQ13"/>
-    <mergeCell ref="AQ21:AQ27"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="AR5:AR6"/>
-    <mergeCell ref="AO5:AO6"/>
-    <mergeCell ref="C21:C27"/>
-    <mergeCell ref="AN5:AN6"/>
-    <mergeCell ref="AR21:AR27"/>
-    <mergeCell ref="B56:B62"/>
-    <mergeCell ref="AR56:AR62"/>
-    <mergeCell ref="A49:A55"/>
-    <mergeCell ref="C42:C48"/>
-    <mergeCell ref="C49:C55"/>
-    <mergeCell ref="AR49:AR55"/>
-    <mergeCell ref="C56:C62"/>
-    <mergeCell ref="A56:A62"/>
-    <mergeCell ref="A42:A48"/>
-    <mergeCell ref="AQ42:AQ48"/>
-    <mergeCell ref="B49:B55"/>
-    <mergeCell ref="B1:D2"/>
-    <mergeCell ref="AR14:AR20"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="C14:C20"/>
-    <mergeCell ref="E63:AI63"/>
-    <mergeCell ref="AQ56:AQ62"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="B42:B48"/>
-    <mergeCell ref="B14:B20"/>
-    <mergeCell ref="C35:C41"/>
-    <mergeCell ref="AR35:AR41"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="AQ49:AQ55"/>
-    <mergeCell ref="C28:C34"/>
-    <mergeCell ref="AQ63:AR63"/>
-    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="E1:V1"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="E2:L2"/>
+    <mergeCell ref="E4:AQ4"/>
+    <mergeCell ref="AQ5:AQ6"/>
+    <mergeCell ref="X2:AB2"/>
+    <mergeCell ref="M2:P2"/>
+    <mergeCell ref="Q2:W2"/>
+    <mergeCell ref="Q3:T3"/>
+    <mergeCell ref="M3:P3"/>
+    <mergeCell ref="AP5:AP6"/>
   </mergeCells>
   <conditionalFormatting sqref="E6">
     <cfRule type="expression" dxfId="61" priority="188">
